--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7746EB5E-B456-48BC-9C81-648DA15CC65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED23739-6419-4747-8C0C-2E4D1CC64B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FİNANSAL MATEMATİK-LİNKLER" sheetId="2" r:id="rId1"/>
-    <sheet name="12MMM-LİNKLER" sheetId="1" r:id="rId2"/>
+    <sheet name="FM-LİNKLER" sheetId="2" r:id="rId1"/>
+    <sheet name="MM-LİNKLER" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="107">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Kitabın Adı:</t>
   </si>
   <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=9d8b9db09fecc05d285f4bcad7185826&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=251677fc058ee3b10e18d14c37525eb6&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
   <si>
@@ -221,12 +218,6 @@
     <t>fm_elim_mk</t>
   </si>
   <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=86c9439bf4e5b2db3a9d24e61a2fcc65&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>fm_geomatik_mk</t>
-  </si>
-  <si>
     <t>http://kitap.eba.gov.tr/KodSor.php?KOD=51890</t>
   </si>
   <si>
@@ -309,6 +300,75 @@
   </si>
   <si>
     <t>http://kitap.eba.gov.tr/KodSor.php?KOD=41521</t>
+  </si>
+  <si>
+    <t>49, 120, 121, 123</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>FİNANSAL MATEMATİK KİTABINDA YER ALAN KAREKOD BİLGİLERİ (MUĞLA - ORTACA - MATEMATİK)</t>
+  </si>
+  <si>
+    <t>mm_analitik11_mk</t>
+  </si>
+  <si>
+    <t>Ek Sorular 1.1</t>
+  </si>
+  <si>
+    <t>Ek Sorular 1.2</t>
+  </si>
+  <si>
+    <t>mm_eksorular11_mk</t>
+  </si>
+  <si>
+    <t>mm_eksorular12_mk</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52347</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52348</t>
+  </si>
+  <si>
+    <t>mm_analitik12_mk</t>
+  </si>
+  <si>
+    <t>mm_analitik13_mk</t>
+  </si>
+  <si>
+    <t>mm_geo3d_mk</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme_mk</t>
+  </si>
+  <si>
+    <t>mm_oruntuler_mk</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=48591</t>
+  </si>
+  <si>
+    <t>mm_anakarekod1_mk</t>
+  </si>
+  <si>
+    <t>mm_anakarekod2_mk</t>
+  </si>
+  <si>
+    <t>geomatik_mk</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=b780f6113706fa6f5bc3bcd9cdbf1882&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=3a366eae039c995967f81d931b83e088&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=ff629ee7538b1018ed436d0d5a58e1c3&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=880fe137ea71f2d5776e6d74b4fec7ab&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
 </sst>
 </file>
@@ -432,9 +492,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -493,7 +552,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Köprü" xfId="1" builtinId="8"/>
@@ -778,317 +836,343 @@
   <dimension ref="B2:F26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="118" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.77734375" style="5"/>
+    <col min="1" max="1" width="1.44140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="3.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="43.109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="118" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3">
+        <v>59</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="14" t="s">
+      <c r="E7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3">
+        <v>67</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="12" t="s">
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="7">
+        <v>32</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="7">
+        <v>63</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="12" t="s">
+      <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="7">
+        <v>81</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
+      <c r="E12" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="7">
+        <v>115</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="7">
+        <v>127</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7">
         <v>11</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="12" t="s">
+      <c r="D15" s="14" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="15" t="s">
+      <c r="E15" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="7">
+        <v>35</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="7">
         <v>65</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="12" t="s">
+      <c r="D17" s="14" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="15" t="s">
+      <c r="E17" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="7">
+        <v>83</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E18" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="15" t="s">
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="7">
+        <v>117</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E19" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="7"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="7"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="7"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1109,297 +1193,333 @@
   <dimension ref="B2:F26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="117.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.77734375" style="5"/>
+    <col min="1" max="1" width="4.44140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="117.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="12" t="s">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="12" t="s">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="12" t="s">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="12" t="s">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED23739-6419-4747-8C0C-2E4D1CC64B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366878E4-1128-4387-BC15-E779F090369C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FM-LİNKLER" sheetId="2" r:id="rId1"/>
-    <sheet name="MM-LİNKLER" sheetId="1" r:id="rId2"/>
+    <sheet name="MM-LİNKLER" sheetId="1" r:id="rId1"/>
+    <sheet name="FM-LİNKLER" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,12 +26,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="152">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
-  </si>
-  <si>
-    <t>SIRA NO</t>
   </si>
   <si>
     <t>1.</t>
@@ -116,9 +113,6 @@
     <t>Ana Karekod-1</t>
   </si>
   <si>
-    <t>Ön Değerlendirme-1</t>
-  </si>
-  <si>
     <t>Örüntüler</t>
   </si>
   <si>
@@ -152,21 +146,6 @@
     <t>Kitabın Adı:</t>
   </si>
   <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=251677fc058ee3b10e18d14c37525eb6&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=be62538f287b7806975aef409457abaa&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=e39eb25e1261f225dea1789c01ffca28&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=902df93a6823515ff081e75bbcad5574&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=bf81b22bc3e09ec92b23259113f3c190&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
     <t>11.</t>
   </si>
   <si>
@@ -341,9 +320,6 @@
     <t>mm_geo3d_mk</t>
   </si>
   <si>
-    <t>mm_ondegerlendirme_mk</t>
-  </si>
-  <si>
     <t>mm_oruntuler_mk</t>
   </si>
   <si>
@@ -362,13 +338,173 @@
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=b780f6113706fa6f5bc3bcd9cdbf1882&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
   <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=3a366eae039c995967f81d931b83e088&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=ff629ee7538b1018ed436d0d5a58e1c3&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
   <si>
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=880fe137ea71f2d5776e6d74b4fec7ab&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>Analitik-21</t>
+  </si>
+  <si>
+    <t>Analitik-22</t>
+  </si>
+  <si>
+    <t>mm_analitik21_mk</t>
+  </si>
+  <si>
+    <t>mm_analitik22_mk</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme21_mk</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-21</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-22</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme22_mk</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-23</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme23_mk</t>
+  </si>
+  <si>
+    <t>21.</t>
+  </si>
+  <si>
+    <t>22.</t>
+  </si>
+  <si>
+    <t>23.</t>
+  </si>
+  <si>
+    <t>24.</t>
+  </si>
+  <si>
+    <t>25.</t>
+  </si>
+  <si>
+    <t>Ek Sorular 2.1</t>
+  </si>
+  <si>
+    <t>Ek Sorular 2.2</t>
+  </si>
+  <si>
+    <t>mm_eksorular21_mk</t>
+  </si>
+  <si>
+    <t>mm_eksorular22_mk</t>
+  </si>
+  <si>
+    <t>Ek Sorular 2.3</t>
+  </si>
+  <si>
+    <t>mm_eksorular23_mk</t>
+  </si>
+  <si>
+    <t>Analitik-23</t>
+  </si>
+  <si>
+    <t>mm_analitik23_mk</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-11</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-12</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme11_mk</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme12_mk</t>
+  </si>
+  <si>
+    <t>SIRA
+NO</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=99edf4198ffc5b61f1aae1a88abd013f&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=5cf0d7e1d57932e265462ef39900459f&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=c2f584a430ac9307a21edbd704102f37&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=9f1457c904bfe7b75d635a5740b4ca65&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=d1860211c4c09861e463ecb946837db4&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=f27332d8ab927a4cb0c9cf8385b6fcd2&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=4a4eb497d0558f901f59b55ffb3b691b&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=80a702ca926c2831f7c7b0a2cbb14a58&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=b48cb6aa85e43344316cc6d426e59a99&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=b3759cc218afb17430c7d5ae350938e3&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=338faead5a079b1627c2ae817884fdcc&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=06d5c6078148bb8140f45158ab1a3527&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=8524be2a4bd7cd5b1f0932a39a75b4dd&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=59ff5ede0f948abc42079ea7c8b71b0f&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=9e7cc7a9ebbd34446f73a07b2868e6f2&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=cd5784ba09b45b9b4d43514d3e605510&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52537</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52538</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52540</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52539</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52541</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52542</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52543</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52545</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52544</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52546</t>
   </si>
 </sst>
 </file>
@@ -419,12 +555,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -492,7 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -537,6 +679,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -551,6 +696,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -832,347 +990,462 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DCAFFA-9F6E-4338-BECC-2378BDDBC781}">
-  <dimension ref="B2:F26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:F31"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.44140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="43.109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="118" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="117.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18" t="s">
+      <c r="B3" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21"/>
+    </row>
+    <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20"/>
-    </row>
-    <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>85</v>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>52</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3">
-        <v>59</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>51</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3">
-        <v>67</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>123</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>103</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="7">
-        <v>32</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>59</v>
+        <v>10</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>69</v>
+        <v>25</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7">
-        <v>63</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>60</v>
+        <v>11</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>70</v>
+        <v>91</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="7">
-        <v>81</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>61</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
+        <v>28</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="7">
-        <v>115</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>62</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="7">
-        <v>127</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>63</v>
+        <v>14</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>73</v>
+        <v>30</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="7">
-        <v>11</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>74</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="7">
-        <v>35</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>75</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="9"/>
+        <v>85</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="7">
-        <v>65</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>76</v>
+        <v>32</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="7">
-        <v>83</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="26"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="7">
-        <v>117</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>78</v>
+        <v>34</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="9"/>
+        <v>43</v>
+      </c>
+      <c r="F19" s="26"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
+        <v>40</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
+        <v>41</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="26"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="26"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1189,334 +1462,344 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DCAFFA-9F6E-4338-BECC-2378BDDBC781}">
   <dimension ref="B2:F26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="117.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="3.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="43.109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="118" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18" t="s">
+      <c r="B3" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21"/>
+    </row>
+    <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20"/>
-    </row>
-    <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>59</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>97</v>
+        <v>2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>67</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>98</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>102</v>
+        <v>10</v>
+      </c>
+      <c r="C10" s="7">
+        <v>32</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>87</v>
+        <v>11</v>
+      </c>
+      <c r="C11" s="7">
+        <v>63</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>94</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="7">
+        <v>81</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>95</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="7">
+        <v>115</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>96</v>
+        <v>14</v>
+      </c>
+      <c r="C14" s="7">
+        <v>127</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>90</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="7">
+        <v>11</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>106</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>91</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="7">
+        <v>35</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>105</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="C17" s="7">
+        <v>65</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="F17" s="9"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>101</v>
+        <v>33</v>
+      </c>
+      <c r="C18" s="7">
+        <v>83</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F18" s="9"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="C19" s="7">
+        <v>117</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>76</v>
+      </c>
       <c r="F19" s="9"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
+        <v>35</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="14"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="C21" s="7"/>
       <c r="D21" s="10"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="10"/>
+        <v>37</v>
+      </c>
+      <c r="C22" s="7"/>
       <c r="D22" s="10"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="10"/>
+        <v>38</v>
+      </c>
+      <c r="C23" s="7"/>
       <c r="D23" s="10"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="C24" s="7"/>
       <c r="D24" s="10"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="C25" s="7"/>
       <c r="D25" s="10"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="C26" s="7"/>
       <c r="D26" s="10"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366878E4-1128-4387-BC15-E779F090369C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42CEDFA-95FA-41BB-8581-00127746F2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -555,21 +555,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -629,12 +623,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -679,8 +686,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -697,18 +713,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1004,35 +1019,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
@@ -1048,7 +1063,7 @@
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="25" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1062,48 +1077,48 @@
       <c r="B7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="26" t="s">
         <v>92</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="27" t="s">
         <v>123</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1111,16 +1126,16 @@
       <c r="B10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="27" t="s">
         <v>90</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="11" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1128,16 +1143,16 @@
       <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="27" t="s">
         <v>94</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="11" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1145,16 +1160,16 @@
       <c r="B12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="27" t="s">
         <v>80</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="11" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1162,16 +1177,16 @@
       <c r="B13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="27" t="s">
         <v>87</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="11" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1179,16 +1194,16 @@
       <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="27" t="s">
         <v>88</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="11" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1196,16 +1211,16 @@
       <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="27" t="s">
         <v>89</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="11" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1213,16 +1228,16 @@
       <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="27" t="s">
         <v>83</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="11" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1230,16 +1245,16 @@
       <c r="B17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="11" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1247,40 +1262,40 @@
       <c r="B18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="27"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="26"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="27" t="s">
         <v>93</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="26"/>
+      <c r="F19" s="17"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="11" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1288,16 +1303,16 @@
       <c r="B21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="11" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1305,16 +1320,16 @@
       <c r="B22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="11" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1322,16 +1337,16 @@
       <c r="B23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="11" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1339,16 +1354,16 @@
       <c r="B24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="11" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1356,16 +1371,16 @@
       <c r="B25" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1373,16 +1388,16 @@
       <c r="B26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="11" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1390,16 +1405,16 @@
       <c r="B27" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="11" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1407,16 +1422,16 @@
       <c r="B28" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="11" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1427,7 +1442,7 @@
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="26"/>
+      <c r="F29" s="17"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
@@ -1436,7 +1451,7 @@
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="26"/>
+      <c r="F30" s="17"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
@@ -1445,7 +1460,7 @@
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
       <c r="E31" s="9"/>
-      <c r="F31" s="26"/>
+      <c r="F31" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1476,35 +1491,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42CEDFA-95FA-41BB-8581-00127746F2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0D45B0-9B33-4BFB-BF58-AC2E40EF65D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="156">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -176,9 +176,6 @@
     <t>20.</t>
   </si>
   <si>
-    <t>Ana Karekod-2</t>
-  </si>
-  <si>
     <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47957</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
     <t>mm_anakarekod1_mk</t>
   </si>
   <si>
-    <t>mm_anakarekod2_mk</t>
-  </si>
-  <si>
     <t>geomatik_mk</t>
   </si>
   <si>
@@ -344,36 +338,6 @@
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=880fe137ea71f2d5776e6d74b4fec7ab&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
   <si>
-    <t>Analitik-21</t>
-  </si>
-  <si>
-    <t>Analitik-22</t>
-  </si>
-  <si>
-    <t>mm_analitik21_mk</t>
-  </si>
-  <si>
-    <t>mm_analitik22_mk</t>
-  </si>
-  <si>
-    <t>mm_ondegerlendirme21_mk</t>
-  </si>
-  <si>
-    <t>Ön Değerlendirme-21</t>
-  </si>
-  <si>
-    <t>Ön Değerlendirme-22</t>
-  </si>
-  <si>
-    <t>mm_ondegerlendirme22_mk</t>
-  </si>
-  <si>
-    <t>Ön Değerlendirme-23</t>
-  </si>
-  <si>
-    <t>mm_ondegerlendirme23_mk</t>
-  </si>
-  <si>
     <t>21.</t>
   </si>
   <si>
@@ -387,30 +351,6 @@
   </si>
   <si>
     <t>25.</t>
-  </si>
-  <si>
-    <t>Ek Sorular 2.1</t>
-  </si>
-  <si>
-    <t>Ek Sorular 2.2</t>
-  </si>
-  <si>
-    <t>mm_eksorular21_mk</t>
-  </si>
-  <si>
-    <t>mm_eksorular22_mk</t>
-  </si>
-  <si>
-    <t>Ek Sorular 2.3</t>
-  </si>
-  <si>
-    <t>mm_eksorular23_mk</t>
-  </si>
-  <si>
-    <t>Analitik-23</t>
-  </si>
-  <si>
-    <t>mm_analitik23_mk</t>
   </si>
   <si>
     <t>Ön Değerlendirme-11</t>
@@ -505,6 +445,78 @@
   </si>
   <si>
     <t>http://kitap.eba.gov.tr/KodSor.php?KOD=52546</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=53141</t>
+  </si>
+  <si>
+    <t>Tarihçe Etkinlik 4.2</t>
+  </si>
+  <si>
+    <t>mm_tarihceetkinlik_mk</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=2974b2acf1c7674064ced91034746658&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>Ana Karekod-4</t>
+  </si>
+  <si>
+    <t>Analitik-41</t>
+  </si>
+  <si>
+    <t>Analitik-42</t>
+  </si>
+  <si>
+    <t>Analitik-43</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-41</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-42</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-43</t>
+  </si>
+  <si>
+    <t>Ek Sorular 4.1</t>
+  </si>
+  <si>
+    <t>Ek Sorular 4.2</t>
+  </si>
+  <si>
+    <t>Ek Sorular 4.3</t>
+  </si>
+  <si>
+    <t>mm_eksorular41_mk</t>
+  </si>
+  <si>
+    <t>mm_eksorular42_mk</t>
+  </si>
+  <si>
+    <t>mm_eksorular43_mk</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme41_mk</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme42_mk</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme43_mk</t>
+  </si>
+  <si>
+    <t>mm_anakarekod4_mk</t>
+  </si>
+  <si>
+    <t>mm_analitik41_mk</t>
+  </si>
+  <si>
+    <t>mm_analitik42_mk</t>
+  </si>
+  <si>
+    <t>mm_analitik43_mk</t>
   </si>
 </sst>
 </file>
@@ -641,7 +653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -698,6 +710,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -713,17 +728,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1006,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F31"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
@@ -1019,35 +1026,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
@@ -1058,13 +1065,13 @@
     </row>
     <row r="6" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="25" t="s">
-        <v>45</v>
+      <c r="D6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1080,8 +1087,8 @@
       <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>92</v>
+      <c r="D7" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>18</v>
@@ -1093,16 +1100,16 @@
         <v>2</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>123</v>
+        <v>101</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -1110,343 +1117,351 @@
         <v>9</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" t="s">
-        <v>142</v>
-      </c>
       <c r="F9" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>90</v>
+      <c r="D10" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>94</v>
+      <c r="D11" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="27" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>80</v>
+      <c r="D12" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>87</v>
+      <c r="D13" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>88</v>
+      <c r="D14" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>30</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="27" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>89</v>
+      <c r="D15" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D17" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>86</v>
-      </c>
       <c r="F17" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="27" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="9"/>
       <c r="F18" s="17"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="27" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>43</v>
-      </c>
       <c r="F19" s="17"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="27" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="F20" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="D29" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="27" t="s">
         <v>99</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="17"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -1454,13 +1469,19 @@
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="7" t="s">
-        <v>112</v>
+      <c r="B31" s="27" t="s">
+        <v>100</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
       <c r="E31" s="9"/>
       <c r="F31" s="17"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1491,35 +1512,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
@@ -1530,13 +1551,13 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1553,13 +1574,13 @@
         <v>59</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
@@ -1570,13 +1591,13 @@
         <v>67</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -1584,16 +1605,16 @@
         <v>9</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
@@ -1604,13 +1625,13 @@
         <v>32</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
@@ -1621,13 +1642,13 @@
         <v>63</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
@@ -1638,13 +1659,13 @@
         <v>81</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
@@ -1655,13 +1676,13 @@
         <v>115</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
@@ -1672,13 +1693,13 @@
         <v>127</v>
       </c>
       <c r="D14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>57</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
@@ -1689,10 +1710,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -1704,10 +1725,10 @@
         <v>35</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -1719,10 +1740,10 @@
         <v>65</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9"/>
     </row>
@@ -1734,10 +1755,10 @@
         <v>83</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F18" s="9"/>
     </row>
@@ -1749,10 +1770,10 @@
         <v>117</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F19" s="9"/>
     </row>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0D45B0-9B33-4BFB-BF58-AC2E40EF65D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200FE63A-D738-4FB2-B688-2BBC55501AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="176">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -517,6 +517,66 @@
   </si>
   <si>
     <t>mm_analitik43_mk</t>
+  </si>
+  <si>
+    <t>26.</t>
+  </si>
+  <si>
+    <t>27.</t>
+  </si>
+  <si>
+    <t>28.</t>
+  </si>
+  <si>
+    <t>29.</t>
+  </si>
+  <si>
+    <t>30.</t>
+  </si>
+  <si>
+    <t>Ana Karekod-2</t>
+  </si>
+  <si>
+    <t>mm_anakarekod2_mk</t>
+  </si>
+  <si>
+    <t>Ek Sorular 2.1</t>
+  </si>
+  <si>
+    <t>mm_eksorular21_mk</t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme-21</t>
+  </si>
+  <si>
+    <t>mm_ondegerlendirme21_mk</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47958</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=53294</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=53295</t>
+  </si>
+  <si>
+    <t>Analitik-21</t>
+  </si>
+  <si>
+    <t>mm_analitik21_mk</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=53296</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=57c6055c0a99d9273bf9838a0b9d9ba6&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=a3d8ec681557effac25308ec06f30db8&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=3abc4d5ce17e46fbdfedc0f0ee9d7dc2&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
 </sst>
 </file>
@@ -567,15 +627,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -635,25 +701,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -704,15 +757,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -728,10 +772,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Köprü" xfId="1" builtinId="8"/>
@@ -1013,48 +1060,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:F36"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.77734375" style="4" customWidth="1"/>
     <col min="6" max="6" width="117.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23" t="s">
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
@@ -1108,29 +1155,29 @@
       <c r="E8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="11" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="10" t="s">
@@ -1147,7 +1194,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -1164,7 +1211,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="10" t="s">
@@ -1181,7 +1228,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -1198,7 +1245,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="10" t="s">
@@ -1215,7 +1262,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -1232,7 +1279,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="10" t="s">
@@ -1249,7 +1296,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -1266,7 +1313,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="10"/>
@@ -1275,213 +1322,282 @@
       <c r="F18" s="17"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" s="17"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="17"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D24" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="17"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="F24" s="17"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D25" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F25" s="11" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="10" t="s">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D26" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F26" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="10" t="s">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D27" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E27" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F27" s="25" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="8" t="s">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D28" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F28" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="8" t="s">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D29" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F29" s="11" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="8" t="s">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D30" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F30" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="10" t="s">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D31" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F31" s="11" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="10" t="s">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D32" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E32" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F32" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="10" t="s">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D33" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F33" s="11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="10" t="s">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D34" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E34" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F34" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="17"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="17"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="17"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1512,35 +1628,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23" t="s">
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200FE63A-D738-4FB2-B688-2BBC55501AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FEB834-C8BC-4999-8A62-9632563240A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="181">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -577,6 +577,21 @@
   </si>
   <si>
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=3abc4d5ce17e46fbdfedc0f0ee9d7dc2&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>31.</t>
+  </si>
+  <si>
+    <t>Tema Tanıtım Videosu-1</t>
+  </si>
+  <si>
+    <t>mm_tematanitim1_mk</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=53297</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=bc4ce7436d380db192c59959ffe06d9f&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
 </sst>
 </file>
@@ -757,6 +772,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -773,12 +792,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Köprü" xfId="1" builtinId="8"/>
@@ -1060,12 +1075,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F36"/>
+  <dimension ref="B2:F37"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43.77734375" style="4" customWidth="1"/>
     <col min="6" max="6" width="117.5546875" style="4" bestFit="1" customWidth="1"/>
@@ -1073,35 +1088,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
@@ -1146,17 +1161,17 @@
       <c r="B8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>106</v>
+      <c r="C8" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -1164,33 +1179,33 @@
         <v>9</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>21</v>
+      <c r="C10" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
@@ -1198,16 +1213,16 @@
         <v>11</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
@@ -1215,16 +1230,16 @@
         <v>12</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
@@ -1232,16 +1247,16 @@
         <v>13</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
@@ -1249,16 +1264,16 @@
         <v>14</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
@@ -1266,16 +1281,16 @@
         <v>15</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
@@ -1283,16 +1298,16 @@
         <v>16</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
@@ -1300,74 +1315,74 @@
         <v>32</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="17"/>
+      <c r="C18" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>167</v>
-      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="9"/>
       <c r="F19" s="17"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>165</v>
+      <c r="C20" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>173</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="F20" s="17"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>163</v>
+      <c r="C21" s="8" t="s">
+        <v>165</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
@@ -1375,40 +1390,42 @@
         <v>37</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="17"/>
+      <c r="C23" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>42</v>
-      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="17"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -1416,67 +1433,65 @@
         <v>40</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>113</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F25" s="17"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D27" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E27" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F27" s="11" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>116</v>
+      <c r="C28" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
@@ -1484,16 +1499,16 @@
         <v>98</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
@@ -1501,33 +1516,33 @@
         <v>99</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>143</v>
+      <c r="C31" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
@@ -1535,16 +1550,16 @@
         <v>156</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
@@ -1552,16 +1567,16 @@
         <v>157</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -1569,26 +1584,34 @@
         <v>158</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="17"/>
+      <c r="C35" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
@@ -1598,6 +1621,15 @@
       <c r="D36" s="10"/>
       <c r="E36" s="9"/>
       <c r="F36" s="17"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1628,35 +1660,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0C36BD-F907-400F-B909-D193B07708B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D41CBA3-BE2C-442A-8FC2-6FC6706D8EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="299">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -922,6 +922,40 @@
   </si>
   <si>
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=d39726eda2de1a6e08effabf907c5490&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=46837</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47957</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47958</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47959</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47960</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47961</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47962</t>
+  </si>
+  <si>
+    <t>http://kitap.eba.gov.tr/KodSor.php?KOD=47963</t>
+  </si>
+  <si>
+    <t>25, 25, 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34, 40, 42,
+48, 50, 53, 54, 57, 58, 63, 64, 72, 73, 75, 76, 79 </t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=2cb0002e70b3711dd473750d48e2cacd&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1267,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1413,18 +1447,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1434,6 +1462,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1475,6 +1509,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1763,9 +1803,9 @@
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="7.44140625" style="31" customWidth="1"/>
     <col min="3" max="3" width="6.44140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="4" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.21875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36" style="60" customWidth="1"/>
     <col min="8" max="8" width="100.6640625" style="60" customWidth="1"/>
     <col min="9" max="16384" width="8.77734375" style="4"/>
@@ -1836,7 +1876,7 @@
       <c r="G6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="65" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1844,7 +1884,7 @@
       <c r="B7" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="67" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="35">
@@ -1856,12 +1896,14 @@
       <c r="F7" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="37"/>
+      <c r="G7" s="37" t="s">
+        <v>288</v>
+      </c>
       <c r="H7" s="38"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="74"/>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="63" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="20">
@@ -1882,7 +1924,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="74"/>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="63" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="20">
@@ -1901,13 +1943,13 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="74"/>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="23">
-        <v>34</v>
+      <c r="D10" s="23" t="s">
+        <v>297</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>161</v>
@@ -1915,20 +1957,20 @@
       <c r="F10" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="82" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="83" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="74"/>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="20">
-        <v>25</v>
+      <c r="D11" s="20" t="s">
+        <v>296</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>70</v>
@@ -1945,7 +1987,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="74"/>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="63" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="20">
@@ -1966,7 +2008,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="74"/>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="63" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="20">
@@ -2000,7 +2042,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="74"/>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="20">
@@ -2021,7 +2063,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="74"/>
-      <c r="C16" s="65" t="s">
+      <c r="C16" s="63" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="20">
@@ -2055,7 +2097,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="75"/>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="64" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="40">
@@ -2086,7 +2128,7 @@
       <c r="B20" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="67" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="43">
@@ -2098,12 +2140,14 @@
       <c r="F20" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="61"/>
+      <c r="G20" s="66" t="s">
+        <v>289</v>
+      </c>
       <c r="H20" s="45"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="71"/>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="63" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="24">
@@ -2115,14 +2159,16 @@
       <c r="F21" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="46"/>
+      <c r="H21" s="47" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="71"/>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="63" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="24">
@@ -2134,7 +2180,7 @@
       <c r="F22" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="61" t="s">
         <v>175</v>
       </c>
       <c r="H22" s="47" t="s">
@@ -2149,7 +2195,7 @@
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="61" t="s">
         <v>176</v>
       </c>
       <c r="H23" s="47"/>
@@ -2162,7 +2208,7 @@
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
-      <c r="G24" s="62" t="s">
+      <c r="G24" s="61" t="s">
         <v>177</v>
       </c>
       <c r="H24" s="47"/>
@@ -2175,7 +2221,7 @@
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
       <c r="F25" s="26"/>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="61" t="s">
         <v>178</v>
       </c>
       <c r="H25" s="47"/>
@@ -2188,7 +2234,7 @@
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
-      <c r="G26" s="62" t="s">
+      <c r="G26" s="61" t="s">
         <v>179</v>
       </c>
       <c r="H26" s="47"/>
@@ -2201,14 +2247,14 @@
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
-      <c r="G27" s="62" t="s">
+      <c r="G27" s="61" t="s">
         <v>180</v>
       </c>
       <c r="H27" s="47"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="71"/>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="24">
@@ -2220,7 +2266,7 @@
       <c r="F28" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="61" t="s">
         <v>181</v>
       </c>
       <c r="H28" s="47" t="s">
@@ -2235,7 +2281,7 @@
       <c r="D29" s="24"/>
       <c r="E29" s="24"/>
       <c r="F29" s="26"/>
-      <c r="G29" s="62" t="s">
+      <c r="G29" s="61" t="s">
         <v>182</v>
       </c>
       <c r="H29" s="47"/>
@@ -2248,14 +2294,14 @@
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
       <c r="F30" s="26"/>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>183</v>
       </c>
       <c r="H30" s="47"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="72"/>
-      <c r="C31" s="66" t="s">
+      <c r="C31" s="64" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="48">
@@ -2267,7 +2313,7 @@
       <c r="F31" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="63" t="s">
+      <c r="G31" s="62" t="s">
         <v>184</v>
       </c>
       <c r="H31" s="50" t="s">
@@ -2298,12 +2344,14 @@
       <c r="F33" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="64"/>
+      <c r="G33" s="37" t="s">
+        <v>290</v>
+      </c>
       <c r="H33" s="51"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
-      <c r="C34" s="65" t="s">
+      <c r="C34" s="63" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="20">
@@ -2324,7 +2372,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="74"/>
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="63" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="20">
@@ -2410,7 +2458,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="74"/>
-      <c r="C41" s="65" t="s">
+      <c r="C41" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="20">
@@ -2457,7 +2505,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="75"/>
-      <c r="C44" s="66" t="s">
+      <c r="C44" s="64" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="40">
@@ -2500,7 +2548,9 @@
       <c r="F46" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="G46" s="61"/>
+      <c r="G46" s="66" t="s">
+        <v>291</v>
+      </c>
       <c r="H46" s="45"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
@@ -2517,7 +2567,7 @@
       <c r="F47" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="61" t="s">
         <v>196</v>
       </c>
       <c r="H47" s="46"/>
@@ -2536,7 +2586,7 @@
       <c r="F48" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="G48" s="62" t="s">
+      <c r="G48" s="61" t="s">
         <v>197</v>
       </c>
       <c r="H48" s="46"/>
@@ -2555,7 +2605,7 @@
       <c r="F49" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="G49" s="62" t="s">
+      <c r="G49" s="61" t="s">
         <v>198</v>
       </c>
       <c r="H49" s="47" t="s">
@@ -2570,7 +2620,7 @@
       <c r="D50" s="24"/>
       <c r="E50" s="24"/>
       <c r="F50" s="24"/>
-      <c r="G50" s="62" t="s">
+      <c r="G50" s="61" t="s">
         <v>199</v>
       </c>
       <c r="H50" s="46"/>
@@ -2583,7 +2633,7 @@
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
       <c r="F51" s="26"/>
-      <c r="G51" s="62" t="s">
+      <c r="G51" s="61" t="s">
         <v>200</v>
       </c>
       <c r="H51" s="46"/>
@@ -2596,7 +2646,7 @@
       <c r="D52" s="24"/>
       <c r="E52" s="24"/>
       <c r="F52" s="26"/>
-      <c r="G52" s="62" t="s">
+      <c r="G52" s="61" t="s">
         <v>201</v>
       </c>
       <c r="H52" s="46"/>
@@ -2609,7 +2659,7 @@
       <c r="D53" s="24"/>
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
-      <c r="G53" s="62" t="s">
+      <c r="G53" s="61" t="s">
         <v>202</v>
       </c>
       <c r="H53" s="46"/>
@@ -2628,7 +2678,7 @@
       <c r="F54" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="G54" s="62" t="s">
+      <c r="G54" s="61" t="s">
         <v>203</v>
       </c>
       <c r="H54" s="46"/>
@@ -2641,7 +2691,7 @@
       <c r="D55" s="24"/>
       <c r="E55" s="24"/>
       <c r="F55" s="26"/>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="61" t="s">
         <v>204</v>
       </c>
       <c r="H55" s="46"/>
@@ -2654,7 +2704,7 @@
       <c r="D56" s="24"/>
       <c r="E56" s="24"/>
       <c r="F56" s="26"/>
-      <c r="G56" s="62" t="s">
+      <c r="G56" s="61" t="s">
         <v>205</v>
       </c>
       <c r="H56" s="46"/>
@@ -2673,7 +2723,7 @@
       <c r="F57" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="G57" s="63" t="s">
+      <c r="G57" s="62" t="s">
         <v>206</v>
       </c>
       <c r="H57" s="54"/>
@@ -2702,7 +2752,9 @@
       <c r="F59" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="G59" s="64"/>
+      <c r="G59" s="37" t="s">
+        <v>292</v>
+      </c>
       <c r="H59" s="51"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
@@ -2726,7 +2778,7 @@
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="74"/>
-      <c r="C61" s="65" t="s">
+      <c r="C61" s="63" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="20">
@@ -2812,7 +2864,7 @@
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="74"/>
-      <c r="C67" s="65" t="s">
+      <c r="C67" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="20">
@@ -2859,7 +2911,7 @@
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="75"/>
-      <c r="C70" s="66" t="s">
+      <c r="C70" s="64" t="s">
         <v>19</v>
       </c>
       <c r="D70" s="40">
@@ -2902,7 +2954,9 @@
       <c r="F72" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="G72" s="61"/>
+      <c r="G72" s="66" t="s">
+        <v>293</v>
+      </c>
       <c r="H72" s="45"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
@@ -2919,14 +2973,14 @@
       <c r="F73" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="G73" s="62" t="s">
+      <c r="G73" s="61" t="s">
         <v>218</v>
       </c>
       <c r="H73" s="46"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="71"/>
-      <c r="C74" s="65" t="s">
+      <c r="C74" s="63" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="24">
@@ -2938,7 +2992,7 @@
       <c r="F74" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="G74" s="62" t="s">
+      <c r="G74" s="61" t="s">
         <v>219</v>
       </c>
       <c r="H74" s="47" t="s">
@@ -2947,7 +3001,7 @@
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="71"/>
-      <c r="C75" s="65" t="s">
+      <c r="C75" s="63" t="s">
         <v>10</v>
       </c>
       <c r="D75" s="24">
@@ -2959,7 +3013,7 @@
       <c r="F75" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="G75" s="62" t="s">
+      <c r="G75" s="61" t="s">
         <v>220</v>
       </c>
       <c r="H75" s="47" t="s">
@@ -2974,7 +3028,7 @@
       <c r="D76" s="24"/>
       <c r="E76" s="24"/>
       <c r="F76" s="24"/>
-      <c r="G76" s="62" t="s">
+      <c r="G76" s="61" t="s">
         <v>221</v>
       </c>
       <c r="H76" s="46"/>
@@ -2987,7 +3041,7 @@
       <c r="D77" s="24"/>
       <c r="E77" s="24"/>
       <c r="F77" s="24"/>
-      <c r="G77" s="62" t="s">
+      <c r="G77" s="61" t="s">
         <v>222</v>
       </c>
       <c r="H77" s="46"/>
@@ -3000,7 +3054,7 @@
       <c r="D78" s="24"/>
       <c r="E78" s="24"/>
       <c r="F78" s="26"/>
-      <c r="G78" s="62" t="s">
+      <c r="G78" s="61" t="s">
         <v>223</v>
       </c>
       <c r="H78" s="46"/>
@@ -3013,14 +3067,14 @@
       <c r="D79" s="24"/>
       <c r="E79" s="24"/>
       <c r="F79" s="24"/>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="61" t="s">
         <v>224</v>
       </c>
       <c r="H79" s="46"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="71"/>
-      <c r="C80" s="65" t="s">
+      <c r="C80" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="24">
@@ -3032,7 +3086,7 @@
       <c r="F80" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="G80" s="62" t="s">
+      <c r="G80" s="61" t="s">
         <v>225</v>
       </c>
       <c r="H80" s="47" t="s">
@@ -3047,7 +3101,7 @@
       <c r="D81" s="24"/>
       <c r="E81" s="24"/>
       <c r="F81" s="26"/>
-      <c r="G81" s="62" t="s">
+      <c r="G81" s="61" t="s">
         <v>226</v>
       </c>
       <c r="H81" s="46"/>
@@ -3060,14 +3114,14 @@
       <c r="D82" s="24"/>
       <c r="E82" s="24"/>
       <c r="F82" s="26"/>
-      <c r="G82" s="62" t="s">
+      <c r="G82" s="61" t="s">
         <v>227</v>
       </c>
       <c r="H82" s="46"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="72"/>
-      <c r="C83" s="66" t="s">
+      <c r="C83" s="64" t="s">
         <v>19</v>
       </c>
       <c r="D83" s="48">
@@ -3079,7 +3133,7 @@
       <c r="F83" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="G83" s="63" t="s">
+      <c r="G83" s="62" t="s">
         <v>228</v>
       </c>
       <c r="H83" s="50" t="s">
@@ -3110,7 +3164,9 @@
       <c r="F85" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="G85" s="64"/>
+      <c r="G85" s="37" t="s">
+        <v>294</v>
+      </c>
       <c r="H85" s="51"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
@@ -3134,7 +3190,7 @@
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="74"/>
-      <c r="C87" s="65" t="s">
+      <c r="C87" s="63" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="20">
@@ -3220,7 +3276,7 @@
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="74"/>
-      <c r="C93" s="65" t="s">
+      <c r="C93" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D93" s="20" t="s">
@@ -3267,7 +3323,7 @@
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B96" s="75"/>
-      <c r="C96" s="66" t="s">
+      <c r="C96" s="64" t="s">
         <v>19</v>
       </c>
       <c r="D96" s="40">
@@ -3310,7 +3366,9 @@
       <c r="F98" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="G98" s="61"/>
+      <c r="G98" s="66" t="s">
+        <v>295</v>
+      </c>
       <c r="H98" s="55"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
@@ -3327,7 +3385,7 @@
       <c r="F99" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="G99" s="62" t="s">
+      <c r="G99" s="61" t="s">
         <v>240</v>
       </c>
       <c r="H99" s="47"/>
@@ -3346,7 +3404,7 @@
       <c r="F100" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="G100" s="62" t="s">
+      <c r="G100" s="61" t="s">
         <v>241</v>
       </c>
       <c r="H100" s="47"/>
@@ -3359,7 +3417,7 @@
       <c r="D101" s="24"/>
       <c r="E101" s="24"/>
       <c r="F101" s="24"/>
-      <c r="G101" s="62" t="s">
+      <c r="G101" s="61" t="s">
         <v>242</v>
       </c>
       <c r="H101" s="47"/>
@@ -3372,7 +3430,7 @@
       <c r="D102" s="24"/>
       <c r="E102" s="24"/>
       <c r="F102" s="24"/>
-      <c r="G102" s="62" t="s">
+      <c r="G102" s="61" t="s">
         <v>243</v>
       </c>
       <c r="H102" s="47"/>
@@ -3385,7 +3443,7 @@
       <c r="D103" s="24"/>
       <c r="E103" s="24"/>
       <c r="F103" s="26"/>
-      <c r="G103" s="62" t="s">
+      <c r="G103" s="61" t="s">
         <v>244</v>
       </c>
       <c r="H103" s="47"/>
@@ -3398,7 +3456,7 @@
       <c r="D104" s="24"/>
       <c r="E104" s="24"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="62" t="s">
+      <c r="G104" s="61" t="s">
         <v>245</v>
       </c>
       <c r="H104" s="47"/>
@@ -3411,7 +3469,7 @@
       <c r="D105" s="24"/>
       <c r="E105" s="24"/>
       <c r="F105" s="24"/>
-      <c r="G105" s="62" t="s">
+      <c r="G105" s="61" t="s">
         <v>246</v>
       </c>
       <c r="H105" s="47"/>
@@ -3430,7 +3488,7 @@
       <c r="F106" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="G106" s="62" t="s">
+      <c r="G106" s="61" t="s">
         <v>247</v>
       </c>
       <c r="H106" s="47"/>
@@ -3443,7 +3501,7 @@
       <c r="D107" s="24"/>
       <c r="E107" s="24"/>
       <c r="F107" s="26"/>
-      <c r="G107" s="62" t="s">
+      <c r="G107" s="61" t="s">
         <v>248</v>
       </c>
       <c r="H107" s="47"/>
@@ -3456,7 +3514,7 @@
       <c r="D108" s="24"/>
       <c r="E108" s="24"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="62" t="s">
+      <c r="G108" s="61" t="s">
         <v>249</v>
       </c>
       <c r="H108" s="47"/>
@@ -3475,7 +3533,7 @@
       <c r="F109" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="G109" s="63" t="s">
+      <c r="G109" s="62" t="s">
         <v>250</v>
       </c>
       <c r="H109" s="54"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D41CBA3-BE2C-442A-8FC2-6FC6706D8EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92EEA9B-CE64-4D30-A004-C3D26C856169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -951,11 +951,11 @@
     <t>25, 25, 31</t>
   </si>
   <si>
-    <t xml:space="preserve">34, 40, 42,
-48, 50, 53, 54, 57, 58, 63, 64, 72, 73, 75, 76, 79 </t>
-  </si>
-  <si>
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=2cb0002e70b3711dd473750d48e2cacd&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>T1: 34, 40, 42
+T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81,</t>
   </si>
 </sst>
 </file>
@@ -1468,6 +1468,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1509,12 +1515,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1812,41 +1812,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="78" t="s">
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="78" t="s">
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="29"/>
@@ -1881,7 +1881,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="75" t="s">
         <v>153</v>
       </c>
       <c r="C7" s="67" t="s">
@@ -1902,7 +1902,7 @@
       <c r="H7" s="38"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="74"/>
+      <c r="B8" s="76"/>
       <c r="C8" s="63" t="s">
         <v>2</v>
       </c>
@@ -1923,7 +1923,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="74"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="63" t="s">
         <v>9</v>
       </c>
@@ -1943,13 +1943,13 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="74"/>
+    <row r="10" spans="2:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="76"/>
       <c r="C10" s="63" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>161</v>
@@ -1957,15 +1957,15 @@
       <c r="F10" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="G10" s="82" t="s">
+      <c r="G10" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="83" t="s">
+      <c r="H10" s="69" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="74"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="63" t="s">
         <v>11</v>
       </c>
@@ -1986,7 +1986,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="74"/>
+      <c r="B12" s="76"/>
       <c r="C12" s="63" t="s">
         <v>12</v>
       </c>
@@ -2007,7 +2007,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="74"/>
+      <c r="B13" s="76"/>
       <c r="C13" s="63" t="s">
         <v>13</v>
       </c>
@@ -2028,7 +2028,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="74"/>
+      <c r="B14" s="76"/>
       <c r="C14" s="20" t="s">
         <v>14</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="H14" s="39"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="74"/>
+      <c r="B15" s="76"/>
       <c r="C15" s="63" t="s">
         <v>15</v>
       </c>
@@ -2062,7 +2062,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="74"/>
+      <c r="B16" s="76"/>
       <c r="C16" s="63" t="s">
         <v>16</v>
       </c>
@@ -2083,7 +2083,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="74"/>
+      <c r="B17" s="76"/>
       <c r="C17" s="20" t="s">
         <v>18</v>
       </c>
@@ -2096,7 +2096,7 @@
       <c r="H17" s="39"/>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="75"/>
+      <c r="B18" s="77"/>
       <c r="C18" s="64" t="s">
         <v>19</v>
       </c>
@@ -2125,14 +2125,14 @@
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="72" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="67" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="43">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E20" s="44" t="s">
         <v>81</v>
@@ -2146,12 +2146,12 @@
       <c r="H20" s="45"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="71"/>
+      <c r="B21" s="73"/>
       <c r="C21" s="63" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="24">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>68</v>
@@ -2163,16 +2163,16 @@
         <v>174</v>
       </c>
       <c r="H21" s="47" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="71"/>
+      <c r="B22" s="73"/>
       <c r="C22" s="63" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="24">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>92</v>
@@ -2188,7 +2188,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="71"/>
+      <c r="B23" s="73"/>
       <c r="C23" s="24" t="s">
         <v>10</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="H23" s="47"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="71"/>
+      <c r="B24" s="73"/>
       <c r="C24" s="24" t="s">
         <v>11</v>
       </c>
@@ -2214,7 +2214,7 @@
       <c r="H24" s="47"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="71"/>
+      <c r="B25" s="73"/>
       <c r="C25" s="24" t="s">
         <v>12</v>
       </c>
@@ -2227,7 +2227,7 @@
       <c r="H25" s="47"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="71"/>
+      <c r="B26" s="73"/>
       <c r="C26" s="24" t="s">
         <v>13</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="H26" s="47"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="71"/>
+      <c r="B27" s="73"/>
       <c r="C27" s="24" t="s">
         <v>14</v>
       </c>
@@ -2253,7 +2253,7 @@
       <c r="H27" s="47"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="71"/>
+      <c r="B28" s="73"/>
       <c r="C28" s="63" t="s">
         <v>15</v>
       </c>
@@ -2274,7 +2274,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="71"/>
+      <c r="B29" s="73"/>
       <c r="C29" s="24" t="s">
         <v>16</v>
       </c>
@@ -2287,7 +2287,7 @@
       <c r="H29" s="47"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="71"/>
+      <c r="B30" s="73"/>
       <c r="C30" s="24" t="s">
         <v>18</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="H30" s="47"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="72"/>
+      <c r="B31" s="74"/>
       <c r="C31" s="64" t="s">
         <v>19</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="H32" s="18"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="73" t="s">
+      <c r="B33" s="75" t="s">
         <v>155</v>
       </c>
       <c r="C33" s="35" t="s">
@@ -2350,7 +2350,7 @@
       <c r="H33" s="51"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="74"/>
+      <c r="B34" s="76"/>
       <c r="C34" s="63" t="s">
         <v>2</v>
       </c>
@@ -2371,7 +2371,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="74"/>
+      <c r="B35" s="76"/>
       <c r="C35" s="63" t="s">
         <v>9</v>
       </c>
@@ -2392,7 +2392,7 @@
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="74"/>
+      <c r="B36" s="76"/>
       <c r="C36" s="20" t="s">
         <v>10</v>
       </c>
@@ -2405,7 +2405,7 @@
       <c r="H36" s="39"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="74"/>
+      <c r="B37" s="76"/>
       <c r="C37" s="20" t="s">
         <v>11</v>
       </c>
@@ -2418,7 +2418,7 @@
       <c r="H37" s="52"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="74"/>
+      <c r="B38" s="76"/>
       <c r="C38" s="20" t="s">
         <v>12</v>
       </c>
@@ -2431,7 +2431,7 @@
       <c r="H38" s="52"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="74"/>
+      <c r="B39" s="76"/>
       <c r="C39" s="20" t="s">
         <v>13</v>
       </c>
@@ -2444,7 +2444,7 @@
       <c r="H39" s="52"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="74"/>
+      <c r="B40" s="76"/>
       <c r="C40" s="20" t="s">
         <v>14</v>
       </c>
@@ -2457,7 +2457,7 @@
       <c r="H40" s="52"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="74"/>
+      <c r="B41" s="76"/>
       <c r="C41" s="63" t="s">
         <v>15</v>
       </c>
@@ -2478,7 +2478,7 @@
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="74"/>
+      <c r="B42" s="76"/>
       <c r="C42" s="20" t="s">
         <v>16</v>
       </c>
@@ -2491,7 +2491,7 @@
       <c r="H42" s="52"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="74"/>
+      <c r="B43" s="76"/>
       <c r="C43" s="20" t="s">
         <v>18</v>
       </c>
@@ -2504,7 +2504,7 @@
       <c r="H43" s="52"/>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="75"/>
+      <c r="B44" s="77"/>
       <c r="C44" s="64" t="s">
         <v>19</v>
       </c>
@@ -2533,7 +2533,7 @@
       <c r="H45" s="19"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="70" t="s">
+      <c r="B46" s="72" t="s">
         <v>156</v>
       </c>
       <c r="C46" s="43" t="s">
@@ -2554,7 +2554,7 @@
       <c r="H46" s="45"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="71"/>
+      <c r="B47" s="73"/>
       <c r="C47" s="24" t="s">
         <v>2</v>
       </c>
@@ -2573,7 +2573,7 @@
       <c r="H47" s="46"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="71"/>
+      <c r="B48" s="73"/>
       <c r="C48" s="24" t="s">
         <v>9</v>
       </c>
@@ -2592,7 +2592,7 @@
       <c r="H48" s="46"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="71"/>
+      <c r="B49" s="73"/>
       <c r="C49" s="24" t="s">
         <v>10</v>
       </c>
@@ -2613,7 +2613,7 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="71"/>
+      <c r="B50" s="73"/>
       <c r="C50" s="24" t="s">
         <v>11</v>
       </c>
@@ -2626,7 +2626,7 @@
       <c r="H50" s="46"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="71"/>
+      <c r="B51" s="73"/>
       <c r="C51" s="24" t="s">
         <v>12</v>
       </c>
@@ -2639,7 +2639,7 @@
       <c r="H51" s="46"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="71"/>
+      <c r="B52" s="73"/>
       <c r="C52" s="24" t="s">
         <v>13</v>
       </c>
@@ -2652,7 +2652,7 @@
       <c r="H52" s="46"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="71"/>
+      <c r="B53" s="73"/>
       <c r="C53" s="24" t="s">
         <v>14</v>
       </c>
@@ -2665,7 +2665,7 @@
       <c r="H53" s="46"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="71"/>
+      <c r="B54" s="73"/>
       <c r="C54" s="24" t="s">
         <v>15</v>
       </c>
@@ -2684,7 +2684,7 @@
       <c r="H54" s="46"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="71"/>
+      <c r="B55" s="73"/>
       <c r="C55" s="24" t="s">
         <v>16</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="H55" s="46"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="71"/>
+      <c r="B56" s="73"/>
       <c r="C56" s="24" t="s">
         <v>18</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="H56" s="46"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="72"/>
+      <c r="B57" s="74"/>
       <c r="C57" s="48" t="s">
         <v>19</v>
       </c>
@@ -2737,7 +2737,7 @@
       <c r="H58" s="19"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="73" t="s">
+      <c r="B59" s="75" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="35" t="s">
@@ -2758,7 +2758,7 @@
       <c r="H59" s="51"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="74"/>
+      <c r="B60" s="76"/>
       <c r="C60" s="20" t="s">
         <v>2</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="H60" s="52"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="74"/>
+      <c r="B61" s="76"/>
       <c r="C61" s="63" t="s">
         <v>9</v>
       </c>
@@ -2798,7 +2798,7 @@
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="74"/>
+      <c r="B62" s="76"/>
       <c r="C62" s="20" t="s">
         <v>10</v>
       </c>
@@ -2811,7 +2811,7 @@
       <c r="H62" s="52"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="74"/>
+      <c r="B63" s="76"/>
       <c r="C63" s="20" t="s">
         <v>11</v>
       </c>
@@ -2824,7 +2824,7 @@
       <c r="H63" s="52"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="74"/>
+      <c r="B64" s="76"/>
       <c r="C64" s="20" t="s">
         <v>12</v>
       </c>
@@ -2837,7 +2837,7 @@
       <c r="H64" s="52"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="74"/>
+      <c r="B65" s="76"/>
       <c r="C65" s="20" t="s">
         <v>13</v>
       </c>
@@ -2850,7 +2850,7 @@
       <c r="H65" s="52"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="74"/>
+      <c r="B66" s="76"/>
       <c r="C66" s="20" t="s">
         <v>14</v>
       </c>
@@ -2863,7 +2863,7 @@
       <c r="H66" s="52"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="74"/>
+      <c r="B67" s="76"/>
       <c r="C67" s="63" t="s">
         <v>15</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="74"/>
+      <c r="B68" s="76"/>
       <c r="C68" s="20" t="s">
         <v>16</v>
       </c>
@@ -2897,7 +2897,7 @@
       <c r="H68" s="52"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="74"/>
+      <c r="B69" s="76"/>
       <c r="C69" s="20" t="s">
         <v>18</v>
       </c>
@@ -2910,7 +2910,7 @@
       <c r="H69" s="52"/>
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="75"/>
+      <c r="B70" s="77"/>
       <c r="C70" s="64" t="s">
         <v>19</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="H71" s="19"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="70" t="s">
+      <c r="B72" s="72" t="s">
         <v>158</v>
       </c>
       <c r="C72" s="43" t="s">
@@ -2960,7 +2960,7 @@
       <c r="H72" s="45"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="71"/>
+      <c r="B73" s="73"/>
       <c r="C73" s="24" t="s">
         <v>2</v>
       </c>
@@ -2979,7 +2979,7 @@
       <c r="H73" s="46"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="71"/>
+      <c r="B74" s="73"/>
       <c r="C74" s="63" t="s">
         <v>9</v>
       </c>
@@ -3000,7 +3000,7 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="71"/>
+      <c r="B75" s="73"/>
       <c r="C75" s="63" t="s">
         <v>10</v>
       </c>
@@ -3021,7 +3021,7 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="71"/>
+      <c r="B76" s="73"/>
       <c r="C76" s="24" t="s">
         <v>11</v>
       </c>
@@ -3034,7 +3034,7 @@
       <c r="H76" s="46"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="71"/>
+      <c r="B77" s="73"/>
       <c r="C77" s="24" t="s">
         <v>12</v>
       </c>
@@ -3047,7 +3047,7 @@
       <c r="H77" s="46"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="71"/>
+      <c r="B78" s="73"/>
       <c r="C78" s="24" t="s">
         <v>13</v>
       </c>
@@ -3060,7 +3060,7 @@
       <c r="H78" s="46"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="71"/>
+      <c r="B79" s="73"/>
       <c r="C79" s="24" t="s">
         <v>14</v>
       </c>
@@ -3073,7 +3073,7 @@
       <c r="H79" s="46"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="71"/>
+      <c r="B80" s="73"/>
       <c r="C80" s="63" t="s">
         <v>15</v>
       </c>
@@ -3094,7 +3094,7 @@
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="71"/>
+      <c r="B81" s="73"/>
       <c r="C81" s="24" t="s">
         <v>16</v>
       </c>
@@ -3107,7 +3107,7 @@
       <c r="H81" s="46"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="71"/>
+      <c r="B82" s="73"/>
       <c r="C82" s="24" t="s">
         <v>18</v>
       </c>
@@ -3120,7 +3120,7 @@
       <c r="H82" s="46"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="72"/>
+      <c r="B83" s="74"/>
       <c r="C83" s="64" t="s">
         <v>19</v>
       </c>
@@ -3149,7 +3149,7 @@
       <c r="H84" s="19"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="73" t="s">
+      <c r="B85" s="75" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="35" t="s">
@@ -3170,7 +3170,7 @@
       <c r="H85" s="51"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="74"/>
+      <c r="B86" s="76"/>
       <c r="C86" s="20" t="s">
         <v>2</v>
       </c>
@@ -3189,7 +3189,7 @@
       <c r="H86" s="52"/>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="74"/>
+      <c r="B87" s="76"/>
       <c r="C87" s="63" t="s">
         <v>9</v>
       </c>
@@ -3210,7 +3210,7 @@
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="74"/>
+      <c r="B88" s="76"/>
       <c r="C88" s="20" t="s">
         <v>10</v>
       </c>
@@ -3223,7 +3223,7 @@
       <c r="H88" s="52"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="74"/>
+      <c r="B89" s="76"/>
       <c r="C89" s="20" t="s">
         <v>11</v>
       </c>
@@ -3236,7 +3236,7 @@
       <c r="H89" s="39"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" s="74"/>
+      <c r="B90" s="76"/>
       <c r="C90" s="20" t="s">
         <v>12</v>
       </c>
@@ -3249,7 +3249,7 @@
       <c r="H90" s="39"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="74"/>
+      <c r="B91" s="76"/>
       <c r="C91" s="20" t="s">
         <v>13</v>
       </c>
@@ -3262,7 +3262,7 @@
       <c r="H91" s="39"/>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="74"/>
+      <c r="B92" s="76"/>
       <c r="C92" s="20" t="s">
         <v>14</v>
       </c>
@@ -3275,7 +3275,7 @@
       <c r="H92" s="39"/>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="74"/>
+      <c r="B93" s="76"/>
       <c r="C93" s="63" t="s">
         <v>15</v>
       </c>
@@ -3296,7 +3296,7 @@
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="74"/>
+      <c r="B94" s="76"/>
       <c r="C94" s="20" t="s">
         <v>16</v>
       </c>
@@ -3309,7 +3309,7 @@
       <c r="H94" s="39"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="74"/>
+      <c r="B95" s="76"/>
       <c r="C95" s="20" t="s">
         <v>18</v>
       </c>
@@ -3322,7 +3322,7 @@
       <c r="H95" s="39"/>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="75"/>
+      <c r="B96" s="77"/>
       <c r="C96" s="64" t="s">
         <v>19</v>
       </c>
@@ -3351,7 +3351,7 @@
       <c r="H97" s="18"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="70" t="s">
+      <c r="B98" s="72" t="s">
         <v>160</v>
       </c>
       <c r="C98" s="43" t="s">
@@ -3372,7 +3372,7 @@
       <c r="H98" s="55"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="71"/>
+      <c r="B99" s="73"/>
       <c r="C99" s="24" t="s">
         <v>2</v>
       </c>
@@ -3391,7 +3391,7 @@
       <c r="H99" s="47"/>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="71"/>
+      <c r="B100" s="73"/>
       <c r="C100" s="24" t="s">
         <v>9</v>
       </c>
@@ -3410,7 +3410,7 @@
       <c r="H100" s="47"/>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="71"/>
+      <c r="B101" s="73"/>
       <c r="C101" s="24" t="s">
         <v>10</v>
       </c>
@@ -3423,7 +3423,7 @@
       <c r="H101" s="47"/>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="71"/>
+      <c r="B102" s="73"/>
       <c r="C102" s="24" t="s">
         <v>11</v>
       </c>
@@ -3436,7 +3436,7 @@
       <c r="H102" s="47"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="71"/>
+      <c r="B103" s="73"/>
       <c r="C103" s="24" t="s">
         <v>12</v>
       </c>
@@ -3449,7 +3449,7 @@
       <c r="H103" s="47"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="71"/>
+      <c r="B104" s="73"/>
       <c r="C104" s="24" t="s">
         <v>13</v>
       </c>
@@ -3462,7 +3462,7 @@
       <c r="H104" s="47"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="71"/>
+      <c r="B105" s="73"/>
       <c r="C105" s="24" t="s">
         <v>14</v>
       </c>
@@ -3475,7 +3475,7 @@
       <c r="H105" s="47"/>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="71"/>
+      <c r="B106" s="73"/>
       <c r="C106" s="24" t="s">
         <v>15</v>
       </c>
@@ -3494,7 +3494,7 @@
       <c r="H106" s="47"/>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="71"/>
+      <c r="B107" s="73"/>
       <c r="C107" s="24" t="s">
         <v>16</v>
       </c>
@@ -3507,7 +3507,7 @@
       <c r="H107" s="47"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="71"/>
+      <c r="B108" s="73"/>
       <c r="C108" s="24" t="s">
         <v>18</v>
       </c>
@@ -3520,7 +3520,7 @@
       <c r="H108" s="47"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="72"/>
+      <c r="B109" s="74"/>
       <c r="C109" s="48" t="s">
         <v>19</v>
       </c>
@@ -3539,32 +3539,32 @@
       <c r="H109" s="54"/>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B112" s="68" t="s">
+      <c r="B112" s="70" t="s">
         <v>272</v>
       </c>
-      <c r="C112" s="68"/>
-      <c r="D112" s="68"/>
-      <c r="E112" s="68"/>
-      <c r="F112" s="68"/>
-      <c r="G112" s="68"/>
-      <c r="H112" s="68"/>
+      <c r="C112" s="70"/>
+      <c r="D112" s="70"/>
+      <c r="E112" s="70"/>
+      <c r="F112" s="70"/>
+      <c r="G112" s="70"/>
+      <c r="H112" s="70"/>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B113" s="68"/>
-      <c r="C113" s="68"/>
-      <c r="D113" s="68"/>
-      <c r="E113" s="68"/>
-      <c r="F113" s="68"/>
-      <c r="G113" s="68"/>
-      <c r="H113" s="68"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="70"/>
+      <c r="D113" s="70"/>
+      <c r="E113" s="70"/>
+      <c r="F113" s="70"/>
+      <c r="G113" s="70"/>
+      <c r="H113" s="70"/>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="E114" s="69" t="s">
+      <c r="E114" s="71" t="s">
         <v>278</v>
       </c>
-      <c r="F114" s="69"/>
-      <c r="G114" s="69"/>
-      <c r="H114" s="69"/>
+      <c r="F114" s="71"/>
+      <c r="G114" s="71"/>
+      <c r="H114" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3606,35 +3606,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="79" t="s">
+      <c r="C3" s="79"/>
+      <c r="D3" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="80"/>
-      <c r="F3" s="81"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="83"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="79" t="s">
+      <c r="C4" s="79"/>
+      <c r="D4" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="80"/>
-      <c r="F4" s="81"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="83"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92EEA9B-CE64-4D30-A004-C3D26C856169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552A69BC-ECC8-47D9-975B-6F70BCEE944E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MM-LİNKLER" sheetId="1" r:id="rId1"/>
@@ -955,7 +955,13 @@
   </si>
   <si>
     <t>T1: 34, 40, 42
-T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81,</t>
+T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81
+T3: 100, 107
+T4:
+T5:163, 168, 177, 179, 180, 190,
+T6:
+T7:
+T8:</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1333,9 +1339,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1474,38 +1477,38 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1801,109 +1804,109 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="30" customWidth="1"/>
     <col min="3" max="3" width="6.44140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19" style="4" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36" style="60" customWidth="1"/>
-    <col min="8" max="8" width="100.6640625" style="60" customWidth="1"/>
+    <col min="7" max="7" width="36" style="59" customWidth="1"/>
+    <col min="8" max="8" width="100.6640625" style="59" customWidth="1"/>
     <col min="9" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80" t="s">
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="80" t="s">
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="29"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="32"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="65" t="s">
+      <c r="H6" s="64" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="72" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="34">
         <v>13</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="H7" s="38"/>
+      <c r="H7" s="37"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="76"/>
-      <c r="C8" s="63" t="s">
+      <c r="B8" s="73"/>
+      <c r="C8" s="62" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="20">
@@ -1915,16 +1918,16 @@
       <c r="F8" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="38" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="76"/>
-      <c r="C9" s="63" t="s">
+      <c r="B9" s="73"/>
+      <c r="C9" s="62" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="20">
@@ -1936,19 +1939,19 @@
       <c r="F9" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="G9" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="38" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="76"/>
-      <c r="C10" s="63" t="s">
+    <row r="10" spans="2:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="73"/>
+      <c r="C10" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="21" t="s">
         <v>298</v>
       </c>
       <c r="E10" s="22" t="s">
@@ -1957,16 +1960,16 @@
       <c r="F10" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="69" t="s">
+      <c r="H10" s="68" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="76"/>
-      <c r="C11" s="63" t="s">
+      <c r="B11" s="73"/>
+      <c r="C11" s="62" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="20" t="s">
@@ -1978,16 +1981,16 @@
       <c r="F11" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="58" t="s">
+      <c r="G11" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="H11" s="39" t="s">
+      <c r="H11" s="38" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="76"/>
-      <c r="C12" s="63" t="s">
+      <c r="B12" s="73"/>
+      <c r="C12" s="62" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="20">
@@ -1999,16 +2002,16 @@
       <c r="F12" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="G12" s="58" t="s">
+      <c r="G12" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="H12" s="39" t="s">
+      <c r="H12" s="38" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="76"/>
-      <c r="C13" s="63" t="s">
+      <c r="B13" s="73"/>
+      <c r="C13" s="62" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="20">
@@ -2020,29 +2023,29 @@
       <c r="F13" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="58" t="s">
+      <c r="G13" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="38" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="76"/>
+      <c r="B14" s="73"/>
       <c r="C14" s="20" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
       <c r="F14" s="20"/>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="H14" s="39"/>
+      <c r="H14" s="38"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="76"/>
-      <c r="C15" s="63" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="20">
@@ -2054,16 +2057,16 @@
       <c r="F15" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G15" s="57" t="s">
         <v>170</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="38" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="76"/>
-      <c r="C16" s="63" t="s">
+      <c r="B16" s="73"/>
+      <c r="C16" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="20">
@@ -2075,49 +2078,49 @@
       <c r="F16" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="H16" s="38" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="76"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
       <c r="F17" s="20"/>
-      <c r="G17" s="58" t="s">
+      <c r="G17" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="H17" s="39"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="77"/>
-      <c r="C18" s="64" t="s">
+      <c r="B18" s="74"/>
+      <c r="C18" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="39">
         <v>45</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="40" t="s">
         <v>251</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="41" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="30"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="17"/>
@@ -2125,203 +2128,203 @@
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="75" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="42">
         <v>45</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="H20" s="45"/>
+      <c r="H20" s="44"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="73"/>
-      <c r="C21" s="63" t="s">
+      <c r="B21" s="76"/>
+      <c r="C21" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <v>45</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="61" t="s">
+      <c r="G21" s="60" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="47" t="s">
+      <c r="H21" s="46" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="73"/>
-      <c r="C22" s="63" t="s">
+      <c r="B22" s="76"/>
+      <c r="C22" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="23">
         <v>46</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="61" t="s">
+      <c r="G22" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="H22" s="47" t="s">
+      <c r="H22" s="46" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="73"/>
-      <c r="C23" s="24" t="s">
+      <c r="B23" s="76"/>
+      <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="61" t="s">
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="H23" s="47"/>
+      <c r="H23" s="46"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="73"/>
-      <c r="C24" s="24" t="s">
+      <c r="B24" s="76"/>
+      <c r="C24" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="61" t="s">
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="60" t="s">
         <v>177</v>
       </c>
-      <c r="H24" s="47"/>
+      <c r="H24" s="46"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="73"/>
-      <c r="C25" s="24" t="s">
+      <c r="B25" s="76"/>
+      <c r="C25" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="61" t="s">
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="H25" s="47"/>
+      <c r="H25" s="46"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="73"/>
-      <c r="C26" s="24" t="s">
+      <c r="B26" s="76"/>
+      <c r="C26" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="61" t="s">
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="H26" s="47"/>
+      <c r="H26" s="46"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="73"/>
-      <c r="C27" s="24" t="s">
+      <c r="B27" s="76"/>
+      <c r="C27" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="61" t="s">
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="H27" s="47"/>
+      <c r="H27" s="46"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="73"/>
-      <c r="C28" s="63" t="s">
+      <c r="B28" s="76"/>
+      <c r="C28" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="23">
         <v>53</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="G28" s="61" t="s">
+      <c r="G28" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="H28" s="47" t="s">
+      <c r="H28" s="46" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="73"/>
-      <c r="C29" s="24" t="s">
+      <c r="B29" s="76"/>
+      <c r="C29" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="61" t="s">
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="60" t="s">
         <v>182</v>
       </c>
-      <c r="H29" s="47"/>
+      <c r="H29" s="46"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="73"/>
-      <c r="C30" s="24" t="s">
+      <c r="B30" s="76"/>
+      <c r="C30" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="61" t="s">
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="60" t="s">
         <v>183</v>
       </c>
-      <c r="H30" s="47"/>
+      <c r="H30" s="46"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="74"/>
-      <c r="C31" s="64" t="s">
+      <c r="B31" s="77"/>
+      <c r="C31" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="47">
         <v>87</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="62" t="s">
+      <c r="G31" s="61" t="s">
         <v>184</v>
       </c>
-      <c r="H31" s="50" t="s">
+      <c r="H31" s="49" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="30"/>
+      <c r="B32" s="29"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="17"/>
@@ -2329,29 +2332,29 @@
       <c r="H32" s="18"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="34">
         <v>89</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E33" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="37" t="s">
+      <c r="G33" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="H33" s="51"/>
+      <c r="H33" s="50"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="76"/>
-      <c r="C34" s="63" t="s">
+      <c r="B34" s="73"/>
+      <c r="C34" s="62" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="20">
@@ -2363,16 +2366,16 @@
       <c r="F34" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="G34" s="58" t="s">
+      <c r="G34" s="57" t="s">
         <v>185</v>
       </c>
-      <c r="H34" s="39" t="s">
+      <c r="H34" s="38" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="76"/>
-      <c r="C35" s="63" t="s">
+      <c r="B35" s="73"/>
+      <c r="C35" s="62" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="20">
@@ -2384,81 +2387,81 @@
       <c r="F35" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="G35" s="58" t="s">
+      <c r="G35" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="39" t="s">
+      <c r="H35" s="38" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="76"/>
+      <c r="B36" s="73"/>
       <c r="C36" s="20" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="20"/>
       <c r="E36" s="20"/>
       <c r="F36" s="20"/>
-      <c r="G36" s="58" t="s">
+      <c r="G36" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="H36" s="39"/>
+      <c r="H36" s="38"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="76"/>
+      <c r="B37" s="73"/>
       <c r="C37" s="20" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="20"/>
       <c r="F37" s="20"/>
-      <c r="G37" s="58" t="s">
+      <c r="G37" s="57" t="s">
         <v>188</v>
       </c>
-      <c r="H37" s="52"/>
+      <c r="H37" s="51"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="76"/>
+      <c r="B38" s="73"/>
       <c r="C38" s="20" t="s">
         <v>12</v>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
       <c r="F38" s="22"/>
-      <c r="G38" s="58" t="s">
+      <c r="G38" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="H38" s="52"/>
+      <c r="H38" s="51"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="76"/>
+      <c r="B39" s="73"/>
       <c r="C39" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
       <c r="F39" s="22"/>
-      <c r="G39" s="58" t="s">
+      <c r="G39" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="H39" s="52"/>
+      <c r="H39" s="51"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="76"/>
+      <c r="B40" s="73"/>
       <c r="C40" s="20" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
       <c r="F40" s="20"/>
-      <c r="G40" s="58" t="s">
+      <c r="G40" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="H40" s="52"/>
+      <c r="H40" s="51"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="76"/>
-      <c r="C41" s="63" t="s">
+      <c r="B41" s="73"/>
+      <c r="C41" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="20">
@@ -2470,62 +2473,62 @@
       <c r="F41" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="G41" s="58" t="s">
+      <c r="G41" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="H41" s="39" t="s">
+      <c r="H41" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="76"/>
+      <c r="B42" s="73"/>
       <c r="C42" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
       <c r="F42" s="22"/>
-      <c r="G42" s="58" t="s">
+      <c r="G42" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="H42" s="52"/>
+      <c r="H42" s="51"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="76"/>
+      <c r="B43" s="73"/>
       <c r="C43" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
       <c r="F43" s="22"/>
-      <c r="G43" s="58" t="s">
+      <c r="G43" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="H43" s="52"/>
+      <c r="H43" s="51"/>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="77"/>
-      <c r="C44" s="64" t="s">
+      <c r="B44" s="74"/>
+      <c r="C44" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="40">
+      <c r="D44" s="39">
         <v>147</v>
       </c>
-      <c r="E44" s="41" t="s">
+      <c r="E44" s="40" t="s">
         <v>253</v>
       </c>
-      <c r="F44" s="41" t="s">
+      <c r="F44" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="G44" s="59" t="s">
+      <c r="G44" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="H44" s="42" t="s">
+      <c r="H44" s="41" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="30"/>
+      <c r="B45" s="29"/>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
       <c r="E45" s="17"/>
@@ -2533,203 +2536,203 @@
       <c r="H45" s="19"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="72" t="s">
+      <c r="B46" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="C46" s="43" t="s">
+      <c r="C46" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D46" s="43" t="s">
+      <c r="D46" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="E46" s="53" t="s">
+      <c r="E46" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="F46" s="53" t="s">
+      <c r="F46" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="G46" s="66" t="s">
+      <c r="G46" s="65" t="s">
         <v>291</v>
       </c>
-      <c r="H46" s="45"/>
+      <c r="H46" s="44"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="73"/>
-      <c r="C47" s="24" t="s">
+      <c r="B47" s="76"/>
+      <c r="C47" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="24" t="s">
+      <c r="D47" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E47" s="25" t="s">
+      <c r="E47" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="25" t="s">
+      <c r="F47" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="G47" s="61" t="s">
+      <c r="G47" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="H47" s="46"/>
+      <c r="H47" s="45"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="73"/>
-      <c r="C48" s="24" t="s">
+      <c r="B48" s="76"/>
+      <c r="C48" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="24" t="s">
+      <c r="D48" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E48" s="25" t="s">
+      <c r="E48" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="F48" s="26" t="s">
+      <c r="F48" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="G48" s="61" t="s">
+      <c r="G48" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="H48" s="46"/>
+      <c r="H48" s="45"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="73"/>
-      <c r="C49" s="24" t="s">
+      <c r="B49" s="76"/>
+      <c r="C49" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="24" t="s">
+      <c r="D49" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E49" s="26" t="s">
+      <c r="E49" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="F49" s="26" t="s">
+      <c r="F49" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="G49" s="61" t="s">
+      <c r="G49" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="H49" s="47" t="s">
+      <c r="H49" s="46" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="73"/>
-      <c r="C50" s="24" t="s">
+      <c r="B50" s="76"/>
+      <c r="C50" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="61" t="s">
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="60" t="s">
         <v>199</v>
       </c>
-      <c r="H50" s="46"/>
+      <c r="H50" s="45"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="73"/>
-      <c r="C51" s="24" t="s">
+      <c r="B51" s="76"/>
+      <c r="C51" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="61" t="s">
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="H51" s="46"/>
+      <c r="H51" s="45"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="73"/>
-      <c r="C52" s="24" t="s">
+      <c r="B52" s="76"/>
+      <c r="C52" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="61" t="s">
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="H52" s="46"/>
+      <c r="H52" s="45"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="73"/>
-      <c r="C53" s="24" t="s">
+      <c r="B53" s="76"/>
+      <c r="C53" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="61" t="s">
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="H53" s="46"/>
+      <c r="H53" s="45"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="73"/>
-      <c r="C54" s="24" t="s">
+      <c r="B54" s="76"/>
+      <c r="C54" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D54" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="26" t="s">
+      <c r="E54" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="F54" s="26" t="s">
+      <c r="F54" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="G54" s="61" t="s">
+      <c r="G54" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="H54" s="46"/>
+      <c r="H54" s="45"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="73"/>
-      <c r="C55" s="24" t="s">
+      <c r="B55" s="76"/>
+      <c r="C55" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="61" t="s">
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="H55" s="46"/>
+      <c r="H55" s="45"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="73"/>
-      <c r="C56" s="24" t="s">
+      <c r="B56" s="76"/>
+      <c r="C56" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="61" t="s">
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="46"/>
+      <c r="H56" s="45"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="74"/>
-      <c r="C57" s="48" t="s">
+      <c r="B57" s="77"/>
+      <c r="C57" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="48" t="s">
+      <c r="D57" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="E57" s="49" t="s">
+      <c r="E57" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="F57" s="49" t="s">
+      <c r="F57" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="G57" s="62" t="s">
+      <c r="G57" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="H57" s="54"/>
+      <c r="H57" s="53"/>
     </row>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="30"/>
+      <c r="B58" s="29"/>
       <c r="C58" s="15"/>
       <c r="D58" s="15"/>
       <c r="E58" s="17"/>
@@ -2737,33 +2740,33 @@
       <c r="H58" s="19"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="75" t="s">
+      <c r="B59" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="C59" s="35" t="s">
+      <c r="C59" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D59" s="35">
-        <v>201</v>
-      </c>
-      <c r="E59" s="36" t="s">
+      <c r="D59" s="34">
+        <v>151</v>
+      </c>
+      <c r="E59" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="F59" s="36" t="s">
+      <c r="F59" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G59" s="37" t="s">
+      <c r="G59" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="H59" s="51"/>
+      <c r="H59" s="50"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="76"/>
+      <c r="B60" s="73"/>
       <c r="C60" s="20" t="s">
         <v>2</v>
       </c>
       <c r="D60" s="20">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>76</v>
@@ -2771,18 +2774,18 @@
       <c r="F60" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="G60" s="58" t="s">
+      <c r="G60" s="57" t="s">
         <v>207</v>
       </c>
-      <c r="H60" s="52"/>
+      <c r="H60" s="51"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="76"/>
-      <c r="C61" s="63" t="s">
+      <c r="B61" s="73"/>
+      <c r="C61" s="62" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="20">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>98</v>
@@ -2790,85 +2793,85 @@
       <c r="F61" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="G61" s="58" t="s">
+      <c r="G61" s="57" t="s">
         <v>208</v>
       </c>
-      <c r="H61" s="39" t="s">
+      <c r="H61" s="38" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="76"/>
+      <c r="B62" s="73"/>
       <c r="C62" s="20" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="20"/>
-      <c r="G62" s="58" t="s">
+      <c r="G62" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="H62" s="52"/>
+      <c r="H62" s="51"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="76"/>
+      <c r="B63" s="73"/>
       <c r="C63" s="20" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
-      <c r="G63" s="58" t="s">
+      <c r="G63" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="H63" s="52"/>
+      <c r="H63" s="51"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="76"/>
+      <c r="B64" s="73"/>
       <c r="C64" s="20" t="s">
         <v>12</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="22"/>
-      <c r="G64" s="58" t="s">
+      <c r="G64" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="H64" s="52"/>
+      <c r="H64" s="51"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="76"/>
+      <c r="B65" s="73"/>
       <c r="C65" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
       <c r="F65" s="22"/>
-      <c r="G65" s="58" t="s">
+      <c r="G65" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="H65" s="52"/>
+      <c r="H65" s="51"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="76"/>
+      <c r="B66" s="73"/>
       <c r="C66" s="20" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="20"/>
-      <c r="G66" s="58" t="s">
+      <c r="G66" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H66" s="52"/>
+      <c r="H66" s="51"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="76"/>
-      <c r="C67" s="63" t="s">
+      <c r="B67" s="73"/>
+      <c r="C67" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="20">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="E67" s="22" t="s">
         <v>99</v>
@@ -2876,62 +2879,62 @@
       <c r="F67" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="G67" s="58" t="s">
+      <c r="G67" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="H67" s="39" t="s">
+      <c r="H67" s="38" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="76"/>
+      <c r="B68" s="73"/>
       <c r="C68" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
       <c r="F68" s="22"/>
-      <c r="G68" s="58" t="s">
+      <c r="G68" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="H68" s="52"/>
+      <c r="H68" s="51"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="76"/>
+      <c r="B69" s="73"/>
       <c r="C69" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
       <c r="F69" s="22"/>
-      <c r="G69" s="58" t="s">
+      <c r="G69" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="H69" s="52"/>
+      <c r="H69" s="51"/>
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="77"/>
-      <c r="C70" s="64" t="s">
+      <c r="B70" s="74"/>
+      <c r="C70" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D70" s="40">
-        <v>245</v>
-      </c>
-      <c r="E70" s="41" t="s">
+      <c r="D70" s="39">
+        <v>195</v>
+      </c>
+      <c r="E70" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="F70" s="41" t="s">
+      <c r="F70" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="59" t="s">
+      <c r="G70" s="58" t="s">
         <v>217</v>
       </c>
-      <c r="H70" s="42" t="s">
+      <c r="H70" s="41" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="30"/>
+      <c r="B71" s="29"/>
       <c r="C71" s="15"/>
       <c r="D71" s="15"/>
       <c r="E71" s="17"/>
@@ -2939,209 +2942,209 @@
       <c r="H71" s="19"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="72" t="s">
+      <c r="B72" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="C72" s="43" t="s">
+      <c r="C72" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D72" s="43">
+      <c r="D72" s="42">
         <v>139</v>
       </c>
-      <c r="E72" s="53" t="s">
+      <c r="E72" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="F72" s="53" t="s">
+      <c r="F72" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="G72" s="66" t="s">
+      <c r="G72" s="65" t="s">
         <v>293</v>
       </c>
-      <c r="H72" s="45"/>
+      <c r="H72" s="44"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="73"/>
-      <c r="C73" s="24" t="s">
+      <c r="B73" s="76"/>
+      <c r="C73" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="24">
+      <c r="D73" s="23">
         <v>139</v>
       </c>
-      <c r="E73" s="25" t="s">
+      <c r="E73" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="F73" s="25" t="s">
+      <c r="F73" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="G73" s="61" t="s">
+      <c r="G73" s="60" t="s">
         <v>218</v>
       </c>
-      <c r="H73" s="46"/>
+      <c r="H73" s="45"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="73"/>
-      <c r="C74" s="63" t="s">
+      <c r="B74" s="76"/>
+      <c r="C74" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D74" s="24">
+      <c r="D74" s="23">
         <v>142</v>
       </c>
-      <c r="E74" s="25" t="s">
+      <c r="E74" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="F74" s="26" t="s">
+      <c r="F74" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="G74" s="61" t="s">
+      <c r="G74" s="60" t="s">
         <v>219</v>
       </c>
-      <c r="H74" s="47" t="s">
+      <c r="H74" s="46" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="73"/>
-      <c r="C75" s="63" t="s">
+      <c r="B75" s="76"/>
+      <c r="C75" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="23">
         <v>176</v>
       </c>
-      <c r="E75" s="26" t="s">
+      <c r="E75" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F75" s="26" t="s">
+      <c r="F75" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="G75" s="61" t="s">
+      <c r="G75" s="60" t="s">
         <v>220</v>
       </c>
-      <c r="H75" s="47" t="s">
+      <c r="H75" s="46" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="73"/>
-      <c r="C76" s="24" t="s">
+      <c r="B76" s="76"/>
+      <c r="C76" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="61" t="s">
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="H76" s="46"/>
+      <c r="H76" s="45"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="73"/>
-      <c r="C77" s="24" t="s">
+      <c r="B77" s="76"/>
+      <c r="C77" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="61" t="s">
+      <c r="D77" s="23"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="60" t="s">
         <v>222</v>
       </c>
-      <c r="H77" s="46"/>
+      <c r="H77" s="45"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="73"/>
-      <c r="C78" s="24" t="s">
+      <c r="B78" s="76"/>
+      <c r="C78" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="61" t="s">
+      <c r="D78" s="23"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="60" t="s">
         <v>223</v>
       </c>
-      <c r="H78" s="46"/>
+      <c r="H78" s="45"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="73"/>
-      <c r="C79" s="24" t="s">
+      <c r="B79" s="76"/>
+      <c r="C79" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="61" t="s">
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="H79" s="46"/>
+      <c r="H79" s="45"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="73"/>
-      <c r="C80" s="63" t="s">
+      <c r="B80" s="76"/>
+      <c r="C80" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D80" s="24">
+      <c r="D80" s="23">
         <v>206</v>
       </c>
-      <c r="E80" s="26" t="s">
+      <c r="E80" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="F80" s="26" t="s">
+      <c r="F80" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="G80" s="61" t="s">
+      <c r="G80" s="60" t="s">
         <v>225</v>
       </c>
-      <c r="H80" s="47" t="s">
+      <c r="H80" s="46" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="73"/>
-      <c r="C81" s="24" t="s">
+      <c r="B81" s="76"/>
+      <c r="C81" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D81" s="24"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="26"/>
-      <c r="G81" s="61" t="s">
+      <c r="D81" s="23"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="60" t="s">
         <v>226</v>
       </c>
-      <c r="H81" s="46"/>
+      <c r="H81" s="45"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="73"/>
-      <c r="C82" s="24" t="s">
+      <c r="B82" s="76"/>
+      <c r="C82" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="24"/>
-      <c r="E82" s="24"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="61" t="s">
+      <c r="D82" s="23"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="60" t="s">
         <v>227</v>
       </c>
-      <c r="H82" s="46"/>
+      <c r="H82" s="45"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="74"/>
-      <c r="C83" s="64" t="s">
+      <c r="B83" s="77"/>
+      <c r="C83" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D83" s="48">
+      <c r="D83" s="47">
         <v>211</v>
       </c>
-      <c r="E83" s="49" t="s">
+      <c r="E83" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="F83" s="49" t="s">
+      <c r="F83" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="G83" s="62" t="s">
+      <c r="G83" s="61" t="s">
         <v>228</v>
       </c>
-      <c r="H83" s="50" t="s">
+      <c r="H83" s="49" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="30"/>
+      <c r="B84" s="29"/>
       <c r="C84" s="15"/>
       <c r="D84" s="15"/>
       <c r="E84" s="17"/>
@@ -3149,28 +3152,28 @@
       <c r="H84" s="19"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="75" t="s">
+      <c r="B85" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="C85" s="35" t="s">
+      <c r="C85" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D85" s="35">
+      <c r="D85" s="34">
         <v>131</v>
       </c>
-      <c r="E85" s="36" t="s">
+      <c r="E85" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="F85" s="36" t="s">
+      <c r="F85" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="G85" s="37" t="s">
+      <c r="G85" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="H85" s="51"/>
+      <c r="H85" s="50"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="76"/>
+      <c r="B86" s="73"/>
       <c r="C86" s="20" t="s">
         <v>2</v>
       </c>
@@ -3183,14 +3186,14 @@
       <c r="F86" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="G86" s="58" t="s">
+      <c r="G86" s="57" t="s">
         <v>229</v>
       </c>
-      <c r="H86" s="52"/>
+      <c r="H86" s="51"/>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="76"/>
-      <c r="C87" s="63" t="s">
+      <c r="B87" s="73"/>
+      <c r="C87" s="62" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="20">
@@ -3202,81 +3205,81 @@
       <c r="F87" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="G87" s="58" t="s">
+      <c r="G87" s="57" t="s">
         <v>230</v>
       </c>
-      <c r="H87" s="39" t="s">
+      <c r="H87" s="38" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="76"/>
+      <c r="B88" s="73"/>
       <c r="C88" s="20" t="s">
         <v>10</v>
       </c>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
-      <c r="G88" s="58" t="s">
+      <c r="G88" s="57" t="s">
         <v>231</v>
       </c>
-      <c r="H88" s="52"/>
+      <c r="H88" s="51"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="76"/>
+      <c r="B89" s="73"/>
       <c r="C89" s="20" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
-      <c r="G89" s="58" t="s">
+      <c r="G89" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="H89" s="39"/>
+      <c r="H89" s="38"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" s="76"/>
+      <c r="B90" s="73"/>
       <c r="C90" s="20" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="22"/>
-      <c r="G90" s="58" t="s">
+      <c r="G90" s="57" t="s">
         <v>233</v>
       </c>
-      <c r="H90" s="39"/>
+      <c r="H90" s="38"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="76"/>
+      <c r="B91" s="73"/>
       <c r="C91" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="22"/>
-      <c r="G91" s="58" t="s">
+      <c r="G91" s="57" t="s">
         <v>234</v>
       </c>
-      <c r="H91" s="39"/>
+      <c r="H91" s="38"/>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="76"/>
+      <c r="B92" s="73"/>
       <c r="C92" s="20" t="s">
         <v>14</v>
       </c>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="20"/>
-      <c r="G92" s="58" t="s">
+      <c r="G92" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="H92" s="39"/>
+      <c r="H92" s="38"/>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="76"/>
-      <c r="C93" s="63" t="s">
+      <c r="B93" s="73"/>
+      <c r="C93" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D93" s="20" t="s">
@@ -3288,62 +3291,62 @@
       <c r="F93" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="G93" s="58" t="s">
+      <c r="G93" s="57" t="s">
         <v>236</v>
       </c>
-      <c r="H93" s="39" t="s">
+      <c r="H93" s="38" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="76"/>
+      <c r="B94" s="73"/>
       <c r="C94" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
       <c r="F94" s="22"/>
-      <c r="G94" s="58" t="s">
+      <c r="G94" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="H94" s="39"/>
+      <c r="H94" s="38"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="76"/>
+      <c r="B95" s="73"/>
       <c r="C95" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="22"/>
-      <c r="G95" s="58" t="s">
+      <c r="G95" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="H95" s="39"/>
+      <c r="H95" s="38"/>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="77"/>
-      <c r="C96" s="64" t="s">
+      <c r="B96" s="74"/>
+      <c r="C96" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D96" s="40">
+      <c r="D96" s="39">
         <v>191</v>
       </c>
-      <c r="E96" s="41" t="s">
+      <c r="E96" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="F96" s="41" t="s">
+      <c r="F96" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="G96" s="59" t="s">
+      <c r="G96" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="H96" s="42" t="s">
+      <c r="H96" s="41" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="30"/>
+      <c r="B97" s="29"/>
       <c r="C97" s="15"/>
       <c r="D97" s="15"/>
       <c r="E97" s="17"/>
@@ -3351,239 +3354,239 @@
       <c r="H97" s="18"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="72" t="s">
+      <c r="B98" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="C98" s="43" t="s">
+      <c r="C98" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D98" s="43" t="s">
+      <c r="D98" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="E98" s="53" t="s">
+      <c r="E98" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="F98" s="53" t="s">
+      <c r="F98" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="G98" s="66" t="s">
+      <c r="G98" s="65" t="s">
         <v>295</v>
       </c>
-      <c r="H98" s="55"/>
+      <c r="H98" s="54"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="73"/>
-      <c r="C99" s="24" t="s">
+      <c r="B99" s="76"/>
+      <c r="C99" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D99" s="24" t="s">
+      <c r="D99" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E99" s="25" t="s">
+      <c r="E99" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F99" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="G99" s="61" t="s">
+      <c r="G99" s="60" t="s">
         <v>240</v>
       </c>
-      <c r="H99" s="47"/>
+      <c r="H99" s="46"/>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="73"/>
-      <c r="C100" s="24" t="s">
+      <c r="B100" s="76"/>
+      <c r="C100" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D100" s="24" t="s">
+      <c r="D100" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E100" s="25" t="s">
+      <c r="E100" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="F100" s="26" t="s">
+      <c r="F100" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="G100" s="61" t="s">
+      <c r="G100" s="60" t="s">
         <v>241</v>
       </c>
-      <c r="H100" s="47"/>
+      <c r="H100" s="46"/>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="73"/>
-      <c r="C101" s="24" t="s">
+      <c r="B101" s="76"/>
+      <c r="C101" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="61" t="s">
+      <c r="D101" s="23"/>
+      <c r="E101" s="23"/>
+      <c r="F101" s="23"/>
+      <c r="G101" s="60" t="s">
         <v>242</v>
       </c>
-      <c r="H101" s="47"/>
+      <c r="H101" s="46"/>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="73"/>
-      <c r="C102" s="24" t="s">
+      <c r="B102" s="76"/>
+      <c r="C102" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="24"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="24"/>
-      <c r="G102" s="61" t="s">
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="60" t="s">
         <v>243</v>
       </c>
-      <c r="H102" s="47"/>
+      <c r="H102" s="46"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="73"/>
-      <c r="C103" s="24" t="s">
+      <c r="B103" s="76"/>
+      <c r="C103" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D103" s="24"/>
-      <c r="E103" s="24"/>
-      <c r="F103" s="26"/>
-      <c r="G103" s="61" t="s">
+      <c r="D103" s="23"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="25"/>
+      <c r="G103" s="60" t="s">
         <v>244</v>
       </c>
-      <c r="H103" s="47"/>
+      <c r="H103" s="46"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="73"/>
-      <c r="C104" s="24" t="s">
+      <c r="B104" s="76"/>
+      <c r="C104" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D104" s="24"/>
-      <c r="E104" s="24"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="61" t="s">
+      <c r="D104" s="23"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="25"/>
+      <c r="G104" s="60" t="s">
         <v>245</v>
       </c>
-      <c r="H104" s="47"/>
+      <c r="H104" s="46"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="73"/>
-      <c r="C105" s="24" t="s">
+      <c r="B105" s="76"/>
+      <c r="C105" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="24"/>
-      <c r="E105" s="24"/>
-      <c r="F105" s="24"/>
-      <c r="G105" s="61" t="s">
+      <c r="D105" s="23"/>
+      <c r="E105" s="23"/>
+      <c r="F105" s="23"/>
+      <c r="G105" s="60" t="s">
         <v>246</v>
       </c>
-      <c r="H105" s="47"/>
+      <c r="H105" s="46"/>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="73"/>
-      <c r="C106" s="24" t="s">
+      <c r="B106" s="76"/>
+      <c r="C106" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="24" t="s">
+      <c r="D106" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E106" s="26" t="s">
+      <c r="E106" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="F106" s="26" t="s">
+      <c r="F106" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="G106" s="61" t="s">
+      <c r="G106" s="60" t="s">
         <v>247</v>
       </c>
-      <c r="H106" s="47"/>
+      <c r="H106" s="46"/>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="73"/>
-      <c r="C107" s="24" t="s">
+      <c r="B107" s="76"/>
+      <c r="C107" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D107" s="24"/>
-      <c r="E107" s="24"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="61" t="s">
+      <c r="D107" s="23"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="25"/>
+      <c r="G107" s="60" t="s">
         <v>248</v>
       </c>
-      <c r="H107" s="47"/>
+      <c r="H107" s="46"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="73"/>
-      <c r="C108" s="24" t="s">
+      <c r="B108" s="76"/>
+      <c r="C108" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D108" s="24"/>
-      <c r="E108" s="24"/>
-      <c r="F108" s="26"/>
-      <c r="G108" s="61" t="s">
+      <c r="D108" s="23"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="25"/>
+      <c r="G108" s="60" t="s">
         <v>249</v>
       </c>
-      <c r="H108" s="47"/>
+      <c r="H108" s="46"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="74"/>
-      <c r="C109" s="48" t="s">
+      <c r="B109" s="77"/>
+      <c r="C109" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D109" s="48" t="s">
+      <c r="D109" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="E109" s="49" t="s">
+      <c r="E109" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="F109" s="49" t="s">
+      <c r="F109" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="G109" s="62" t="s">
+      <c r="G109" s="61" t="s">
         <v>250</v>
       </c>
-      <c r="H109" s="54"/>
+      <c r="H109" s="53"/>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B112" s="70" t="s">
+      <c r="B112" s="78" t="s">
         <v>272</v>
       </c>
-      <c r="C112" s="70"/>
-      <c r="D112" s="70"/>
-      <c r="E112" s="70"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="70"/>
-      <c r="H112" s="70"/>
+      <c r="C112" s="78"/>
+      <c r="D112" s="78"/>
+      <c r="E112" s="78"/>
+      <c r="F112" s="78"/>
+      <c r="G112" s="78"/>
+      <c r="H112" s="78"/>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B113" s="70"/>
-      <c r="C113" s="70"/>
-      <c r="D113" s="70"/>
-      <c r="E113" s="70"/>
-      <c r="F113" s="70"/>
-      <c r="G113" s="70"/>
-      <c r="H113" s="70"/>
+      <c r="B113" s="78"/>
+      <c r="C113" s="78"/>
+      <c r="D113" s="78"/>
+      <c r="E113" s="78"/>
+      <c r="F113" s="78"/>
+      <c r="G113" s="78"/>
+      <c r="H113" s="78"/>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="E114" s="71" t="s">
+      <c r="E114" s="79" t="s">
         <v>278</v>
       </c>
-      <c r="F114" s="71"/>
-      <c r="G114" s="71"/>
-      <c r="H114" s="71"/>
+      <c r="F114" s="79"/>
+      <c r="G114" s="79"/>
+      <c r="H114" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B7:B18"/>
-    <mergeCell ref="B20:B31"/>
-    <mergeCell ref="B33:B44"/>
-    <mergeCell ref="B46:B57"/>
-    <mergeCell ref="B59:B70"/>
     <mergeCell ref="B112:H112"/>
     <mergeCell ref="B113:H113"/>
     <mergeCell ref="E114:H114"/>
     <mergeCell ref="B72:B83"/>
     <mergeCell ref="B85:B96"/>
     <mergeCell ref="B98:B109"/>
+    <mergeCell ref="B7:B18"/>
+    <mergeCell ref="B20:B31"/>
+    <mergeCell ref="B33:B44"/>
+    <mergeCell ref="B46:B57"/>
+    <mergeCell ref="B59:B70"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3606,35 +3609,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="81" t="s">
+      <c r="C3" s="70"/>
+      <c r="D3" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="83"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="82"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="81" t="s">
+      <c r="C4" s="70"/>
+      <c r="D4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="83"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="82"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BE57B1-A482-455F-AA41-A5D236B73F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D9A6C4-B53C-4E81-8349-F78EAEA67FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -942,56 +942,56 @@
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=2cb0002e70b3711dd473750d48e2cacd&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
   <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=d069b7257f832f99cf096f5f0fe9515d&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=d7eaba5939a30b6038ce73667a70caaa&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=8ecbff58afd7e8cfd2117a89b208a1af&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=aeeb648cd4ef4c0906cfd837cc4717c2&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=3e47622a46c3787c3c32417aad49c53d&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=162fa03fb10c202011592c6090e34d49&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=aa61327dced678304d71a6830bd7c987&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=9f3c68785725e402c445548a04e5a6d9&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=ac813de226fead77bf0db75294335e79&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=8e8ac0b08e5c1feb0913ab8c9bec7868&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=bb220258501b7a27bc4a17d455dfcadc&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=edcb65ab45b5fa3b6c0ebac110a5579c&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>GeoMatik2D</t>
+  </si>
+  <si>
+    <t>GeomMatik3D</t>
+  </si>
+  <si>
     <t>T1: 34, 40, 42
 T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81
-T3: 100, 107
+T3: 99, 100, 101, 107, 112, 115,
 T4:
 T5:163, 168, 177, 179, 180, 190,
 T6:
 T7:
 T8:</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=d069b7257f832f99cf096f5f0fe9515d&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=d7eaba5939a30b6038ce73667a70caaa&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=8ecbff58afd7e8cfd2117a89b208a1af&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=aeeb648cd4ef4c0906cfd837cc4717c2&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=3e47622a46c3787c3c32417aad49c53d&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=162fa03fb10c202011592c6090e34d49&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=aa61327dced678304d71a6830bd7c987&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=9f3c68785725e402c445548a04e5a6d9&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=ac813de226fead77bf0db75294335e79&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=8e8ac0b08e5c1feb0913ab8c9bec7868&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=bb220258501b7a27bc4a17d455dfcadc&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=edcb65ab45b5fa3b6c0ebac110a5579c&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>GeoMatik2D</t>
-  </si>
-  <si>
-    <t>GeomMatik3D</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1510,6 +1510,63 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1522,21 +1579,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1545,60 +1587,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1896,41 +1884,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64" t="s">
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64" t="s">
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="21"/>
@@ -1942,51 +1930,51 @@
       <c r="H5" s="44"/>
     </row>
     <row r="6" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="84" t="s">
+      <c r="G6" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="85" t="s">
+      <c r="H6" s="68" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="72" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="60">
         <v>13</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="78" t="s">
+      <c r="F7" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="62" t="s">
         <v>284</v>
       </c>
-      <c r="H7" s="80"/>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="60"/>
+      <c r="B8" s="73"/>
       <c r="C8" s="50" t="s">
         <v>2</v>
       </c>
@@ -2007,7 +1995,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="60"/>
+      <c r="B9" s="73"/>
       <c r="C9" s="50" t="s">
         <v>9</v>
       </c>
@@ -2028,15 +2016,15 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="60"/>
+      <c r="B10" s="73"/>
       <c r="C10" s="50" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>257</v>
@@ -2049,7 +2037,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="60"/>
+      <c r="B11" s="73"/>
       <c r="C11" s="50" t="s">
         <v>11</v>
       </c>
@@ -2070,7 +2058,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="60"/>
+      <c r="B12" s="73"/>
       <c r="C12" s="50" t="s">
         <v>12</v>
       </c>
@@ -2091,7 +2079,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="60"/>
+      <c r="B13" s="73"/>
       <c r="C13" s="50" t="s">
         <v>13</v>
       </c>
@@ -2112,7 +2100,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="60"/>
+      <c r="B14" s="73"/>
       <c r="C14" s="15" t="s">
         <v>14</v>
       </c>
@@ -2125,7 +2113,7 @@
       <c r="H14" s="28"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="60"/>
+      <c r="B15" s="73"/>
       <c r="C15" s="50" t="s">
         <v>15</v>
       </c>
@@ -2146,7 +2134,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="60"/>
+      <c r="B16" s="73"/>
       <c r="C16" s="50" t="s">
         <v>16</v>
       </c>
@@ -2167,7 +2155,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="60"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="15" t="s">
         <v>18</v>
       </c>
@@ -2180,7 +2168,7 @@
       <c r="H17" s="28"/>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="61"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="51" t="s">
         <v>19</v>
       </c>
@@ -2200,17 +2188,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-    </row>
+    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="75" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="53" t="s">
@@ -2231,7 +2211,7 @@
       <c r="H20" s="34"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="57"/>
+      <c r="B21" s="76"/>
       <c r="C21" s="50" t="s">
         <v>2</v>
       </c>
@@ -2252,7 +2232,7 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="57"/>
+      <c r="B22" s="76"/>
       <c r="C22" s="50" t="s">
         <v>9</v>
       </c>
@@ -2273,7 +2253,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="57"/>
+      <c r="B23" s="76"/>
       <c r="C23" s="18" t="s">
         <v>10</v>
       </c>
@@ -2286,7 +2266,7 @@
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="57"/>
+      <c r="B24" s="76"/>
       <c r="C24" s="18" t="s">
         <v>11</v>
       </c>
@@ -2299,7 +2279,7 @@
       <c r="H24" s="36"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="57"/>
+      <c r="B25" s="76"/>
       <c r="C25" s="18" t="s">
         <v>12</v>
       </c>
@@ -2312,7 +2292,7 @@
       <c r="H25" s="36"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="57"/>
+      <c r="B26" s="76"/>
       <c r="C26" s="18" t="s">
         <v>13</v>
       </c>
@@ -2325,7 +2305,7 @@
       <c r="H26" s="36"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="57"/>
+      <c r="B27" s="76"/>
       <c r="C27" s="18" t="s">
         <v>14</v>
       </c>
@@ -2338,7 +2318,7 @@
       <c r="H27" s="36"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="57"/>
+      <c r="B28" s="76"/>
       <c r="C28" s="50" t="s">
         <v>15</v>
       </c>
@@ -2359,7 +2339,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="57"/>
+      <c r="B29" s="76"/>
       <c r="C29" s="18" t="s">
         <v>16</v>
       </c>
@@ -2372,7 +2352,7 @@
       <c r="H29" s="36"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="57"/>
+      <c r="B30" s="76"/>
       <c r="C30" s="18" t="s">
         <v>18</v>
       </c>
@@ -2385,7 +2365,7 @@
       <c r="H30" s="36"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="58"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="51" t="s">
         <v>19</v>
       </c>
@@ -2406,16 +2386,11 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="68"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="72"/>
+      <c r="F32" s="24"/>
+      <c r="H32" s="56"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="59" t="s">
+      <c r="B33" s="78" t="s">
         <v>155</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -2436,7 +2411,7 @@
       <c r="H33" s="40"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="60"/>
+      <c r="B34" s="73"/>
       <c r="C34" s="15" t="s">
         <v>2</v>
       </c>
@@ -2453,16 +2428,16 @@
         <v>183</v>
       </c>
       <c r="H34" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="60"/>
+      <c r="B35" s="73"/>
       <c r="C35" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="15">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E35" s="16" t="s">
         <v>94</v>
@@ -2478,7 +2453,7 @@
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="60"/>
+      <c r="B36" s="73"/>
       <c r="C36" s="15" t="s">
         <v>10</v>
       </c>
@@ -2491,7 +2466,7 @@
       <c r="H36" s="28"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="60"/>
+      <c r="B37" s="73"/>
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
@@ -2504,7 +2479,7 @@
       <c r="H37" s="41"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="60"/>
+      <c r="B38" s="73"/>
       <c r="C38" s="15" t="s">
         <v>12</v>
       </c>
@@ -2517,7 +2492,7 @@
       <c r="H38" s="41"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="60"/>
+      <c r="B39" s="73"/>
       <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
@@ -2530,7 +2505,7 @@
       <c r="H39" s="41"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="60"/>
+      <c r="B40" s="73"/>
       <c r="C40" s="15" t="s">
         <v>14</v>
       </c>
@@ -2543,12 +2518,12 @@
       <c r="H40" s="41"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="60"/>
+      <c r="B41" s="73"/>
       <c r="C41" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="15">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>95</v>
@@ -2564,7 +2539,7 @@
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="60"/>
+      <c r="B42" s="73"/>
       <c r="C42" s="15" t="s">
         <v>16</v>
       </c>
@@ -2577,7 +2552,7 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="60"/>
+      <c r="B43" s="73"/>
       <c r="C43" s="15" t="s">
         <v>18</v>
       </c>
@@ -2590,12 +2565,12 @@
       <c r="H43" s="41"/>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="61"/>
+      <c r="B44" s="74"/>
       <c r="C44" s="29" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="29">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E44" s="30" t="s">
         <v>251</v>
@@ -2611,16 +2586,11 @@
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="68"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="71"/>
-      <c r="H45" s="73"/>
+      <c r="F45" s="24"/>
+      <c r="H45" s="57"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="75" t="s">
         <v>156</v>
       </c>
       <c r="C46" s="32" t="s">
@@ -2641,7 +2611,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="57"/>
+      <c r="B47" s="76"/>
       <c r="C47" s="18" t="s">
         <v>2</v>
       </c>
@@ -2658,11 +2628,11 @@
         <v>194</v>
       </c>
       <c r="H47" s="36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="57"/>
+      <c r="B48" s="76"/>
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
@@ -2679,11 +2649,11 @@
         <v>195</v>
       </c>
       <c r="H48" s="36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="57"/>
+      <c r="B49" s="76"/>
       <c r="C49" s="18" t="s">
         <v>10</v>
       </c>
@@ -2691,7 +2661,7 @@
         <v>88</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>258</v>
@@ -2704,7 +2674,7 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="57"/>
+      <c r="B50" s="76"/>
       <c r="C50" s="18" t="s">
         <v>11</v>
       </c>
@@ -2717,7 +2687,7 @@
       <c r="H50" s="35"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="57"/>
+      <c r="B51" s="76"/>
       <c r="C51" s="18" t="s">
         <v>12</v>
       </c>
@@ -2730,7 +2700,7 @@
       <c r="H51" s="35"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="57"/>
+      <c r="B52" s="76"/>
       <c r="C52" s="18" t="s">
         <v>13</v>
       </c>
@@ -2743,7 +2713,7 @@
       <c r="H52" s="35"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="57"/>
+      <c r="B53" s="76"/>
       <c r="C53" s="18" t="s">
         <v>14</v>
       </c>
@@ -2756,7 +2726,7 @@
       <c r="H53" s="35"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="57"/>
+      <c r="B54" s="76"/>
       <c r="C54" s="18" t="s">
         <v>15</v>
       </c>
@@ -2773,11 +2743,11 @@
         <v>201</v>
       </c>
       <c r="H54" s="36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="57"/>
+      <c r="B55" s="76"/>
       <c r="C55" s="18" t="s">
         <v>16</v>
       </c>
@@ -2790,7 +2760,7 @@
       <c r="H55" s="35"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="57"/>
+      <c r="B56" s="76"/>
       <c r="C56" s="18" t="s">
         <v>18</v>
       </c>
@@ -2803,7 +2773,7 @@
       <c r="H56" s="35"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="58"/>
+      <c r="B57" s="77"/>
       <c r="C57" s="37" t="s">
         <v>19</v>
       </c>
@@ -2820,20 +2790,15 @@
         <v>204</v>
       </c>
       <c r="H57" s="39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="68"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="69"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="71"/>
-      <c r="H58" s="74"/>
+      <c r="F58" s="24"/>
+      <c r="H58" s="58"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="59" t="s">
+      <c r="B59" s="78" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="25" t="s">
@@ -2854,7 +2819,7 @@
       <c r="H59" s="40"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="60"/>
+      <c r="B60" s="73"/>
       <c r="C60" s="15" t="s">
         <v>2</v>
       </c>
@@ -2871,11 +2836,11 @@
         <v>205</v>
       </c>
       <c r="H60" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="60"/>
+      <c r="B61" s="73"/>
       <c r="C61" s="15" t="s">
         <v>9</v>
       </c>
@@ -2896,7 +2861,7 @@
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="60"/>
+      <c r="B62" s="73"/>
       <c r="C62" s="15" t="s">
         <v>10</v>
       </c>
@@ -2909,7 +2874,7 @@
       <c r="H62" s="41"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="60"/>
+      <c r="B63" s="73"/>
       <c r="C63" s="15" t="s">
         <v>11</v>
       </c>
@@ -2922,7 +2887,7 @@
       <c r="H63" s="41"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="60"/>
+      <c r="B64" s="73"/>
       <c r="C64" s="15" t="s">
         <v>12</v>
       </c>
@@ -2935,7 +2900,7 @@
       <c r="H64" s="41"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="60"/>
+      <c r="B65" s="73"/>
       <c r="C65" s="15" t="s">
         <v>13</v>
       </c>
@@ -2948,7 +2913,7 @@
       <c r="H65" s="41"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="60"/>
+      <c r="B66" s="73"/>
       <c r="C66" s="15" t="s">
         <v>14</v>
       </c>
@@ -2961,7 +2926,7 @@
       <c r="H66" s="41"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="60"/>
+      <c r="B67" s="73"/>
       <c r="C67" s="15" t="s">
         <v>15</v>
       </c>
@@ -2982,7 +2947,7 @@
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="60"/>
+      <c r="B68" s="73"/>
       <c r="C68" s="15" t="s">
         <v>16</v>
       </c>
@@ -2995,7 +2960,7 @@
       <c r="H68" s="41"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="60"/>
+      <c r="B69" s="73"/>
       <c r="C69" s="15" t="s">
         <v>18</v>
       </c>
@@ -3008,7 +2973,7 @@
       <c r="H69" s="41"/>
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="61"/>
+      <c r="B70" s="74"/>
       <c r="C70" s="29" t="s">
         <v>19</v>
       </c>
@@ -3029,16 +2994,11 @@
       </c>
     </row>
     <row r="71" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="68"/>
-      <c r="C71" s="69"/>
-      <c r="D71" s="69"/>
-      <c r="E71" s="70"/>
-      <c r="F71" s="70"/>
-      <c r="G71" s="71"/>
-      <c r="H71" s="74"/>
+      <c r="F71" s="24"/>
+      <c r="H71" s="58"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="56" t="s">
+      <c r="B72" s="75" t="s">
         <v>158</v>
       </c>
       <c r="C72" s="32" t="s">
@@ -3059,7 +3019,7 @@
       <c r="H72" s="34"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="57"/>
+      <c r="B73" s="76"/>
       <c r="C73" s="18" t="s">
         <v>2</v>
       </c>
@@ -3076,11 +3036,11 @@
         <v>216</v>
       </c>
       <c r="H73" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="57"/>
+      <c r="B74" s="76"/>
       <c r="C74" s="18" t="s">
         <v>9</v>
       </c>
@@ -3101,7 +3061,7 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="57"/>
+      <c r="B75" s="76"/>
       <c r="C75" s="18" t="s">
         <v>10</v>
       </c>
@@ -3122,7 +3082,7 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="57"/>
+      <c r="B76" s="76"/>
       <c r="C76" s="18" t="s">
         <v>11</v>
       </c>
@@ -3135,7 +3095,7 @@
       <c r="H76" s="35"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="57"/>
+      <c r="B77" s="76"/>
       <c r="C77" s="18" t="s">
         <v>12</v>
       </c>
@@ -3148,7 +3108,7 @@
       <c r="H77" s="35"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="57"/>
+      <c r="B78" s="76"/>
       <c r="C78" s="18" t="s">
         <v>13</v>
       </c>
@@ -3161,7 +3121,7 @@
       <c r="H78" s="35"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="57"/>
+      <c r="B79" s="76"/>
       <c r="C79" s="18" t="s">
         <v>14</v>
       </c>
@@ -3174,7 +3134,7 @@
       <c r="H79" s="35"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="57"/>
+      <c r="B80" s="76"/>
       <c r="C80" s="18" t="s">
         <v>15</v>
       </c>
@@ -3195,7 +3155,7 @@
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="57"/>
+      <c r="B81" s="76"/>
       <c r="C81" s="18" t="s">
         <v>16</v>
       </c>
@@ -3208,7 +3168,7 @@
       <c r="H81" s="35"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="57"/>
+      <c r="B82" s="76"/>
       <c r="C82" s="18" t="s">
         <v>18</v>
       </c>
@@ -3221,7 +3181,7 @@
       <c r="H82" s="35"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="58"/>
+      <c r="B83" s="77"/>
       <c r="C83" s="37" t="s">
         <v>19</v>
       </c>
@@ -3242,16 +3202,10 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="68"/>
-      <c r="C84" s="69"/>
-      <c r="D84" s="69"/>
-      <c r="E84" s="70"/>
-      <c r="F84" s="69"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="74"/>
+      <c r="H84" s="58"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="59" t="s">
+      <c r="B85" s="78" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="25" t="s">
@@ -3272,7 +3226,7 @@
       <c r="H85" s="40"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="60"/>
+      <c r="B86" s="73"/>
       <c r="C86" s="15" t="s">
         <v>2</v>
       </c>
@@ -3289,11 +3243,11 @@
         <v>227</v>
       </c>
       <c r="H86" s="28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="60"/>
+      <c r="B87" s="73"/>
       <c r="C87" s="15" t="s">
         <v>9</v>
       </c>
@@ -3314,7 +3268,7 @@
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="60"/>
+      <c r="B88" s="73"/>
       <c r="C88" s="15" t="s">
         <v>10</v>
       </c>
@@ -3327,7 +3281,7 @@
       <c r="H88" s="41"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="60"/>
+      <c r="B89" s="73"/>
       <c r="C89" s="15" t="s">
         <v>11</v>
       </c>
@@ -3340,7 +3294,7 @@
       <c r="H89" s="28"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" s="60"/>
+      <c r="B90" s="73"/>
       <c r="C90" s="15" t="s">
         <v>12</v>
       </c>
@@ -3353,7 +3307,7 @@
       <c r="H90" s="28"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="60"/>
+      <c r="B91" s="73"/>
       <c r="C91" s="15" t="s">
         <v>13</v>
       </c>
@@ -3366,7 +3320,7 @@
       <c r="H91" s="28"/>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="60"/>
+      <c r="B92" s="73"/>
       <c r="C92" s="15" t="s">
         <v>14</v>
       </c>
@@ -3379,7 +3333,7 @@
       <c r="H92" s="28"/>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="60"/>
+      <c r="B93" s="73"/>
       <c r="C93" s="15" t="s">
         <v>15</v>
       </c>
@@ -3400,7 +3354,7 @@
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="60"/>
+      <c r="B94" s="73"/>
       <c r="C94" s="15" t="s">
         <v>16</v>
       </c>
@@ -3413,7 +3367,7 @@
       <c r="H94" s="28"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="60"/>
+      <c r="B95" s="73"/>
       <c r="C95" s="15" t="s">
         <v>18</v>
       </c>
@@ -3426,7 +3380,7 @@
       <c r="H95" s="28"/>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="61"/>
+      <c r="B96" s="74"/>
       <c r="C96" s="29" t="s">
         <v>19</v>
       </c>
@@ -3447,16 +3401,11 @@
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="68"/>
-      <c r="C97" s="69"/>
-      <c r="D97" s="69"/>
-      <c r="E97" s="70"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="71"/>
-      <c r="H97" s="72"/>
+      <c r="F97" s="24"/>
+      <c r="H97" s="56"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="56" t="s">
+      <c r="B98" s="75" t="s">
         <v>160</v>
       </c>
       <c r="C98" s="32" t="s">
@@ -3477,7 +3426,7 @@
       <c r="H98" s="43"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="57"/>
+      <c r="B99" s="76"/>
       <c r="C99" s="18" t="s">
         <v>2</v>
       </c>
@@ -3494,11 +3443,11 @@
         <v>238</v>
       </c>
       <c r="H99" s="36" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="57"/>
+      <c r="B100" s="76"/>
       <c r="C100" s="18" t="s">
         <v>9</v>
       </c>
@@ -3515,11 +3464,11 @@
         <v>239</v>
       </c>
       <c r="H100" s="36" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="57"/>
+      <c r="B101" s="76"/>
       <c r="C101" s="18" t="s">
         <v>10</v>
       </c>
@@ -3532,7 +3481,7 @@
       <c r="H101" s="36"/>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="57"/>
+      <c r="B102" s="76"/>
       <c r="C102" s="18" t="s">
         <v>11</v>
       </c>
@@ -3545,7 +3494,7 @@
       <c r="H102" s="36"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="57"/>
+      <c r="B103" s="76"/>
       <c r="C103" s="18" t="s">
         <v>12</v>
       </c>
@@ -3558,7 +3507,7 @@
       <c r="H103" s="36"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="57"/>
+      <c r="B104" s="76"/>
       <c r="C104" s="18" t="s">
         <v>13</v>
       </c>
@@ -3571,7 +3520,7 @@
       <c r="H104" s="36"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="57"/>
+      <c r="B105" s="76"/>
       <c r="C105" s="18" t="s">
         <v>14</v>
       </c>
@@ -3584,7 +3533,7 @@
       <c r="H105" s="36"/>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="57"/>
+      <c r="B106" s="76"/>
       <c r="C106" s="18" t="s">
         <v>15</v>
       </c>
@@ -3601,11 +3550,11 @@
         <v>245</v>
       </c>
       <c r="H106" s="36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="57"/>
+      <c r="B107" s="76"/>
       <c r="C107" s="18" t="s">
         <v>16</v>
       </c>
@@ -3618,7 +3567,7 @@
       <c r="H107" s="36"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="57"/>
+      <c r="B108" s="76"/>
       <c r="C108" s="18" t="s">
         <v>18</v>
       </c>
@@ -3631,7 +3580,7 @@
       <c r="H108" s="36"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="58"/>
+      <c r="B109" s="77"/>
       <c r="C109" s="37" t="s">
         <v>19</v>
       </c>
@@ -3648,24 +3597,24 @@
         <v>248</v>
       </c>
       <c r="H109" s="39" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B72:B83"/>
+    <mergeCell ref="B85:B96"/>
+    <mergeCell ref="B98:B109"/>
+    <mergeCell ref="B7:B18"/>
+    <mergeCell ref="B20:B31"/>
+    <mergeCell ref="B33:B44"/>
+    <mergeCell ref="B46:B57"/>
+    <mergeCell ref="B59:B70"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B7:B18"/>
-    <mergeCell ref="B20:B31"/>
-    <mergeCell ref="B33:B44"/>
-    <mergeCell ref="B46:B57"/>
-    <mergeCell ref="B59:B70"/>
-    <mergeCell ref="B72:B83"/>
-    <mergeCell ref="B85:B96"/>
-    <mergeCell ref="B98:B109"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3688,35 +3637,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="65" t="s">
+      <c r="C3" s="70"/>
+      <c r="D3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="67"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="81"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="65" t="s">
+      <c r="C4" s="70"/>
+      <c r="D4" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="66"/>
-      <c r="F4" s="67"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="81"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D9A6C4-B53C-4E81-8349-F78EAEA67FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794C0133-FE17-4225-A9D9-1B057B3A9471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -986,9 +986,9 @@
   <si>
     <t>T1: 34, 40, 42
 T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81
-T3: 99, 100, 101, 107, 112, 115,
+T3: 99, 100, 101, 107, 112, 115
 T4:
-T5:163, 168, 177, 179, 180, 190,
+T5:165, 170, 171, 177, 179, 181, 193
 T6:
 T7:
 T8:</t>
@@ -1345,7 +1345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1549,6 +1549,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1558,27 +1579,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1587,6 +1587,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1884,41 +1887,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="71" t="s">
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="71" t="s">
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="21"/>
@@ -1953,7 +1956,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="75" t="s">
         <v>153</v>
       </c>
       <c r="C7" s="59" t="s">
@@ -2190,7 +2193,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="69" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="53" t="s">
@@ -2211,7 +2214,7 @@
       <c r="H20" s="34"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="76"/>
+      <c r="B21" s="70"/>
       <c r="C21" s="50" t="s">
         <v>2</v>
       </c>
@@ -2232,7 +2235,7 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="76"/>
+      <c r="B22" s="70"/>
       <c r="C22" s="50" t="s">
         <v>9</v>
       </c>
@@ -2253,7 +2256,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="76"/>
+      <c r="B23" s="70"/>
       <c r="C23" s="18" t="s">
         <v>10</v>
       </c>
@@ -2266,7 +2269,7 @@
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="76"/>
+      <c r="B24" s="70"/>
       <c r="C24" s="18" t="s">
         <v>11</v>
       </c>
@@ -2279,7 +2282,7 @@
       <c r="H24" s="36"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="76"/>
+      <c r="B25" s="70"/>
       <c r="C25" s="18" t="s">
         <v>12</v>
       </c>
@@ -2292,7 +2295,7 @@
       <c r="H25" s="36"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="76"/>
+      <c r="B26" s="70"/>
       <c r="C26" s="18" t="s">
         <v>13</v>
       </c>
@@ -2305,7 +2308,7 @@
       <c r="H26" s="36"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="76"/>
+      <c r="B27" s="70"/>
       <c r="C27" s="18" t="s">
         <v>14</v>
       </c>
@@ -2318,7 +2321,7 @@
       <c r="H27" s="36"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="76"/>
+      <c r="B28" s="70"/>
       <c r="C28" s="50" t="s">
         <v>15</v>
       </c>
@@ -2339,7 +2342,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="76"/>
+      <c r="B29" s="70"/>
       <c r="C29" s="18" t="s">
         <v>16</v>
       </c>
@@ -2352,7 +2355,7 @@
       <c r="H29" s="36"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="76"/>
+      <c r="B30" s="70"/>
       <c r="C30" s="18" t="s">
         <v>18</v>
       </c>
@@ -2365,7 +2368,7 @@
       <c r="H30" s="36"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="77"/>
+      <c r="B31" s="71"/>
       <c r="C31" s="51" t="s">
         <v>19</v>
       </c>
@@ -2390,7 +2393,7 @@
       <c r="H32" s="56"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="72" t="s">
         <v>155</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -2590,7 +2593,7 @@
       <c r="H45" s="57"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="75" t="s">
+      <c r="B46" s="69" t="s">
         <v>156</v>
       </c>
       <c r="C46" s="32" t="s">
@@ -2611,7 +2614,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="76"/>
+      <c r="B47" s="70"/>
       <c r="C47" s="18" t="s">
         <v>2</v>
       </c>
@@ -2632,7 +2635,7 @@
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="76"/>
+      <c r="B48" s="70"/>
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
@@ -2653,7 +2656,7 @@
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="76"/>
+      <c r="B49" s="70"/>
       <c r="C49" s="18" t="s">
         <v>10</v>
       </c>
@@ -2674,7 +2677,7 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="76"/>
+      <c r="B50" s="70"/>
       <c r="C50" s="18" t="s">
         <v>11</v>
       </c>
@@ -2687,7 +2690,7 @@
       <c r="H50" s="35"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="76"/>
+      <c r="B51" s="70"/>
       <c r="C51" s="18" t="s">
         <v>12</v>
       </c>
@@ -2700,7 +2703,7 @@
       <c r="H51" s="35"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="76"/>
+      <c r="B52" s="70"/>
       <c r="C52" s="18" t="s">
         <v>13</v>
       </c>
@@ -2713,7 +2716,7 @@
       <c r="H52" s="35"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="76"/>
+      <c r="B53" s="70"/>
       <c r="C53" s="18" t="s">
         <v>14</v>
       </c>
@@ -2726,7 +2729,7 @@
       <c r="H53" s="35"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="76"/>
+      <c r="B54" s="70"/>
       <c r="C54" s="18" t="s">
         <v>15</v>
       </c>
@@ -2747,7 +2750,7 @@
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="76"/>
+      <c r="B55" s="70"/>
       <c r="C55" s="18" t="s">
         <v>16</v>
       </c>
@@ -2760,7 +2763,7 @@
       <c r="H55" s="35"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="76"/>
+      <c r="B56" s="70"/>
       <c r="C56" s="18" t="s">
         <v>18</v>
       </c>
@@ -2773,7 +2776,7 @@
       <c r="H56" s="35"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="77"/>
+      <c r="B57" s="71"/>
       <c r="C57" s="37" t="s">
         <v>19</v>
       </c>
@@ -2798,14 +2801,14 @@
       <c r="H58" s="58"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="78" t="s">
+      <c r="B59" s="72" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="25" t="s">
         <v>1</v>
       </c>
       <c r="D59" s="25">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>79</v>
@@ -2824,7 +2827,7 @@
         <v>2</v>
       </c>
       <c r="D60" s="15">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E60" s="16" t="s">
         <v>76</v>
@@ -2845,7 +2848,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="15">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>98</v>
@@ -2931,7 +2934,7 @@
         <v>15</v>
       </c>
       <c r="D67" s="15">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>99</v>
@@ -2978,7 +2981,7 @@
         <v>19</v>
       </c>
       <c r="D70" s="29">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E70" s="30" t="s">
         <v>253</v>
@@ -2986,7 +2989,7 @@
       <c r="F70" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="46" t="s">
+      <c r="G70" s="82" t="s">
         <v>215</v>
       </c>
       <c r="H70" s="31" t="s">
@@ -2998,7 +3001,7 @@
       <c r="H71" s="58"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="75" t="s">
+      <c r="B72" s="69" t="s">
         <v>158</v>
       </c>
       <c r="C72" s="32" t="s">
@@ -3019,7 +3022,7 @@
       <c r="H72" s="34"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="76"/>
+      <c r="B73" s="70"/>
       <c r="C73" s="18" t="s">
         <v>2</v>
       </c>
@@ -3040,7 +3043,7 @@
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="76"/>
+      <c r="B74" s="70"/>
       <c r="C74" s="18" t="s">
         <v>9</v>
       </c>
@@ -3061,7 +3064,7 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="76"/>
+      <c r="B75" s="70"/>
       <c r="C75" s="18" t="s">
         <v>10</v>
       </c>
@@ -3082,7 +3085,7 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="76"/>
+      <c r="B76" s="70"/>
       <c r="C76" s="18" t="s">
         <v>11</v>
       </c>
@@ -3095,7 +3098,7 @@
       <c r="H76" s="35"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="76"/>
+      <c r="B77" s="70"/>
       <c r="C77" s="18" t="s">
         <v>12</v>
       </c>
@@ -3108,7 +3111,7 @@
       <c r="H77" s="35"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="76"/>
+      <c r="B78" s="70"/>
       <c r="C78" s="18" t="s">
         <v>13</v>
       </c>
@@ -3121,7 +3124,7 @@
       <c r="H78" s="35"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="76"/>
+      <c r="B79" s="70"/>
       <c r="C79" s="18" t="s">
         <v>14</v>
       </c>
@@ -3134,7 +3137,7 @@
       <c r="H79" s="35"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="76"/>
+      <c r="B80" s="70"/>
       <c r="C80" s="18" t="s">
         <v>15</v>
       </c>
@@ -3155,7 +3158,7 @@
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="76"/>
+      <c r="B81" s="70"/>
       <c r="C81" s="18" t="s">
         <v>16</v>
       </c>
@@ -3168,7 +3171,7 @@
       <c r="H81" s="35"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="76"/>
+      <c r="B82" s="70"/>
       <c r="C82" s="18" t="s">
         <v>18</v>
       </c>
@@ -3181,7 +3184,7 @@
       <c r="H82" s="35"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="77"/>
+      <c r="B83" s="71"/>
       <c r="C83" s="37" t="s">
         <v>19</v>
       </c>
@@ -3205,7 +3208,7 @@
       <c r="H84" s="58"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="78" t="s">
+      <c r="B85" s="72" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="25" t="s">
@@ -3405,7 +3408,7 @@
       <c r="H97" s="56"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="75" t="s">
+      <c r="B98" s="69" t="s">
         <v>160</v>
       </c>
       <c r="C98" s="32" t="s">
@@ -3426,7 +3429,7 @@
       <c r="H98" s="43"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="76"/>
+      <c r="B99" s="70"/>
       <c r="C99" s="18" t="s">
         <v>2</v>
       </c>
@@ -3447,7 +3450,7 @@
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="76"/>
+      <c r="B100" s="70"/>
       <c r="C100" s="18" t="s">
         <v>9</v>
       </c>
@@ -3468,7 +3471,7 @@
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="76"/>
+      <c r="B101" s="70"/>
       <c r="C101" s="18" t="s">
         <v>10</v>
       </c>
@@ -3481,7 +3484,7 @@
       <c r="H101" s="36"/>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="76"/>
+      <c r="B102" s="70"/>
       <c r="C102" s="18" t="s">
         <v>11</v>
       </c>
@@ -3494,7 +3497,7 @@
       <c r="H102" s="36"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="76"/>
+      <c r="B103" s="70"/>
       <c r="C103" s="18" t="s">
         <v>12</v>
       </c>
@@ -3507,7 +3510,7 @@
       <c r="H103" s="36"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="76"/>
+      <c r="B104" s="70"/>
       <c r="C104" s="18" t="s">
         <v>13</v>
       </c>
@@ -3520,7 +3523,7 @@
       <c r="H104" s="36"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="76"/>
+      <c r="B105" s="70"/>
       <c r="C105" s="18" t="s">
         <v>14</v>
       </c>
@@ -3533,7 +3536,7 @@
       <c r="H105" s="36"/>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="76"/>
+      <c r="B106" s="70"/>
       <c r="C106" s="18" t="s">
         <v>15</v>
       </c>
@@ -3554,7 +3557,7 @@
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="76"/>
+      <c r="B107" s="70"/>
       <c r="C107" s="18" t="s">
         <v>16</v>
       </c>
@@ -3567,7 +3570,7 @@
       <c r="H107" s="36"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="76"/>
+      <c r="B108" s="70"/>
       <c r="C108" s="18" t="s">
         <v>18</v>
       </c>
@@ -3580,7 +3583,7 @@
       <c r="H108" s="36"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="77"/>
+      <c r="B109" s="71"/>
       <c r="C109" s="37" t="s">
         <v>19</v>
       </c>
@@ -3602,6 +3605,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="B72:B83"/>
     <mergeCell ref="B85:B96"/>
     <mergeCell ref="B98:B109"/>
@@ -3610,15 +3618,13 @@
     <mergeCell ref="B33:B44"/>
     <mergeCell ref="B46:B57"/>
     <mergeCell ref="B59:B70"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G70" r:id="rId1" xr:uid="{9F46544A-29C9-47B0-BCDD-EE396CAA67D7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3637,19 +3643,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="70"/>
+      <c r="C3" s="77"/>
       <c r="D3" s="79" t="s">
         <v>6</v>
       </c>
@@ -3657,10 +3663,10 @@
       <c r="F3" s="81"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="70"/>
+      <c r="C4" s="77"/>
       <c r="D4" s="79" t="s">
         <v>8</v>
       </c>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794C0133-FE17-4225-A9D9-1B057B3A9471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015EA9FF-A256-44AD-B665-48C636C3FED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MM-LİNKLER" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="312">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -981,9 +981,6 @@
     <t>GeoMatik2D</t>
   </si>
   <si>
-    <t>GeomMatik3D</t>
-  </si>
-  <si>
     <t>T1: 34, 40, 42
 T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81
 T3: 99, 100, 101, 107, 112, 115
@@ -992,6 +989,18 @@
 T6:
 T7:
 T8:</t>
+  </si>
+  <si>
+    <t>GeoMatik3D</t>
+  </si>
+  <si>
+    <t>avCELL</t>
+  </si>
+  <si>
+    <t>avcell_mk</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=0e5aa0333fdcff9dff7e9dec4b39269a&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
 </sst>
 </file>
@@ -1549,6 +1558,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1570,15 +1591,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1587,9 +1599,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1887,41 +1896,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="78" t="s">
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="78" t="s">
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="21"/>
@@ -1956,7 +1965,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="79" t="s">
         <v>153</v>
       </c>
       <c r="C7" s="59" t="s">
@@ -1977,7 +1986,7 @@
       <c r="H7" s="63"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="73"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="50" t="s">
         <v>2</v>
       </c>
@@ -1998,7 +2007,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="73"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="50" t="s">
         <v>9</v>
       </c>
@@ -2019,12 +2028,12 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="73"/>
+      <c r="B10" s="77"/>
       <c r="C10" s="50" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>306</v>
@@ -2040,7 +2049,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="73"/>
+      <c r="B11" s="77"/>
       <c r="C11" s="50" t="s">
         <v>11</v>
       </c>
@@ -2061,7 +2070,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="73"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="50" t="s">
         <v>12</v>
       </c>
@@ -2082,7 +2091,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="73"/>
+      <c r="B13" s="77"/>
       <c r="C13" s="50" t="s">
         <v>13</v>
       </c>
@@ -2103,20 +2112,20 @@
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="73"/>
+      <c r="B14" s="77"/>
       <c r="C14" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="45" t="s">
         <v>167</v>
       </c>
       <c r="H14" s="28"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="73"/>
+      <c r="B15" s="77"/>
       <c r="C15" s="50" t="s">
         <v>15</v>
       </c>
@@ -2137,7 +2146,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="73"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="50" t="s">
         <v>16</v>
       </c>
@@ -2158,20 +2167,20 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="73"/>
+      <c r="B17" s="77"/>
       <c r="C17" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
       <c r="G17" s="45" t="s">
         <v>170</v>
       </c>
       <c r="H17" s="28"/>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="74"/>
+      <c r="B18" s="78"/>
       <c r="C18" s="51" t="s">
         <v>19</v>
       </c>
@@ -2193,7 +2202,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="73" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="53" t="s">
@@ -2214,7 +2223,7 @@
       <c r="H20" s="34"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="70"/>
+      <c r="B21" s="74"/>
       <c r="C21" s="50" t="s">
         <v>2</v>
       </c>
@@ -2235,7 +2244,7 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="70"/>
+      <c r="B22" s="74"/>
       <c r="C22" s="50" t="s">
         <v>9</v>
       </c>
@@ -2256,38 +2265,38 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="70"/>
+      <c r="B23" s="74"/>
       <c r="C23" s="18" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="48" t="s">
         <v>174</v>
       </c>
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="70"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="18" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="48" t="s">
         <v>175</v>
       </c>
       <c r="H24" s="36"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="70"/>
+      <c r="B25" s="74"/>
       <c r="C25" s="18" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="E25" s="20"/>
       <c r="F25" s="20"/>
       <c r="G25" s="48" t="s">
         <v>176</v>
@@ -2295,33 +2304,33 @@
       <c r="H25" s="36"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="70"/>
+      <c r="B26" s="74"/>
       <c r="C26" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="48" t="s">
         <v>177</v>
       </c>
       <c r="H26" s="36"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="70"/>
+      <c r="B27" s="74"/>
       <c r="C27" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
       <c r="G27" s="48" t="s">
         <v>178</v>
       </c>
       <c r="H27" s="36"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="70"/>
+      <c r="B28" s="74"/>
       <c r="C28" s="50" t="s">
         <v>15</v>
       </c>
@@ -2342,12 +2351,12 @@
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="70"/>
+      <c r="B29" s="74"/>
       <c r="C29" s="18" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="E29" s="20"/>
       <c r="F29" s="20"/>
       <c r="G29" s="48" t="s">
         <v>180</v>
@@ -2355,12 +2364,12 @@
       <c r="H29" s="36"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="70"/>
+      <c r="B30" s="74"/>
       <c r="C30" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="E30" s="20"/>
       <c r="F30" s="20"/>
       <c r="G30" s="48" t="s">
         <v>181</v>
@@ -2368,7 +2377,7 @@
       <c r="H30" s="36"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="71"/>
+      <c r="B31" s="75"/>
       <c r="C31" s="51" t="s">
         <v>19</v>
       </c>
@@ -2393,7 +2402,7 @@
       <c r="H32" s="56"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="72" t="s">
+      <c r="B33" s="76" t="s">
         <v>155</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -2414,7 +2423,7 @@
       <c r="H33" s="40"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="73"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="15" t="s">
         <v>2</v>
       </c>
@@ -2435,7 +2444,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="73"/>
+      <c r="B35" s="77"/>
       <c r="C35" s="15" t="s">
         <v>9</v>
       </c>
@@ -2456,38 +2465,38 @@
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="73"/>
+      <c r="B36" s="77"/>
       <c r="C36" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
       <c r="G36" s="45" t="s">
         <v>185</v>
       </c>
       <c r="H36" s="28"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="73"/>
+      <c r="B37" s="77"/>
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
       <c r="G37" s="45" t="s">
         <v>186</v>
       </c>
       <c r="H37" s="41"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="73"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
+      <c r="E38" s="17"/>
       <c r="F38" s="17"/>
       <c r="G38" s="45" t="s">
         <v>187</v>
@@ -2495,12 +2504,12 @@
       <c r="H38" s="41"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="73"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
+      <c r="E39" s="17"/>
       <c r="F39" s="17"/>
       <c r="G39" s="45" t="s">
         <v>188</v>
@@ -2508,20 +2517,20 @@
       <c r="H39" s="41"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="73"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
       <c r="G40" s="45" t="s">
         <v>189</v>
       </c>
       <c r="H40" s="41"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="73"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="15" t="s">
         <v>15</v>
       </c>
@@ -2542,12 +2551,12 @@
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="73"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
+      <c r="E42" s="17"/>
       <c r="F42" s="17"/>
       <c r="G42" s="45" t="s">
         <v>191</v>
@@ -2555,12 +2564,12 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="73"/>
+      <c r="B43" s="77"/>
       <c r="C43" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
+      <c r="E43" s="17"/>
       <c r="F43" s="17"/>
       <c r="G43" s="45" t="s">
         <v>192</v>
@@ -2568,7 +2577,7 @@
       <c r="H43" s="41"/>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="74"/>
+      <c r="B44" s="78"/>
       <c r="C44" s="29" t="s">
         <v>19</v>
       </c>
@@ -2593,7 +2602,7 @@
       <c r="H45" s="57"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="73" t="s">
         <v>156</v>
       </c>
       <c r="C46" s="32" t="s">
@@ -2614,7 +2623,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="70"/>
+      <c r="B47" s="74"/>
       <c r="C47" s="18" t="s">
         <v>2</v>
       </c>
@@ -2635,7 +2644,7 @@
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="70"/>
+      <c r="B48" s="74"/>
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
@@ -2656,7 +2665,7 @@
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="70"/>
+      <c r="B49" s="74"/>
       <c r="C49" s="18" t="s">
         <v>10</v>
       </c>
@@ -2664,7 +2673,7 @@
         <v>88</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>258</v>
@@ -2677,25 +2686,25 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="70"/>
+      <c r="B50" s="74"/>
       <c r="C50" s="18" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
       <c r="G50" s="48" t="s">
         <v>197</v>
       </c>
       <c r="H50" s="35"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="70"/>
+      <c r="B51" s="74"/>
       <c r="C51" s="18" t="s">
         <v>12</v>
       </c>
       <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
+      <c r="E51" s="20"/>
       <c r="F51" s="20"/>
       <c r="G51" s="48" t="s">
         <v>198</v>
@@ -2703,12 +2712,12 @@
       <c r="H51" s="35"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="70"/>
+      <c r="B52" s="74"/>
       <c r="C52" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
+      <c r="E52" s="20"/>
       <c r="F52" s="20"/>
       <c r="G52" s="48" t="s">
         <v>199</v>
@@ -2716,20 +2725,20 @@
       <c r="H52" s="35"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="70"/>
+      <c r="B53" s="74"/>
       <c r="C53" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
       <c r="G53" s="48" t="s">
         <v>200</v>
       </c>
       <c r="H53" s="35"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="70"/>
+      <c r="B54" s="74"/>
       <c r="C54" s="18" t="s">
         <v>15</v>
       </c>
@@ -2750,12 +2759,12 @@
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="70"/>
+      <c r="B55" s="74"/>
       <c r="C55" s="18" t="s">
         <v>16</v>
       </c>
       <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
+      <c r="E55" s="20"/>
       <c r="F55" s="20"/>
       <c r="G55" s="48" t="s">
         <v>202</v>
@@ -2763,12 +2772,12 @@
       <c r="H55" s="35"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="70"/>
+      <c r="B56" s="74"/>
       <c r="C56" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
+      <c r="E56" s="20"/>
       <c r="F56" s="20"/>
       <c r="G56" s="48" t="s">
         <v>203</v>
@@ -2776,7 +2785,7 @@
       <c r="H56" s="35"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="71"/>
+      <c r="B57" s="75"/>
       <c r="C57" s="37" t="s">
         <v>19</v>
       </c>
@@ -2801,7 +2810,7 @@
       <c r="H58" s="58"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="72" t="s">
+      <c r="B59" s="76" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="25" t="s">
@@ -2822,7 +2831,7 @@
       <c r="H59" s="40"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="73"/>
+      <c r="B60" s="77"/>
       <c r="C60" s="15" t="s">
         <v>2</v>
       </c>
@@ -2843,7 +2852,7 @@
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="73"/>
+      <c r="B61" s="77"/>
       <c r="C61" s="15" t="s">
         <v>9</v>
       </c>
@@ -2864,38 +2873,38 @@
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="73"/>
+      <c r="B62" s="77"/>
       <c r="C62" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
       <c r="G62" s="45" t="s">
         <v>207</v>
       </c>
       <c r="H62" s="41"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="73"/>
+      <c r="B63" s="77"/>
       <c r="C63" s="15" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
       <c r="G63" s="45" t="s">
         <v>208</v>
       </c>
       <c r="H63" s="41"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="73"/>
+      <c r="B64" s="77"/>
       <c r="C64" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
+      <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="45" t="s">
         <v>209</v>
@@ -2903,12 +2912,12 @@
       <c r="H64" s="41"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="73"/>
+      <c r="B65" s="77"/>
       <c r="C65" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
+      <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="45" t="s">
         <v>210</v>
@@ -2916,20 +2925,20 @@
       <c r="H65" s="41"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="73"/>
+      <c r="B66" s="77"/>
       <c r="C66" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
       <c r="G66" s="45" t="s">
         <v>211</v>
       </c>
       <c r="H66" s="41"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="73"/>
+      <c r="B67" s="77"/>
       <c r="C67" s="15" t="s">
         <v>15</v>
       </c>
@@ -2950,12 +2959,12 @@
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="73"/>
+      <c r="B68" s="77"/>
       <c r="C68" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
+      <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="45" t="s">
         <v>213</v>
@@ -2963,12 +2972,12 @@
       <c r="H68" s="41"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="73"/>
+      <c r="B69" s="77"/>
       <c r="C69" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
+      <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="45" t="s">
         <v>214</v>
@@ -2976,7 +2985,7 @@
       <c r="H69" s="41"/>
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="74"/>
+      <c r="B70" s="78"/>
       <c r="C70" s="29" t="s">
         <v>19</v>
       </c>
@@ -2989,7 +2998,7 @@
       <c r="F70" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="82" t="s">
+      <c r="G70" s="69" t="s">
         <v>215</v>
       </c>
       <c r="H70" s="31" t="s">
@@ -3001,7 +3010,7 @@
       <c r="H71" s="58"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="69" t="s">
+      <c r="B72" s="73" t="s">
         <v>158</v>
       </c>
       <c r="C72" s="32" t="s">
@@ -3022,7 +3031,7 @@
       <c r="H72" s="34"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="70"/>
+      <c r="B73" s="74"/>
       <c r="C73" s="18" t="s">
         <v>2</v>
       </c>
@@ -3043,7 +3052,7 @@
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="70"/>
+      <c r="B74" s="74"/>
       <c r="C74" s="18" t="s">
         <v>9</v>
       </c>
@@ -3064,7 +3073,7 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="70"/>
+      <c r="B75" s="74"/>
       <c r="C75" s="18" t="s">
         <v>10</v>
       </c>
@@ -3085,38 +3094,38 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="70"/>
+      <c r="B76" s="74"/>
       <c r="C76" s="18" t="s">
         <v>11</v>
       </c>
       <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
       <c r="G76" s="48" t="s">
         <v>219</v>
       </c>
       <c r="H76" s="35"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="70"/>
+      <c r="B77" s="74"/>
       <c r="C77" s="18" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
       <c r="G77" s="48" t="s">
         <v>220</v>
       </c>
       <c r="H77" s="35"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="70"/>
+      <c r="B78" s="74"/>
       <c r="C78" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
+      <c r="E78" s="20"/>
       <c r="F78" s="20"/>
       <c r="G78" s="48" t="s">
         <v>221</v>
@@ -3124,20 +3133,20 @@
       <c r="H78" s="35"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="70"/>
+      <c r="B79" s="74"/>
       <c r="C79" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
       <c r="G79" s="48" t="s">
         <v>222</v>
       </c>
       <c r="H79" s="35"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="70"/>
+      <c r="B80" s="74"/>
       <c r="C80" s="18" t="s">
         <v>15</v>
       </c>
@@ -3158,12 +3167,12 @@
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="70"/>
+      <c r="B81" s="74"/>
       <c r="C81" s="18" t="s">
         <v>16</v>
       </c>
       <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
+      <c r="E81" s="20"/>
       <c r="F81" s="20"/>
       <c r="G81" s="48" t="s">
         <v>224</v>
@@ -3171,12 +3180,12 @@
       <c r="H81" s="35"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="70"/>
+      <c r="B82" s="74"/>
       <c r="C82" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
+      <c r="E82" s="20"/>
       <c r="F82" s="20"/>
       <c r="G82" s="48" t="s">
         <v>225</v>
@@ -3184,7 +3193,7 @@
       <c r="H82" s="35"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="71"/>
+      <c r="B83" s="75"/>
       <c r="C83" s="37" t="s">
         <v>19</v>
       </c>
@@ -3208,7 +3217,7 @@
       <c r="H84" s="58"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="72" t="s">
+      <c r="B85" s="76" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="25" t="s">
@@ -3229,7 +3238,7 @@
       <c r="H85" s="40"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="73"/>
+      <c r="B86" s="77"/>
       <c r="C86" s="15" t="s">
         <v>2</v>
       </c>
@@ -3250,7 +3259,7 @@
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="73"/>
+      <c r="B87" s="77"/>
       <c r="C87" s="15" t="s">
         <v>9</v>
       </c>
@@ -3271,38 +3280,38 @@
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="73"/>
+      <c r="B88" s="77"/>
       <c r="C88" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="15"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
       <c r="G88" s="45" t="s">
         <v>229</v>
       </c>
       <c r="H88" s="41"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="73"/>
+      <c r="B89" s="77"/>
       <c r="C89" s="15" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
       <c r="G89" s="45" t="s">
         <v>230</v>
       </c>
       <c r="H89" s="28"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" s="73"/>
+      <c r="B90" s="77"/>
       <c r="C90" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
+      <c r="E90" s="17"/>
       <c r="F90" s="17"/>
       <c r="G90" s="45" t="s">
         <v>231</v>
@@ -3310,12 +3319,12 @@
       <c r="H90" s="28"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="73"/>
+      <c r="B91" s="77"/>
       <c r="C91" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
+      <c r="E91" s="17"/>
       <c r="F91" s="17"/>
       <c r="G91" s="45" t="s">
         <v>232</v>
@@ -3323,20 +3332,20 @@
       <c r="H91" s="28"/>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="73"/>
+      <c r="B92" s="77"/>
       <c r="C92" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
       <c r="G92" s="45" t="s">
         <v>233</v>
       </c>
       <c r="H92" s="28"/>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="73"/>
+      <c r="B93" s="77"/>
       <c r="C93" s="15" t="s">
         <v>15</v>
       </c>
@@ -3357,12 +3366,12 @@
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="73"/>
+      <c r="B94" s="77"/>
       <c r="C94" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
+      <c r="E94" s="17"/>
       <c r="F94" s="17"/>
       <c r="G94" s="45" t="s">
         <v>235</v>
@@ -3370,12 +3379,12 @@
       <c r="H94" s="28"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="73"/>
+      <c r="B95" s="77"/>
       <c r="C95" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
+      <c r="E95" s="17"/>
       <c r="F95" s="17"/>
       <c r="G95" s="45" t="s">
         <v>236</v>
@@ -3383,7 +3392,7 @@
       <c r="H95" s="28"/>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="74"/>
+      <c r="B96" s="78"/>
       <c r="C96" s="29" t="s">
         <v>19</v>
       </c>
@@ -3408,7 +3417,7 @@
       <c r="H97" s="56"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="69" t="s">
+      <c r="B98" s="73" t="s">
         <v>160</v>
       </c>
       <c r="C98" s="32" t="s">
@@ -3429,7 +3438,7 @@
       <c r="H98" s="43"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="70"/>
+      <c r="B99" s="74"/>
       <c r="C99" s="18" t="s">
         <v>2</v>
       </c>
@@ -3450,7 +3459,7 @@
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="70"/>
+      <c r="B100" s="74"/>
       <c r="C100" s="18" t="s">
         <v>9</v>
       </c>
@@ -3471,38 +3480,46 @@
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="70"/>
+      <c r="B101" s="74"/>
       <c r="C101" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D101" s="18"/>
-      <c r="E101" s="18"/>
-      <c r="F101" s="18"/>
+      <c r="D101" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>310</v>
+      </c>
       <c r="G101" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="H101" s="36"/>
+      <c r="H101" s="36" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="70"/>
+      <c r="B102" s="74"/>
       <c r="C102" s="18" t="s">
         <v>11</v>
       </c>
       <c r="D102" s="18"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="20"/>
       <c r="G102" s="48" t="s">
         <v>241</v>
       </c>
       <c r="H102" s="36"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="70"/>
+      <c r="B103" s="74"/>
       <c r="C103" s="18" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="18"/>
-      <c r="E103" s="18"/>
+      <c r="E103" s="20"/>
       <c r="F103" s="20"/>
       <c r="G103" s="48" t="s">
         <v>242</v>
@@ -3510,12 +3527,12 @@
       <c r="H103" s="36"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="70"/>
+      <c r="B104" s="74"/>
       <c r="C104" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D104" s="18"/>
-      <c r="E104" s="18"/>
+      <c r="E104" s="20"/>
       <c r="F104" s="20"/>
       <c r="G104" s="48" t="s">
         <v>243</v>
@@ -3523,20 +3540,20 @@
       <c r="H104" s="36"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="70"/>
+      <c r="B105" s="74"/>
       <c r="C105" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="18"/>
+      <c r="E105" s="20"/>
+      <c r="F105" s="20"/>
       <c r="G105" s="48" t="s">
         <v>244</v>
       </c>
       <c r="H105" s="36"/>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="70"/>
+      <c r="B106" s="74"/>
       <c r="C106" s="18" t="s">
         <v>15</v>
       </c>
@@ -3557,12 +3574,12 @@
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="70"/>
+      <c r="B107" s="74"/>
       <c r="C107" s="18" t="s">
         <v>16</v>
       </c>
       <c r="D107" s="18"/>
-      <c r="E107" s="18"/>
+      <c r="E107" s="20"/>
       <c r="F107" s="20"/>
       <c r="G107" s="48" t="s">
         <v>246</v>
@@ -3570,12 +3587,12 @@
       <c r="H107" s="36"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="70"/>
+      <c r="B108" s="74"/>
       <c r="C108" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D108" s="18"/>
-      <c r="E108" s="18"/>
+      <c r="E108" s="20"/>
       <c r="F108" s="20"/>
       <c r="G108" s="48" t="s">
         <v>247</v>
@@ -3583,7 +3600,7 @@
       <c r="H108" s="36"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="71"/>
+      <c r="B109" s="75"/>
       <c r="C109" s="37" t="s">
         <v>19</v>
       </c>
@@ -3605,11 +3622,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="B72:B83"/>
     <mergeCell ref="B85:B96"/>
     <mergeCell ref="B98:B109"/>
@@ -3618,6 +3630,11 @@
     <mergeCell ref="B33:B44"/>
     <mergeCell ref="B46:B57"/>
     <mergeCell ref="B59:B70"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -3643,35 +3660,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="79" t="s">
+      <c r="C3" s="71"/>
+      <c r="D3" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="80"/>
-      <c r="F3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="82"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="79" t="s">
+      <c r="C4" s="71"/>
+      <c r="D4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="80"/>
-      <c r="F4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="82"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015EA9FF-A256-44AD-B665-48C636C3FED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB23B9B-C3E6-4465-888D-3DC1D3B80185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MM-LİNKLER" sheetId="1" r:id="rId1"/>
@@ -981,26 +981,26 @@
     <t>GeoMatik2D</t>
   </si>
   <si>
+    <t>GeoMatik3D</t>
+  </si>
+  <si>
+    <t>avCELL</t>
+  </si>
+  <si>
+    <t>avcell_mk</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=0e5aa0333fdcff9dff7e9dec4b39269a&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
     <t>T1: 34, 40, 42
 T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81
 T3: 99, 100, 101, 107, 112, 115
 T4:
-T5:165, 170, 171, 177, 179, 181, 193
+T5: 165, 170, 177, 179, 181, 193
 T6:
 T7:
 T8:</t>
-  </si>
-  <si>
-    <t>GeoMatik3D</t>
-  </si>
-  <si>
-    <t>avCELL</t>
-  </si>
-  <si>
-    <t>avcell_mk</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=0e5aa0333fdcff9dff7e9dec4b39269a&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
 </sst>
 </file>
@@ -1561,6 +1561,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1569,27 +1590,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1896,41 +1896,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72" t="s">
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="72" t="s">
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="21"/>
@@ -1965,7 +1965,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="76" t="s">
         <v>153</v>
       </c>
       <c r="C7" s="59" t="s">
@@ -1986,7 +1986,7 @@
       <c r="H7" s="63"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="77"/>
+      <c r="B8" s="74"/>
       <c r="C8" s="50" t="s">
         <v>2</v>
       </c>
@@ -2007,7 +2007,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="77"/>
+      <c r="B9" s="74"/>
       <c r="C9" s="50" t="s">
         <v>9</v>
       </c>
@@ -2028,12 +2028,12 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="77"/>
+      <c r="B10" s="74"/>
       <c r="C10" s="50" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>306</v>
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="77"/>
+      <c r="B11" s="74"/>
       <c r="C11" s="50" t="s">
         <v>11</v>
       </c>
@@ -2070,7 +2070,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="77"/>
+      <c r="B12" s="74"/>
       <c r="C12" s="50" t="s">
         <v>12</v>
       </c>
@@ -2091,7 +2091,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="77"/>
+      <c r="B13" s="74"/>
       <c r="C13" s="50" t="s">
         <v>13</v>
       </c>
@@ -2112,7 +2112,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="77"/>
+      <c r="B14" s="74"/>
       <c r="C14" s="15" t="s">
         <v>14</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="H14" s="28"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="77"/>
+      <c r="B15" s="74"/>
       <c r="C15" s="50" t="s">
         <v>15</v>
       </c>
@@ -2146,7 +2146,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="77"/>
+      <c r="B16" s="74"/>
       <c r="C16" s="50" t="s">
         <v>16</v>
       </c>
@@ -2167,7 +2167,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="77"/>
+      <c r="B17" s="74"/>
       <c r="C17" s="15" t="s">
         <v>18</v>
       </c>
@@ -2180,7 +2180,7 @@
       <c r="H17" s="28"/>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="78"/>
+      <c r="B18" s="75"/>
       <c r="C18" s="51" t="s">
         <v>19</v>
       </c>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="73" t="s">
+      <c r="B20" s="70" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="53" t="s">
@@ -2223,7 +2223,7 @@
       <c r="H20" s="34"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="74"/>
+      <c r="B21" s="71"/>
       <c r="C21" s="50" t="s">
         <v>2</v>
       </c>
@@ -2244,7 +2244,7 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="74"/>
+      <c r="B22" s="71"/>
       <c r="C22" s="50" t="s">
         <v>9</v>
       </c>
@@ -2265,7 +2265,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="74"/>
+      <c r="B23" s="71"/>
       <c r="C23" s="18" t="s">
         <v>10</v>
       </c>
@@ -2278,7 +2278,7 @@
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="74"/>
+      <c r="B24" s="71"/>
       <c r="C24" s="18" t="s">
         <v>11</v>
       </c>
@@ -2291,7 +2291,7 @@
       <c r="H24" s="36"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="74"/>
+      <c r="B25" s="71"/>
       <c r="C25" s="18" t="s">
         <v>12</v>
       </c>
@@ -2304,7 +2304,7 @@
       <c r="H25" s="36"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="74"/>
+      <c r="B26" s="71"/>
       <c r="C26" s="18" t="s">
         <v>13</v>
       </c>
@@ -2317,7 +2317,7 @@
       <c r="H26" s="36"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="74"/>
+      <c r="B27" s="71"/>
       <c r="C27" s="18" t="s">
         <v>14</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="H27" s="36"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="74"/>
+      <c r="B28" s="71"/>
       <c r="C28" s="50" t="s">
         <v>15</v>
       </c>
@@ -2351,7 +2351,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="74"/>
+      <c r="B29" s="71"/>
       <c r="C29" s="18" t="s">
         <v>16</v>
       </c>
@@ -2364,7 +2364,7 @@
       <c r="H29" s="36"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="74"/>
+      <c r="B30" s="71"/>
       <c r="C30" s="18" t="s">
         <v>18</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="H30" s="36"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="75"/>
+      <c r="B31" s="72"/>
       <c r="C31" s="51" t="s">
         <v>19</v>
       </c>
@@ -2402,7 +2402,7 @@
       <c r="H32" s="56"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="76" t="s">
+      <c r="B33" s="73" t="s">
         <v>155</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -2423,7 +2423,7 @@
       <c r="H33" s="40"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="77"/>
+      <c r="B34" s="74"/>
       <c r="C34" s="15" t="s">
         <v>2</v>
       </c>
@@ -2444,7 +2444,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="77"/>
+      <c r="B35" s="74"/>
       <c r="C35" s="15" t="s">
         <v>9</v>
       </c>
@@ -2465,7 +2465,7 @@
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="77"/>
+      <c r="B36" s="74"/>
       <c r="C36" s="15" t="s">
         <v>10</v>
       </c>
@@ -2478,7 +2478,7 @@
       <c r="H36" s="28"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="77"/>
+      <c r="B37" s="74"/>
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
@@ -2491,7 +2491,7 @@
       <c r="H37" s="41"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="77"/>
+      <c r="B38" s="74"/>
       <c r="C38" s="15" t="s">
         <v>12</v>
       </c>
@@ -2504,7 +2504,7 @@
       <c r="H38" s="41"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="77"/>
+      <c r="B39" s="74"/>
       <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
@@ -2517,7 +2517,7 @@
       <c r="H39" s="41"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="77"/>
+      <c r="B40" s="74"/>
       <c r="C40" s="15" t="s">
         <v>14</v>
       </c>
@@ -2530,7 +2530,7 @@
       <c r="H40" s="41"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="77"/>
+      <c r="B41" s="74"/>
       <c r="C41" s="15" t="s">
         <v>15</v>
       </c>
@@ -2551,7 +2551,7 @@
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="77"/>
+      <c r="B42" s="74"/>
       <c r="C42" s="15" t="s">
         <v>16</v>
       </c>
@@ -2564,7 +2564,7 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="77"/>
+      <c r="B43" s="74"/>
       <c r="C43" s="15" t="s">
         <v>18</v>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="H43" s="41"/>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="78"/>
+      <c r="B44" s="75"/>
       <c r="C44" s="29" t="s">
         <v>19</v>
       </c>
@@ -2602,7 +2602,7 @@
       <c r="H45" s="57"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="73" t="s">
+      <c r="B46" s="70" t="s">
         <v>156</v>
       </c>
       <c r="C46" s="32" t="s">
@@ -2623,7 +2623,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="74"/>
+      <c r="B47" s="71"/>
       <c r="C47" s="18" t="s">
         <v>2</v>
       </c>
@@ -2644,7 +2644,7 @@
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="74"/>
+      <c r="B48" s="71"/>
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="74"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="18" t="s">
         <v>10</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>88</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>258</v>
@@ -2686,7 +2686,7 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="74"/>
+      <c r="B50" s="71"/>
       <c r="C50" s="18" t="s">
         <v>11</v>
       </c>
@@ -2699,7 +2699,7 @@
       <c r="H50" s="35"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="74"/>
+      <c r="B51" s="71"/>
       <c r="C51" s="18" t="s">
         <v>12</v>
       </c>
@@ -2712,7 +2712,7 @@
       <c r="H51" s="35"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="74"/>
+      <c r="B52" s="71"/>
       <c r="C52" s="18" t="s">
         <v>13</v>
       </c>
@@ -2725,7 +2725,7 @@
       <c r="H52" s="35"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="74"/>
+      <c r="B53" s="71"/>
       <c r="C53" s="18" t="s">
         <v>14</v>
       </c>
@@ -2738,7 +2738,7 @@
       <c r="H53" s="35"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="74"/>
+      <c r="B54" s="71"/>
       <c r="C54" s="18" t="s">
         <v>15</v>
       </c>
@@ -2759,7 +2759,7 @@
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="74"/>
+      <c r="B55" s="71"/>
       <c r="C55" s="18" t="s">
         <v>16</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="H55" s="35"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="74"/>
+      <c r="B56" s="71"/>
       <c r="C56" s="18" t="s">
         <v>18</v>
       </c>
@@ -2785,7 +2785,7 @@
       <c r="H56" s="35"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="75"/>
+      <c r="B57" s="72"/>
       <c r="C57" s="37" t="s">
         <v>19</v>
       </c>
@@ -2810,7 +2810,7 @@
       <c r="H58" s="58"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="76" t="s">
+      <c r="B59" s="73" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="25" t="s">
@@ -2831,7 +2831,7 @@
       <c r="H59" s="40"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="77"/>
+      <c r="B60" s="74"/>
       <c r="C60" s="15" t="s">
         <v>2</v>
       </c>
@@ -2852,7 +2852,7 @@
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="77"/>
+      <c r="B61" s="74"/>
       <c r="C61" s="15" t="s">
         <v>9</v>
       </c>
@@ -2873,7 +2873,7 @@
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="77"/>
+      <c r="B62" s="74"/>
       <c r="C62" s="15" t="s">
         <v>10</v>
       </c>
@@ -2886,7 +2886,7 @@
       <c r="H62" s="41"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="77"/>
+      <c r="B63" s="74"/>
       <c r="C63" s="15" t="s">
         <v>11</v>
       </c>
@@ -2899,7 +2899,7 @@
       <c r="H63" s="41"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="77"/>
+      <c r="B64" s="74"/>
       <c r="C64" s="15" t="s">
         <v>12</v>
       </c>
@@ -2912,7 +2912,7 @@
       <c r="H64" s="41"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="77"/>
+      <c r="B65" s="74"/>
       <c r="C65" s="15" t="s">
         <v>13</v>
       </c>
@@ -2925,7 +2925,7 @@
       <c r="H65" s="41"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="77"/>
+      <c r="B66" s="74"/>
       <c r="C66" s="15" t="s">
         <v>14</v>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="H66" s="41"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="77"/>
+      <c r="B67" s="74"/>
       <c r="C67" s="15" t="s">
         <v>15</v>
       </c>
@@ -2959,7 +2959,7 @@
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="77"/>
+      <c r="B68" s="74"/>
       <c r="C68" s="15" t="s">
         <v>16</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="H68" s="41"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="77"/>
+      <c r="B69" s="74"/>
       <c r="C69" s="15" t="s">
         <v>18</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="H69" s="41"/>
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="78"/>
+      <c r="B70" s="75"/>
       <c r="C70" s="29" t="s">
         <v>19</v>
       </c>
@@ -3010,7 +3010,7 @@
       <c r="H71" s="58"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="73" t="s">
+      <c r="B72" s="70" t="s">
         <v>158</v>
       </c>
       <c r="C72" s="32" t="s">
@@ -3031,7 +3031,7 @@
       <c r="H72" s="34"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="74"/>
+      <c r="B73" s="71"/>
       <c r="C73" s="18" t="s">
         <v>2</v>
       </c>
@@ -3052,7 +3052,7 @@
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="74"/>
+      <c r="B74" s="71"/>
       <c r="C74" s="18" t="s">
         <v>9</v>
       </c>
@@ -3073,7 +3073,7 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="74"/>
+      <c r="B75" s="71"/>
       <c r="C75" s="18" t="s">
         <v>10</v>
       </c>
@@ -3094,7 +3094,7 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="74"/>
+      <c r="B76" s="71"/>
       <c r="C76" s="18" t="s">
         <v>11</v>
       </c>
@@ -3107,7 +3107,7 @@
       <c r="H76" s="35"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="74"/>
+      <c r="B77" s="71"/>
       <c r="C77" s="18" t="s">
         <v>12</v>
       </c>
@@ -3120,7 +3120,7 @@
       <c r="H77" s="35"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="74"/>
+      <c r="B78" s="71"/>
       <c r="C78" s="18" t="s">
         <v>13</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="H78" s="35"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="74"/>
+      <c r="B79" s="71"/>
       <c r="C79" s="18" t="s">
         <v>14</v>
       </c>
@@ -3146,7 +3146,7 @@
       <c r="H79" s="35"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="74"/>
+      <c r="B80" s="71"/>
       <c r="C80" s="18" t="s">
         <v>15</v>
       </c>
@@ -3167,7 +3167,7 @@
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="74"/>
+      <c r="B81" s="71"/>
       <c r="C81" s="18" t="s">
         <v>16</v>
       </c>
@@ -3180,7 +3180,7 @@
       <c r="H81" s="35"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="74"/>
+      <c r="B82" s="71"/>
       <c r="C82" s="18" t="s">
         <v>18</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="H82" s="35"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="75"/>
+      <c r="B83" s="72"/>
       <c r="C83" s="37" t="s">
         <v>19</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="H84" s="58"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="76" t="s">
+      <c r="B85" s="73" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="25" t="s">
@@ -3238,7 +3238,7 @@
       <c r="H85" s="40"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="77"/>
+      <c r="B86" s="74"/>
       <c r="C86" s="15" t="s">
         <v>2</v>
       </c>
@@ -3259,7 +3259,7 @@
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="77"/>
+      <c r="B87" s="74"/>
       <c r="C87" s="15" t="s">
         <v>9</v>
       </c>
@@ -3280,7 +3280,7 @@
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="77"/>
+      <c r="B88" s="74"/>
       <c r="C88" s="15" t="s">
         <v>10</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="H88" s="41"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="77"/>
+      <c r="B89" s="74"/>
       <c r="C89" s="15" t="s">
         <v>11</v>
       </c>
@@ -3306,7 +3306,7 @@
       <c r="H89" s="28"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" s="77"/>
+      <c r="B90" s="74"/>
       <c r="C90" s="15" t="s">
         <v>12</v>
       </c>
@@ -3319,7 +3319,7 @@
       <c r="H90" s="28"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="77"/>
+      <c r="B91" s="74"/>
       <c r="C91" s="15" t="s">
         <v>13</v>
       </c>
@@ -3332,7 +3332,7 @@
       <c r="H91" s="28"/>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="77"/>
+      <c r="B92" s="74"/>
       <c r="C92" s="15" t="s">
         <v>14</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="H92" s="28"/>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="77"/>
+      <c r="B93" s="74"/>
       <c r="C93" s="15" t="s">
         <v>15</v>
       </c>
@@ -3366,7 +3366,7 @@
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="77"/>
+      <c r="B94" s="74"/>
       <c r="C94" s="15" t="s">
         <v>16</v>
       </c>
@@ -3379,7 +3379,7 @@
       <c r="H94" s="28"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="77"/>
+      <c r="B95" s="74"/>
       <c r="C95" s="15" t="s">
         <v>18</v>
       </c>
@@ -3392,7 +3392,7 @@
       <c r="H95" s="28"/>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="78"/>
+      <c r="B96" s="75"/>
       <c r="C96" s="29" t="s">
         <v>19</v>
       </c>
@@ -3417,7 +3417,7 @@
       <c r="H97" s="56"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="73" t="s">
+      <c r="B98" s="70" t="s">
         <v>160</v>
       </c>
       <c r="C98" s="32" t="s">
@@ -3438,7 +3438,7 @@
       <c r="H98" s="43"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="74"/>
+      <c r="B99" s="71"/>
       <c r="C99" s="18" t="s">
         <v>2</v>
       </c>
@@ -3459,7 +3459,7 @@
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="74"/>
+      <c r="B100" s="71"/>
       <c r="C100" s="18" t="s">
         <v>9</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="74"/>
+      <c r="B101" s="71"/>
       <c r="C101" s="18" t="s">
         <v>10</v>
       </c>
@@ -3488,20 +3488,20 @@
         <v>88</v>
       </c>
       <c r="E101" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="F101" s="20" t="s">
         <v>309</v>
-      </c>
-      <c r="F101" s="20" t="s">
-        <v>310</v>
       </c>
       <c r="G101" s="48" t="s">
         <v>240</v>
       </c>
       <c r="H101" s="36" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="74"/>
+      <c r="B102" s="71"/>
       <c r="C102" s="18" t="s">
         <v>11</v>
       </c>
@@ -3514,7 +3514,7 @@
       <c r="H102" s="36"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="74"/>
+      <c r="B103" s="71"/>
       <c r="C103" s="18" t="s">
         <v>12</v>
       </c>
@@ -3527,7 +3527,7 @@
       <c r="H103" s="36"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="74"/>
+      <c r="B104" s="71"/>
       <c r="C104" s="18" t="s">
         <v>13</v>
       </c>
@@ -3540,7 +3540,7 @@
       <c r="H104" s="36"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="74"/>
+      <c r="B105" s="71"/>
       <c r="C105" s="18" t="s">
         <v>14</v>
       </c>
@@ -3553,7 +3553,7 @@
       <c r="H105" s="36"/>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="74"/>
+      <c r="B106" s="71"/>
       <c r="C106" s="18" t="s">
         <v>15</v>
       </c>
@@ -3574,7 +3574,7 @@
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="74"/>
+      <c r="B107" s="71"/>
       <c r="C107" s="18" t="s">
         <v>16</v>
       </c>
@@ -3587,7 +3587,7 @@
       <c r="H107" s="36"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="74"/>
+      <c r="B108" s="71"/>
       <c r="C108" s="18" t="s">
         <v>18</v>
       </c>
@@ -3600,7 +3600,7 @@
       <c r="H108" s="36"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="75"/>
+      <c r="B109" s="72"/>
       <c r="C109" s="37" t="s">
         <v>19</v>
       </c>
@@ -3622,6 +3622,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="B72:B83"/>
     <mergeCell ref="B85:B96"/>
     <mergeCell ref="B98:B109"/>
@@ -3630,11 +3635,6 @@
     <mergeCell ref="B33:B44"/>
     <mergeCell ref="B46:B57"/>
     <mergeCell ref="B59:B70"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -3660,19 +3660,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="71"/>
+      <c r="C3" s="78"/>
       <c r="D3" s="80" t="s">
         <v>6</v>
       </c>
@@ -3680,10 +3680,10 @@
       <c r="F3" s="82"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="71"/>
+      <c r="C4" s="78"/>
       <c r="D4" s="80" t="s">
         <v>8</v>
       </c>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB23B9B-C3E6-4465-888D-3DC1D3B80185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BA29E5-AD45-434B-8B32-32DDB01B9D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MM-LİNKLER" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="318">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -994,13 +994,31 @@
   </si>
   <si>
     <t>T1: 34, 40, 42
-T2: 47, 50, 53, 54, 56, 57, 59, 61, 66, 71, 72,  73, 77, 81
+T2: 48, 52, 56, 57, 59, 60, 61, 63, 64, 66, 67, 72, 73, 74, 76, 83
 T3: 99, 100, 101, 107, 112, 115
 T4:
 T5: 165, 170, 177, 179, 181, 193
-T6:
+T6: 248, 254, 256, 284, 285, 294, 300, 303
 T7:
 T8:</t>
+  </si>
+  <si>
+    <t>Akran 8.1</t>
+  </si>
+  <si>
+    <t>mm_81akran_mk</t>
+  </si>
+  <si>
+    <t>Grup 8.1</t>
+  </si>
+  <si>
+    <t>mm_81grup_mk</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=ad2bcdbe346be64237f6399eb85e4300&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=075d0be38ae0e1bcf74c3aa830d29e1e&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
 </sst>
 </file>
@@ -1561,6 +1579,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1581,15 +1608,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1887,7 +1905,7 @@
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="7.44140625" style="22" customWidth="1"/>
     <col min="3" max="3" width="6.44140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="45.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.44140625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" style="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.21875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36" style="47" customWidth="1"/>
@@ -1896,41 +1914,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="79" t="s">
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="79" t="s">
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="21"/>
@@ -1965,7 +1983,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="79" t="s">
         <v>153</v>
       </c>
       <c r="C7" s="59" t="s">
@@ -1986,7 +2004,7 @@
       <c r="H7" s="63"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="74"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="50" t="s">
         <v>2</v>
       </c>
@@ -2007,7 +2025,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="74"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="50" t="s">
         <v>9</v>
       </c>
@@ -2027,8 +2045,8 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="74"/>
+    <row r="10" spans="2:8" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="77"/>
       <c r="C10" s="50" t="s">
         <v>10</v>
       </c>
@@ -2049,7 +2067,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="74"/>
+      <c r="B11" s="77"/>
       <c r="C11" s="50" t="s">
         <v>11</v>
       </c>
@@ -2070,7 +2088,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="74"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="50" t="s">
         <v>12</v>
       </c>
@@ -2091,7 +2109,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="74"/>
+      <c r="B13" s="77"/>
       <c r="C13" s="50" t="s">
         <v>13</v>
       </c>
@@ -2112,7 +2130,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="74"/>
+      <c r="B14" s="77"/>
       <c r="C14" s="15" t="s">
         <v>14</v>
       </c>
@@ -2125,7 +2143,7 @@
       <c r="H14" s="28"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="74"/>
+      <c r="B15" s="77"/>
       <c r="C15" s="50" t="s">
         <v>15</v>
       </c>
@@ -2146,7 +2164,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="74"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="50" t="s">
         <v>16</v>
       </c>
@@ -2167,7 +2185,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="74"/>
+      <c r="B17" s="77"/>
       <c r="C17" s="15" t="s">
         <v>18</v>
       </c>
@@ -2180,7 +2198,7 @@
       <c r="H17" s="28"/>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="75"/>
+      <c r="B18" s="78"/>
       <c r="C18" s="51" t="s">
         <v>19</v>
       </c>
@@ -2202,7 +2220,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="73" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="53" t="s">
@@ -2223,7 +2241,7 @@
       <c r="H20" s="34"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="71"/>
+      <c r="B21" s="74"/>
       <c r="C21" s="50" t="s">
         <v>2</v>
       </c>
@@ -2244,12 +2262,12 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="71"/>
+      <c r="B22" s="74"/>
       <c r="C22" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="18">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>92</v>
@@ -2265,7 +2283,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="71"/>
+      <c r="B23" s="74"/>
       <c r="C23" s="18" t="s">
         <v>10</v>
       </c>
@@ -2278,7 +2296,7 @@
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="71"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="18" t="s">
         <v>11</v>
       </c>
@@ -2291,7 +2309,7 @@
       <c r="H24" s="36"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="71"/>
+      <c r="B25" s="74"/>
       <c r="C25" s="18" t="s">
         <v>12</v>
       </c>
@@ -2304,7 +2322,7 @@
       <c r="H25" s="36"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="71"/>
+      <c r="B26" s="74"/>
       <c r="C26" s="18" t="s">
         <v>13</v>
       </c>
@@ -2317,7 +2335,7 @@
       <c r="H26" s="36"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="71"/>
+      <c r="B27" s="74"/>
       <c r="C27" s="18" t="s">
         <v>14</v>
       </c>
@@ -2330,12 +2348,12 @@
       <c r="H27" s="36"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="71"/>
+      <c r="B28" s="74"/>
       <c r="C28" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="18">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E28" s="20" t="s">
         <v>93</v>
@@ -2351,7 +2369,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="71"/>
+      <c r="B29" s="74"/>
       <c r="C29" s="18" t="s">
         <v>16</v>
       </c>
@@ -2364,7 +2382,7 @@
       <c r="H29" s="36"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="71"/>
+      <c r="B30" s="74"/>
       <c r="C30" s="18" t="s">
         <v>18</v>
       </c>
@@ -2377,12 +2395,12 @@
       <c r="H30" s="36"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="72"/>
+      <c r="B31" s="75"/>
       <c r="C31" s="51" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="37">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E31" s="38" t="s">
         <v>250</v>
@@ -2402,7 +2420,7 @@
       <c r="H32" s="56"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="73" t="s">
+      <c r="B33" s="76" t="s">
         <v>155</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -2423,7 +2441,7 @@
       <c r="H33" s="40"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="74"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="15" t="s">
         <v>2</v>
       </c>
@@ -2444,7 +2462,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="74"/>
+      <c r="B35" s="77"/>
       <c r="C35" s="15" t="s">
         <v>9</v>
       </c>
@@ -2465,7 +2483,7 @@
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="74"/>
+      <c r="B36" s="77"/>
       <c r="C36" s="15" t="s">
         <v>10</v>
       </c>
@@ -2478,7 +2496,7 @@
       <c r="H36" s="28"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="74"/>
+      <c r="B37" s="77"/>
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
@@ -2491,7 +2509,7 @@
       <c r="H37" s="41"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="74"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="15" t="s">
         <v>12</v>
       </c>
@@ -2504,7 +2522,7 @@
       <c r="H38" s="41"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="74"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
@@ -2517,7 +2535,7 @@
       <c r="H39" s="41"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="74"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="15" t="s">
         <v>14</v>
       </c>
@@ -2530,7 +2548,7 @@
       <c r="H40" s="41"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="74"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="15" t="s">
         <v>15</v>
       </c>
@@ -2551,7 +2569,7 @@
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="74"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="15" t="s">
         <v>16</v>
       </c>
@@ -2564,7 +2582,7 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="74"/>
+      <c r="B43" s="77"/>
       <c r="C43" s="15" t="s">
         <v>18</v>
       </c>
@@ -2577,7 +2595,7 @@
       <c r="H43" s="41"/>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="75"/>
+      <c r="B44" s="78"/>
       <c r="C44" s="29" t="s">
         <v>19</v>
       </c>
@@ -2602,7 +2620,7 @@
       <c r="H45" s="57"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="70" t="s">
+      <c r="B46" s="73" t="s">
         <v>156</v>
       </c>
       <c r="C46" s="32" t="s">
@@ -2623,7 +2641,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="71"/>
+      <c r="B47" s="74"/>
       <c r="C47" s="18" t="s">
         <v>2</v>
       </c>
@@ -2644,7 +2662,7 @@
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="71"/>
+      <c r="B48" s="74"/>
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
@@ -2665,7 +2683,7 @@
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="71"/>
+      <c r="B49" s="74"/>
       <c r="C49" s="18" t="s">
         <v>10</v>
       </c>
@@ -2686,7 +2704,7 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="71"/>
+      <c r="B50" s="74"/>
       <c r="C50" s="18" t="s">
         <v>11</v>
       </c>
@@ -2699,7 +2717,7 @@
       <c r="H50" s="35"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="71"/>
+      <c r="B51" s="74"/>
       <c r="C51" s="18" t="s">
         <v>12</v>
       </c>
@@ -2712,7 +2730,7 @@
       <c r="H51" s="35"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="71"/>
+      <c r="B52" s="74"/>
       <c r="C52" s="18" t="s">
         <v>13</v>
       </c>
@@ -2725,7 +2743,7 @@
       <c r="H52" s="35"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="71"/>
+      <c r="B53" s="74"/>
       <c r="C53" s="18" t="s">
         <v>14</v>
       </c>
@@ -2738,7 +2756,7 @@
       <c r="H53" s="35"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="71"/>
+      <c r="B54" s="74"/>
       <c r="C54" s="18" t="s">
         <v>15</v>
       </c>
@@ -2759,7 +2777,7 @@
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="71"/>
+      <c r="B55" s="74"/>
       <c r="C55" s="18" t="s">
         <v>16</v>
       </c>
@@ -2772,7 +2790,7 @@
       <c r="H55" s="35"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="71"/>
+      <c r="B56" s="74"/>
       <c r="C56" s="18" t="s">
         <v>18</v>
       </c>
@@ -2785,7 +2803,7 @@
       <c r="H56" s="35"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="72"/>
+      <c r="B57" s="75"/>
       <c r="C57" s="37" t="s">
         <v>19</v>
       </c>
@@ -2810,7 +2828,7 @@
       <c r="H58" s="58"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="73" t="s">
+      <c r="B59" s="76" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="25" t="s">
@@ -2831,7 +2849,7 @@
       <c r="H59" s="40"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="74"/>
+      <c r="B60" s="77"/>
       <c r="C60" s="15" t="s">
         <v>2</v>
       </c>
@@ -2852,7 +2870,7 @@
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="74"/>
+      <c r="B61" s="77"/>
       <c r="C61" s="15" t="s">
         <v>9</v>
       </c>
@@ -2873,7 +2891,7 @@
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="74"/>
+      <c r="B62" s="77"/>
       <c r="C62" s="15" t="s">
         <v>10</v>
       </c>
@@ -2886,7 +2904,7 @@
       <c r="H62" s="41"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="74"/>
+      <c r="B63" s="77"/>
       <c r="C63" s="15" t="s">
         <v>11</v>
       </c>
@@ -2899,7 +2917,7 @@
       <c r="H63" s="41"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="74"/>
+      <c r="B64" s="77"/>
       <c r="C64" s="15" t="s">
         <v>12</v>
       </c>
@@ -2912,7 +2930,7 @@
       <c r="H64" s="41"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="74"/>
+      <c r="B65" s="77"/>
       <c r="C65" s="15" t="s">
         <v>13</v>
       </c>
@@ -2925,7 +2943,7 @@
       <c r="H65" s="41"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="74"/>
+      <c r="B66" s="77"/>
       <c r="C66" s="15" t="s">
         <v>14</v>
       </c>
@@ -2938,7 +2956,7 @@
       <c r="H66" s="41"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="74"/>
+      <c r="B67" s="77"/>
       <c r="C67" s="15" t="s">
         <v>15</v>
       </c>
@@ -2959,7 +2977,7 @@
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="74"/>
+      <c r="B68" s="77"/>
       <c r="C68" s="15" t="s">
         <v>16</v>
       </c>
@@ -2972,7 +2990,7 @@
       <c r="H68" s="41"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="74"/>
+      <c r="B69" s="77"/>
       <c r="C69" s="15" t="s">
         <v>18</v>
       </c>
@@ -2985,7 +3003,7 @@
       <c r="H69" s="41"/>
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="75"/>
+      <c r="B70" s="78"/>
       <c r="C70" s="29" t="s">
         <v>19</v>
       </c>
@@ -3010,14 +3028,14 @@
       <c r="H71" s="58"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="70" t="s">
+      <c r="B72" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="C72" s="32" t="s">
+      <c r="C72" s="53" t="s">
         <v>1</v>
       </c>
       <c r="D72" s="32">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="E72" s="42" t="s">
         <v>77</v>
@@ -3031,12 +3049,12 @@
       <c r="H72" s="34"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="71"/>
-      <c r="C73" s="18" t="s">
+      <c r="B73" s="74"/>
+      <c r="C73" s="50" t="s">
         <v>2</v>
       </c>
       <c r="D73" s="18">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>87</v>
@@ -3052,12 +3070,12 @@
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="71"/>
-      <c r="C74" s="18" t="s">
+      <c r="B74" s="74"/>
+      <c r="C74" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="18">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>100</v>
@@ -3073,13 +3091,11 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="71"/>
+      <c r="B75" s="74"/>
       <c r="C75" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D75" s="18">
-        <v>176</v>
-      </c>
+      <c r="D75" s="18"/>
       <c r="E75" s="20" t="s">
         <v>75</v>
       </c>
@@ -3094,7 +3110,7 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="71"/>
+      <c r="B76" s="74"/>
       <c r="C76" s="18" t="s">
         <v>11</v>
       </c>
@@ -3107,7 +3123,7 @@
       <c r="H76" s="35"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="71"/>
+      <c r="B77" s="74"/>
       <c r="C77" s="18" t="s">
         <v>12</v>
       </c>
@@ -3120,7 +3136,7 @@
       <c r="H77" s="35"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="71"/>
+      <c r="B78" s="74"/>
       <c r="C78" s="18" t="s">
         <v>13</v>
       </c>
@@ -3133,7 +3149,7 @@
       <c r="H78" s="35"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="71"/>
+      <c r="B79" s="74"/>
       <c r="C79" s="18" t="s">
         <v>14</v>
       </c>
@@ -3146,12 +3162,12 @@
       <c r="H79" s="35"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="71"/>
-      <c r="C80" s="18" t="s">
+      <c r="B80" s="74"/>
+      <c r="C80" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="18">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="E80" s="20" t="s">
         <v>101</v>
@@ -3167,7 +3183,7 @@
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="71"/>
+      <c r="B81" s="74"/>
       <c r="C81" s="18" t="s">
         <v>16</v>
       </c>
@@ -3180,7 +3196,7 @@
       <c r="H81" s="35"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="71"/>
+      <c r="B82" s="74"/>
       <c r="C82" s="18" t="s">
         <v>18</v>
       </c>
@@ -3193,12 +3209,12 @@
       <c r="H82" s="35"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="72"/>
-      <c r="C83" s="37" t="s">
+      <c r="B83" s="75"/>
+      <c r="C83" s="51" t="s">
         <v>19</v>
       </c>
       <c r="D83" s="37">
-        <v>211</v>
+        <v>313</v>
       </c>
       <c r="E83" s="38" t="s">
         <v>254</v>
@@ -3217,7 +3233,7 @@
       <c r="H84" s="58"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="73" t="s">
+      <c r="B85" s="76" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="25" t="s">
@@ -3238,7 +3254,7 @@
       <c r="H85" s="40"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="74"/>
+      <c r="B86" s="77"/>
       <c r="C86" s="15" t="s">
         <v>2</v>
       </c>
@@ -3259,7 +3275,7 @@
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="74"/>
+      <c r="B87" s="77"/>
       <c r="C87" s="15" t="s">
         <v>9</v>
       </c>
@@ -3280,7 +3296,7 @@
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="74"/>
+      <c r="B88" s="77"/>
       <c r="C88" s="15" t="s">
         <v>10</v>
       </c>
@@ -3293,7 +3309,7 @@
       <c r="H88" s="41"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="74"/>
+      <c r="B89" s="77"/>
       <c r="C89" s="15" t="s">
         <v>11</v>
       </c>
@@ -3306,7 +3322,7 @@
       <c r="H89" s="28"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" s="74"/>
+      <c r="B90" s="77"/>
       <c r="C90" s="15" t="s">
         <v>12</v>
       </c>
@@ -3319,7 +3335,7 @@
       <c r="H90" s="28"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="74"/>
+      <c r="B91" s="77"/>
       <c r="C91" s="15" t="s">
         <v>13</v>
       </c>
@@ -3332,7 +3348,7 @@
       <c r="H91" s="28"/>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="74"/>
+      <c r="B92" s="77"/>
       <c r="C92" s="15" t="s">
         <v>14</v>
       </c>
@@ -3345,7 +3361,7 @@
       <c r="H92" s="28"/>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="74"/>
+      <c r="B93" s="77"/>
       <c r="C93" s="15" t="s">
         <v>15</v>
       </c>
@@ -3366,7 +3382,7 @@
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="74"/>
+      <c r="B94" s="77"/>
       <c r="C94" s="15" t="s">
         <v>16</v>
       </c>
@@ -3379,7 +3395,7 @@
       <c r="H94" s="28"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="74"/>
+      <c r="B95" s="77"/>
       <c r="C95" s="15" t="s">
         <v>18</v>
       </c>
@@ -3392,7 +3408,7 @@
       <c r="H95" s="28"/>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="75"/>
+      <c r="B96" s="78"/>
       <c r="C96" s="29" t="s">
         <v>19</v>
       </c>
@@ -3417,7 +3433,7 @@
       <c r="H97" s="56"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="70" t="s">
+      <c r="B98" s="73" t="s">
         <v>160</v>
       </c>
       <c r="C98" s="32" t="s">
@@ -3438,7 +3454,7 @@
       <c r="H98" s="43"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="71"/>
+      <c r="B99" s="74"/>
       <c r="C99" s="18" t="s">
         <v>2</v>
       </c>
@@ -3459,7 +3475,7 @@
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="71"/>
+      <c r="B100" s="74"/>
       <c r="C100" s="18" t="s">
         <v>9</v>
       </c>
@@ -3480,7 +3496,7 @@
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="71"/>
+      <c r="B101" s="74"/>
       <c r="C101" s="18" t="s">
         <v>10</v>
       </c>
@@ -3501,7 +3517,7 @@
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="71"/>
+      <c r="B102" s="74"/>
       <c r="C102" s="18" t="s">
         <v>11</v>
       </c>
@@ -3514,7 +3530,7 @@
       <c r="H102" s="36"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="71"/>
+      <c r="B103" s="74"/>
       <c r="C103" s="18" t="s">
         <v>12</v>
       </c>
@@ -3527,7 +3543,7 @@
       <c r="H103" s="36"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="71"/>
+      <c r="B104" s="74"/>
       <c r="C104" s="18" t="s">
         <v>13</v>
       </c>
@@ -3540,20 +3556,28 @@
       <c r="H104" s="36"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="71"/>
+      <c r="B105" s="74"/>
       <c r="C105" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="18"/>
-      <c r="E105" s="20"/>
-      <c r="F105" s="20"/>
+      <c r="D105" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>313</v>
+      </c>
       <c r="G105" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="H105" s="36"/>
+      <c r="H105" s="36" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="71"/>
+      <c r="B106" s="74"/>
       <c r="C106" s="18" t="s">
         <v>15</v>
       </c>
@@ -3574,20 +3598,28 @@
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="71"/>
+      <c r="B107" s="74"/>
       <c r="C107" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D107" s="18"/>
-      <c r="E107" s="20"/>
-      <c r="F107" s="20"/>
+      <c r="D107" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E107" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="F107" s="20" t="s">
+        <v>315</v>
+      </c>
       <c r="G107" s="48" t="s">
         <v>246</v>
       </c>
-      <c r="H107" s="36"/>
+      <c r="H107" s="36" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="71"/>
+      <c r="B108" s="74"/>
       <c r="C108" s="18" t="s">
         <v>18</v>
       </c>
@@ -3600,7 +3632,7 @@
       <c r="H108" s="36"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="72"/>
+      <c r="B109" s="75"/>
       <c r="C109" s="37" t="s">
         <v>19</v>
       </c>
@@ -3622,11 +3654,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="B72:B83"/>
     <mergeCell ref="B85:B96"/>
     <mergeCell ref="B98:B109"/>
@@ -3635,6 +3662,11 @@
     <mergeCell ref="B33:B44"/>
     <mergeCell ref="B46:B57"/>
     <mergeCell ref="B59:B70"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -3660,19 +3692,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="78"/>
+      <c r="C3" s="71"/>
       <c r="D3" s="80" t="s">
         <v>6</v>
       </c>
@@ -3680,10 +3712,10 @@
       <c r="F3" s="82"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="78"/>
+      <c r="C4" s="71"/>
       <c r="D4" s="80" t="s">
         <v>8</v>
       </c>

--- a/LİNKLER_Ademden.xlsx
+++ b/LİNKLER_Ademden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BA29E5-AD45-434B-8B32-32DDB01B9D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22AF26E-1BF2-4866-812C-8D65A5A00E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="319">
   <si>
     <t>DERS KİTAPLARINDA YER ALAN KAREKOD BİLGİLERİ</t>
   </si>
@@ -993,6 +993,27 @@
     <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=0e5aa0333fdcff9dff7e9dec4b39269a&amp;resourceType=1&amp;resourceLocation=2</t>
   </si>
   <si>
+    <t>Akran 8.1</t>
+  </si>
+  <si>
+    <t>mm_81akran_mk</t>
+  </si>
+  <si>
+    <t>Grup 8.1</t>
+  </si>
+  <si>
+    <t>mm_81grup_mk</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=ad2bcdbe346be64237f6399eb85e4300&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=075d0be38ae0e1bcf74c3aa830d29e1e&amp;resourceType=1&amp;resourceLocation=2</t>
+  </si>
+  <si>
+    <t>385, 390, 394, 396</t>
+  </si>
+  <si>
     <t>T1: 34, 40, 42
 T2: 48, 52, 56, 57, 59, 60, 61, 63, 64, 66, 67, 72, 73, 74, 76, 83
 T3: 99, 100, 101, 107, 112, 115
@@ -1000,25 +1021,7 @@
 T5: 165, 170, 177, 179, 181, 193
 T6: 248, 254, 256, 284, 285, 294, 300, 303
 T7:
-T8:</t>
-  </si>
-  <si>
-    <t>Akran 8.1</t>
-  </si>
-  <si>
-    <t>mm_81akran_mk</t>
-  </si>
-  <si>
-    <t>Grup 8.1</t>
-  </si>
-  <si>
-    <t>mm_81grup_mk</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=ad2bcdbe346be64237f6399eb85e4300&amp;resourceType=1&amp;resourceLocation=2</t>
-  </si>
-  <si>
-    <t>https://ders.eba.gov.tr/ders//redirectContent.jsp?resourceId=075d0be38ae0e1bcf74c3aa830d29e1e&amp;resourceType=1&amp;resourceLocation=2</t>
+T8: -</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1080,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1096,12 +1099,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -1372,7 +1369,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1519,18 +1516,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1545,9 +1533,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1914,41 +1899,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72" t="s">
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="72" t="s">
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
     </row>
     <row r="5" spans="2:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="21"/>
@@ -1960,52 +1945,52 @@
       <c r="H5" s="44"/>
     </row>
     <row r="6" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="66" t="s">
+      <c r="E6" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="65" t="s">
+      <c r="F6" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="64" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="56">
         <v>13</v>
       </c>
-      <c r="E7" s="61" t="s">
+      <c r="E7" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="58" t="s">
         <v>284</v>
       </c>
-      <c r="H7" s="63"/>
+      <c r="H7" s="59"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="77"/>
-      <c r="C8" s="50" t="s">
+      <c r="B8" s="73"/>
+      <c r="C8" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="15">
@@ -2025,8 +2010,8 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="77"/>
-      <c r="C9" s="50" t="s">
+      <c r="B9" s="73"/>
+      <c r="C9" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="15">
@@ -2046,12 +2031,12 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="77"/>
-      <c r="C10" s="50" t="s">
+      <c r="B10" s="73"/>
+      <c r="C10" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>306</v>
@@ -2059,16 +2044,16 @@
       <c r="F10" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="H10" s="55" t="s">
+      <c r="H10" s="52" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="77"/>
-      <c r="C11" s="50" t="s">
+      <c r="B11" s="73"/>
+      <c r="C11" s="15" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -2088,8 +2073,8 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="77"/>
-      <c r="C12" s="50" t="s">
+      <c r="B12" s="73"/>
+      <c r="C12" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="15">
@@ -2109,8 +2094,8 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="77"/>
-      <c r="C13" s="50" t="s">
+      <c r="B13" s="73"/>
+      <c r="C13" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="15">
@@ -2130,7 +2115,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="77"/>
+      <c r="B14" s="73"/>
       <c r="C14" s="15" t="s">
         <v>14</v>
       </c>
@@ -2143,8 +2128,8 @@
       <c r="H14" s="28"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="77"/>
-      <c r="C15" s="50" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="15">
@@ -2164,8 +2149,8 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="77"/>
-      <c r="C16" s="50" t="s">
+      <c r="B16" s="73"/>
+      <c r="C16" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="15">
@@ -2185,7 +2170,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="77"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="15" t="s">
         <v>18</v>
       </c>
@@ -2198,8 +2183,8 @@
       <c r="H17" s="28"/>
     </row>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="78"/>
-      <c r="C18" s="51" t="s">
+      <c r="B18" s="74"/>
+      <c r="C18" s="29" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="29">
@@ -2220,10 +2205,10 @@
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="73" t="s">
+      <c r="B20" s="69" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="32" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="32">
@@ -2235,14 +2220,14 @@
       <c r="F20" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="52" t="s">
+      <c r="G20" s="50" t="s">
         <v>285</v>
       </c>
       <c r="H20" s="34"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="74"/>
-      <c r="C21" s="50" t="s">
+      <c r="B21" s="70"/>
+      <c r="C21" s="18" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="18">
@@ -2262,8 +2247,8 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="74"/>
-      <c r="C22" s="50" t="s">
+      <c r="B22" s="70"/>
+      <c r="C22" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="18">
@@ -2283,7 +2268,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="74"/>
+      <c r="B23" s="70"/>
       <c r="C23" s="18" t="s">
         <v>10</v>
       </c>
@@ -2296,7 +2281,7 @@
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="74"/>
+      <c r="B24" s="70"/>
       <c r="C24" s="18" t="s">
         <v>11</v>
       </c>
@@ -2309,7 +2294,7 @@
       <c r="H24" s="36"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="74"/>
+      <c r="B25" s="70"/>
       <c r="C25" s="18" t="s">
         <v>12</v>
       </c>
@@ -2322,7 +2307,7 @@
       <c r="H25" s="36"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="74"/>
+      <c r="B26" s="70"/>
       <c r="C26" s="18" t="s">
         <v>13</v>
       </c>
@@ -2335,7 +2320,7 @@
       <c r="H26" s="36"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="74"/>
+      <c r="B27" s="70"/>
       <c r="C27" s="18" t="s">
         <v>14</v>
       </c>
@@ -2348,8 +2333,8 @@
       <c r="H27" s="36"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="74"/>
-      <c r="C28" s="50" t="s">
+      <c r="B28" s="70"/>
+      <c r="C28" s="18" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="18">
@@ -2369,7 +2354,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="74"/>
+      <c r="B29" s="70"/>
       <c r="C29" s="18" t="s">
         <v>16</v>
       </c>
@@ -2382,7 +2367,7 @@
       <c r="H29" s="36"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="74"/>
+      <c r="B30" s="70"/>
       <c r="C30" s="18" t="s">
         <v>18</v>
       </c>
@@ -2395,8 +2380,8 @@
       <c r="H30" s="36"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="75"/>
-      <c r="C31" s="51" t="s">
+      <c r="B31" s="71"/>
+      <c r="C31" s="37" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="37">
@@ -2417,10 +2402,10 @@
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F32" s="24"/>
-      <c r="H32" s="56"/>
+      <c r="H32" s="53"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="76" t="s">
+      <c r="B33" s="72" t="s">
         <v>155</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -2441,7 +2426,7 @@
       <c r="H33" s="40"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="77"/>
+      <c r="B34" s="73"/>
       <c r="C34" s="15" t="s">
         <v>2</v>
       </c>
@@ -2462,7 +2447,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="77"/>
+      <c r="B35" s="73"/>
       <c r="C35" s="15" t="s">
         <v>9</v>
       </c>
@@ -2483,7 +2468,7 @@
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="77"/>
+      <c r="B36" s="73"/>
       <c r="C36" s="15" t="s">
         <v>10</v>
       </c>
@@ -2496,7 +2481,7 @@
       <c r="H36" s="28"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="77"/>
+      <c r="B37" s="73"/>
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
@@ -2509,7 +2494,7 @@
       <c r="H37" s="41"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="77"/>
+      <c r="B38" s="73"/>
       <c r="C38" s="15" t="s">
         <v>12</v>
       </c>
@@ -2522,7 +2507,7 @@
       <c r="H38" s="41"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="77"/>
+      <c r="B39" s="73"/>
       <c r="C39" s="15" t="s">
         <v>13</v>
       </c>
@@ -2535,7 +2520,7 @@
       <c r="H39" s="41"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="77"/>
+      <c r="B40" s="73"/>
       <c r="C40" s="15" t="s">
         <v>14</v>
       </c>
@@ -2548,7 +2533,7 @@
       <c r="H40" s="41"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="77"/>
+      <c r="B41" s="73"/>
       <c r="C41" s="15" t="s">
         <v>15</v>
       </c>
@@ -2569,7 +2554,7 @@
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="77"/>
+      <c r="B42" s="73"/>
       <c r="C42" s="15" t="s">
         <v>16</v>
       </c>
@@ -2582,7 +2567,7 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="77"/>
+      <c r="B43" s="73"/>
       <c r="C43" s="15" t="s">
         <v>18</v>
       </c>
@@ -2595,7 +2580,7 @@
       <c r="H43" s="41"/>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="78"/>
+      <c r="B44" s="74"/>
       <c r="C44" s="29" t="s">
         <v>19</v>
       </c>
@@ -2617,10 +2602,10 @@
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F45" s="24"/>
-      <c r="H45" s="57"/>
+      <c r="H45" s="54"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="73" t="s">
+      <c r="B46" s="69" t="s">
         <v>156</v>
       </c>
       <c r="C46" s="32" t="s">
@@ -2635,13 +2620,13 @@
       <c r="F46" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="G46" s="52" t="s">
+      <c r="G46" s="50" t="s">
         <v>287</v>
       </c>
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="74"/>
+      <c r="B47" s="70"/>
       <c r="C47" s="18" t="s">
         <v>2</v>
       </c>
@@ -2662,7 +2647,7 @@
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="74"/>
+      <c r="B48" s="70"/>
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
@@ -2683,7 +2668,7 @@
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="74"/>
+      <c r="B49" s="70"/>
       <c r="C49" s="18" t="s">
         <v>10</v>
       </c>
@@ -2704,7 +2689,7 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="74"/>
+      <c r="B50" s="70"/>
       <c r="C50" s="18" t="s">
         <v>11</v>
       </c>
@@ -2717,7 +2702,7 @@
       <c r="H50" s="35"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="74"/>
+      <c r="B51" s="70"/>
       <c r="C51" s="18" t="s">
         <v>12</v>
       </c>
@@ -2730,7 +2715,7 @@
       <c r="H51" s="35"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="74"/>
+      <c r="B52" s="70"/>
       <c r="C52" s="18" t="s">
         <v>13</v>
       </c>
@@ -2743,7 +2728,7 @@
       <c r="H52" s="35"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="74"/>
+      <c r="B53" s="70"/>
       <c r="C53" s="18" t="s">
         <v>14</v>
       </c>
@@ -2756,7 +2741,7 @@
       <c r="H53" s="35"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="74"/>
+      <c r="B54" s="70"/>
       <c r="C54" s="18" t="s">
         <v>15</v>
       </c>
@@ -2777,7 +2762,7 @@
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="74"/>
+      <c r="B55" s="70"/>
       <c r="C55" s="18" t="s">
         <v>16</v>
       </c>
@@ -2790,7 +2775,7 @@
       <c r="H55" s="35"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="74"/>
+      <c r="B56" s="70"/>
       <c r="C56" s="18" t="s">
         <v>18</v>
       </c>
@@ -2803,7 +2788,7 @@
       <c r="H56" s="35"/>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="75"/>
+      <c r="B57" s="71"/>
       <c r="C57" s="37" t="s">
         <v>19</v>
       </c>
@@ -2825,10 +2810,10 @@
     </row>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F58" s="24"/>
-      <c r="H58" s="58"/>
+      <c r="H58" s="55"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="76" t="s">
+      <c r="B59" s="72" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="25" t="s">
@@ -2849,7 +2834,7 @@
       <c r="H59" s="40"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="77"/>
+      <c r="B60" s="73"/>
       <c r="C60" s="15" t="s">
         <v>2</v>
       </c>
@@ -2870,7 +2855,7 @@
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="77"/>
+      <c r="B61" s="73"/>
       <c r="C61" s="15" t="s">
         <v>9</v>
       </c>
@@ -2891,7 +2876,7 @@
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="77"/>
+      <c r="B62" s="73"/>
       <c r="C62" s="15" t="s">
         <v>10</v>
       </c>
@@ -2904,7 +2889,7 @@
       <c r="H62" s="41"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="77"/>
+      <c r="B63" s="73"/>
       <c r="C63" s="15" t="s">
         <v>11</v>
       </c>
@@ -2917,7 +2902,7 @@
       <c r="H63" s="41"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="77"/>
+      <c r="B64" s="73"/>
       <c r="C64" s="15" t="s">
         <v>12</v>
       </c>
@@ -2930,7 +2915,7 @@
       <c r="H64" s="41"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="77"/>
+      <c r="B65" s="73"/>
       <c r="C65" s="15" t="s">
         <v>13</v>
       </c>
@@ -2943,7 +2928,7 @@
       <c r="H65" s="41"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="77"/>
+      <c r="B66" s="73"/>
       <c r="C66" s="15" t="s">
         <v>14</v>
       </c>
@@ -2956,7 +2941,7 @@
       <c r="H66" s="41"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="77"/>
+      <c r="B67" s="73"/>
       <c r="C67" s="15" t="s">
         <v>15</v>
       </c>
@@ -2977,7 +2962,7 @@
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="77"/>
+      <c r="B68" s="73"/>
       <c r="C68" s="15" t="s">
         <v>16</v>
       </c>
@@ -2990,7 +2975,7 @@
       <c r="H68" s="41"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="77"/>
+      <c r="B69" s="73"/>
       <c r="C69" s="15" t="s">
         <v>18</v>
       </c>
@@ -3003,7 +2988,7 @@
       <c r="H69" s="41"/>
     </row>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="78"/>
+      <c r="B70" s="74"/>
       <c r="C70" s="29" t="s">
         <v>19</v>
       </c>
@@ -3016,7 +3001,7 @@
       <c r="F70" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="G70" s="69" t="s">
+      <c r="G70" s="65" t="s">
         <v>215</v>
       </c>
       <c r="H70" s="31" t="s">
@@ -3025,13 +3010,13 @@
     </row>
     <row r="71" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F71" s="24"/>
-      <c r="H71" s="58"/>
+      <c r="H71" s="55"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="73" t="s">
+      <c r="B72" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="C72" s="53" t="s">
+      <c r="C72" s="32" t="s">
         <v>1</v>
       </c>
       <c r="D72" s="32">
@@ -3043,14 +3028,14 @@
       <c r="F72" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="G72" s="52" t="s">
+      <c r="G72" s="50" t="s">
         <v>289</v>
       </c>
       <c r="H72" s="34"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="74"/>
-      <c r="C73" s="50" t="s">
+      <c r="B73" s="70"/>
+      <c r="C73" s="18" t="s">
         <v>2</v>
       </c>
       <c r="D73" s="18">
@@ -3070,8 +3055,8 @@
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="74"/>
-      <c r="C74" s="50" t="s">
+      <c r="B74" s="70"/>
+      <c r="C74" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="18">
@@ -3091,7 +3076,7 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="74"/>
+      <c r="B75" s="70"/>
       <c r="C75" s="18" t="s">
         <v>10</v>
       </c>
@@ -3110,7 +3095,7 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="74"/>
+      <c r="B76" s="70"/>
       <c r="C76" s="18" t="s">
         <v>11</v>
       </c>
@@ -3123,7 +3108,7 @@
       <c r="H76" s="35"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="74"/>
+      <c r="B77" s="70"/>
       <c r="C77" s="18" t="s">
         <v>12</v>
       </c>
@@ -3136,7 +3121,7 @@
       <c r="H77" s="35"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="74"/>
+      <c r="B78" s="70"/>
       <c r="C78" s="18" t="s">
         <v>13</v>
       </c>
@@ -3149,7 +3134,7 @@
       <c r="H78" s="35"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="74"/>
+      <c r="B79" s="70"/>
       <c r="C79" s="18" t="s">
         <v>14</v>
       </c>
@@ -3162,8 +3147,8 @@
       <c r="H79" s="35"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="74"/>
-      <c r="C80" s="50" t="s">
+      <c r="B80" s="70"/>
+      <c r="C80" s="18" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="18">
@@ -3183,7 +3168,7 @@
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="74"/>
+      <c r="B81" s="70"/>
       <c r="C81" s="18" t="s">
         <v>16</v>
       </c>
@@ -3196,7 +3181,7 @@
       <c r="H81" s="35"/>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="74"/>
+      <c r="B82" s="70"/>
       <c r="C82" s="18" t="s">
         <v>18</v>
       </c>
@@ -3209,8 +3194,8 @@
       <c r="H82" s="35"/>
     </row>
     <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="75"/>
-      <c r="C83" s="51" t="s">
+      <c r="B83" s="71"/>
+      <c r="C83" s="37" t="s">
         <v>19</v>
       </c>
       <c r="D83" s="37">
@@ -3230,10 +3215,10 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H84" s="58"/>
+      <c r="H84" s="55"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="76" t="s">
+      <c r="B85" s="72" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="25" t="s">
@@ -3254,7 +3239,7 @@
       <c r="H85" s="40"/>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="77"/>
+      <c r="B86" s="73"/>
       <c r="C86" s="15" t="s">
         <v>2</v>
       </c>
@@ -3275,7 +3260,7 @@
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="77"/>
+      <c r="B87" s="73"/>
       <c r="C87" s="15" t="s">
         <v>9</v>
       </c>
@@ -3296,7 +3281,7 @@
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="77"/>
+      <c r="B88" s="73"/>
       <c r="C88" s="15" t="s">
         <v>10</v>
       </c>
@@ -3309,7 +3294,7 @@
       <c r="H88" s="41"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="77"/>
+      <c r="B89" s="73"/>
       <c r="C89" s="15" t="s">
         <v>11</v>
       </c>
@@ -3322,7 +3307,7 @@
       <c r="H89" s="28"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" s="77"/>
+      <c r="B90" s="73"/>
       <c r="C90" s="15" t="s">
         <v>12</v>
       </c>
@@ -3335,7 +3320,7 @@
       <c r="H90" s="28"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="77"/>
+      <c r="B91" s="73"/>
       <c r="C91" s="15" t="s">
         <v>13</v>
       </c>
@@ -3348,7 +3333,7 @@
       <c r="H91" s="28"/>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="77"/>
+      <c r="B92" s="73"/>
       <c r="C92" s="15" t="s">
         <v>14</v>
       </c>
@@ -3361,7 +3346,7 @@
       <c r="H92" s="28"/>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="77"/>
+      <c r="B93" s="73"/>
       <c r="C93" s="15" t="s">
         <v>15</v>
       </c>
@@ -3382,7 +3367,7 @@
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="77"/>
+      <c r="B94" s="73"/>
       <c r="C94" s="15" t="s">
         <v>16</v>
       </c>
@@ -3395,7 +3380,7 @@
       <c r="H94" s="28"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="77"/>
+      <c r="B95" s="73"/>
       <c r="C95" s="15" t="s">
         <v>18</v>
       </c>
@@ -3408,7 +3393,7 @@
       <c r="H95" s="28"/>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="78"/>
+      <c r="B96" s="74"/>
       <c r="C96" s="29" t="s">
         <v>19</v>
       </c>
@@ -3430,17 +3415,17 @@
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F97" s="24"/>
-      <c r="H97" s="56"/>
+      <c r="H97" s="53"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" s="73" t="s">
+      <c r="B98" s="69" t="s">
         <v>160</v>
       </c>
       <c r="C98" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D98" s="32" t="s">
-        <v>88</v>
+      <c r="D98" s="32">
+        <v>377</v>
       </c>
       <c r="E98" s="42" t="s">
         <v>84</v>
@@ -3448,18 +3433,18 @@
       <c r="F98" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="G98" s="52" t="s">
+      <c r="G98" s="50" t="s">
         <v>291</v>
       </c>
       <c r="H98" s="43"/>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="74"/>
+      <c r="B99" s="70"/>
       <c r="C99" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D99" s="18" t="s">
-        <v>88</v>
+      <c r="D99" s="18">
+        <v>377</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>85</v>
@@ -3475,12 +3460,12 @@
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" s="74"/>
+      <c r="B100" s="70"/>
       <c r="C100" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D100" s="18" t="s">
-        <v>88</v>
+      <c r="D100" s="18">
+        <v>378</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>104</v>
@@ -3496,12 +3481,12 @@
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" s="74"/>
+      <c r="B101" s="70"/>
       <c r="C101" s="18" t="s">
         <v>10</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>88</v>
+        <v>317</v>
       </c>
       <c r="E101" s="20" t="s">
         <v>308</v>
@@ -3517,7 +3502,7 @@
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="74"/>
+      <c r="B102" s="70"/>
       <c r="C102" s="18" t="s">
         <v>11</v>
       </c>
@@ -3530,7 +3515,7 @@
       <c r="H102" s="36"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="74"/>
+      <c r="B103" s="70"/>
       <c r="C103" s="18" t="s">
         <v>12</v>
       </c>
@@ -3543,7 +3528,7 @@
       <c r="H103" s="36"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B104" s="74"/>
+      <c r="B104" s="70"/>
       <c r="C104" s="18" t="s">
         <v>13</v>
       </c>
@@ -3556,33 +3541,33 @@
       <c r="H104" s="36"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B105" s="74"/>
+      <c r="B105" s="70"/>
       <c r="C105" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="18" t="s">
-        <v>88</v>
+      <c r="D105" s="18">
+        <v>393</v>
       </c>
       <c r="E105" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="F105" s="20" t="s">
         <v>312</v>
-      </c>
-      <c r="F105" s="20" t="s">
-        <v>313</v>
       </c>
       <c r="G105" s="48" t="s">
         <v>244</v>
       </c>
       <c r="H105" s="36" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B106" s="74"/>
+      <c r="B106" s="70"/>
       <c r="C106" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="18" t="s">
-        <v>88</v>
+      <c r="D106" s="18">
+        <v>393</v>
       </c>
       <c r="E106" s="20" t="s">
         <v>105</v>
@@ -3598,28 +3583,28 @@
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="74"/>
+      <c r="B107" s="70"/>
       <c r="C107" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D107" s="18" t="s">
-        <v>88</v>
+      <c r="D107" s="18">
+        <v>393</v>
       </c>
       <c r="E107" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="F107" s="20" t="s">
         <v>314</v>
-      </c>
-      <c r="F107" s="20" t="s">
-        <v>315</v>
       </c>
       <c r="G107" s="48" t="s">
         <v>246</v>
       </c>
       <c r="H107" s="36" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="74"/>
+      <c r="B108" s="70"/>
       <c r="C108" s="18" t="s">
         <v>18</v>
       </c>
@@ -3632,12 +3617,12 @@
       <c r="H108" s="36"/>
     </row>
     <row r="109" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="75"/>
+      <c r="B109" s="71"/>
       <c r="C109" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="D109" s="37" t="s">
-        <v>88</v>
+      <c r="D109" s="37">
+        <v>397</v>
       </c>
       <c r="E109" s="38" t="s">
         <v>256</v>
@@ -3692,35 +3677,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="80" t="s">
+      <c r="C3" s="67"/>
+      <c r="D3" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="82"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="78"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="80" t="s">
+      <c r="C4" s="67"/>
+      <c r="D4" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="82"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="78"/>
     </row>
     <row r="5" spans="2:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
